--- a/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
@@ -678,10 +678,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
+      <c r="A2" s="3" t="n">
+        <v>2001</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>2.7399</v>
@@ -754,10 +752,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="A3" s="3" t="n">
+        <v>2002</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>1.4304</v>
@@ -827,10 +823,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="A4" s="3" t="n">
+        <v>2003</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.4452</v>
@@ -897,10 +891,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="A5" s="3" t="n">
+        <v>2004</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>1.1416</v>
@@ -964,10 +956,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="A6" s="3" t="n">
+        <v>2005</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>1.3029</v>
@@ -1028,10 +1018,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="A7" s="3" t="n">
+        <v>2006</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1.5119</v>
@@ -1089,10 +1077,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>2007</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>1.0888</v>
@@ -1147,10 +1133,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+      <c r="A9" s="3" t="n">
+        <v>2008</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1.3857</v>
@@ -1202,10 +1186,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>2009</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>2.4408</v>
@@ -1254,10 +1236,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>2010</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>2.0292</v>
@@ -1303,10 +1283,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A12" s="3" t="n">
+        <v>2011</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>1.9534</v>
@@ -1349,10 +1327,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A13" s="3" t="n">
+        <v>2012</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>2.0319</v>
@@ -1392,10 +1368,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A14" s="3" t="n">
+        <v>2013</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>1.8261</v>
@@ -1432,10 +1406,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A15" s="3" t="n">
+        <v>2014</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>1.3662</v>
@@ -1469,10 +1441,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="A16" s="3" t="n">
+        <v>2015</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1.9857</v>
@@ -1503,10 +1473,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="A17" s="3" t="n">
+        <v>2016</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>1.8697</v>
@@ -1534,10 +1502,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
+      <c r="A18" s="3" t="n">
+        <v>2017</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1.3328</v>
@@ -1562,10 +1528,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="A19" s="3" t="n">
+        <v>2018</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>2.2994</v>
@@ -1587,10 +1551,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="A20" s="3" t="n">
+        <v>2019</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>2.757</v>
@@ -1609,10 +1571,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="A21" s="3" t="n">
+        <v>2020</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>1.7849</v>
@@ -1628,10 +1588,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="A22" s="3" t="n">
+        <v>2021</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>1.4577</v>
@@ -1644,10 +1602,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="A23" s="3" t="n">
+        <v>2022</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>1.2261</v>
@@ -1657,183 +1613,250 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="A24" s="3" t="n">
+        <v>2023</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>1.6941</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Averages</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>11-23</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>23-35</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>35-47</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>59-71</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83-95</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>95-107</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>107-119</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>119-131</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>131-143</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>143-155</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>155-167</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>179-191</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>191-203</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>203-215</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>215-227</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>239-251</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>251-263</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>263-275</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>275-287</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Averages</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11-23</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>23-35</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>35-47</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>59-71</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>83-95</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>95-107</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>107-119</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>119-131</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>131-143</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>143-155</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>155-167</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>167-179</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>179-191</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>191-203</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>203-215</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>215-227</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>227-239</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>239-251</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>251-263</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>263-275</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>275-287</t>
-        </is>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Average - 3 Years</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1.4593</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1.0596</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1.0798</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1.1226</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1.1022</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.0127</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1.0152</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1.0586</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>1.0092</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.0166</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>1.0119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Average - 3 Years</t>
+          <t>Weighted Average - 3 Years</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>1.4593</v>
+        <v>1.4891</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.0596</v>
+        <v>1.054</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.0798</v>
+        <v>1.0948</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.0225</v>
+        <v>1.0233</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.1226</v>
+        <v>1.1167</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.1022</v>
+        <v>1.0898</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.0127</v>
+        <v>1.0085</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.0152</v>
+        <v>1.0098</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.0389</v>
+        <v>1.0629</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.0002</v>
+        <v>0.9997</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.0586</v>
+        <v>1.0531</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>1.0004</v>
@@ -1845,13 +1868,13 @@
         <v>1.002</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.0016</v>
+        <v>1.0009</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0066</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.0033</v>
+        <v>1.0027</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>1</v>
@@ -1860,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.9979</v>
+        <v>0.9973</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.0166</v>
+        <v>1.0174</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>1</v>
@@ -1875,71 +1898,71 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 3 Years</t>
+          <t>Average - 5 Years</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1.4891</v>
+        <v>1.784</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.054</v>
+        <v>1.2309</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.0948</v>
+        <v>1.1874</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.0233</v>
+        <v>1.057</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.1167</v>
+        <v>1.1071</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.0898</v>
+        <v>1.0836</v>
       </c>
       <c r="H29" s="4" t="n">
+        <v>1.0076</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>1.0354</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>1.0059</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>1.0379</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>1.0086</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="4" t="n">
         <v>1.0085</v>
       </c>
-      <c r="I29" s="4" t="n">
-        <v>1.0098</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>1.0629</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0.9997</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>1.0531</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>1.0004</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>1.0066</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>1.0027</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="U29" s="4" t="n">
-        <v>0.9973</v>
+        <v>1.0043</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.0174</v>
+        <v>1.0166</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>1</v>
@@ -1951,56 +1974,56 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Average - 5 Years</t>
+          <t>Weighted Average - 5 Years</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1.784</v>
+        <v>1.7024</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.2309</v>
+        <v>1.2575</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.1874</v>
+        <v>1.2002</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.057</v>
+        <v>1.0567</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.1071</v>
+        <v>1.1027</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.0836</v>
+        <v>1.087</v>
       </c>
       <c r="H30" s="4" t="n">
+        <v>1.0065</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>1.0146</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>1.0485</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>1.0082</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>1.0211</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="Q30" s="4" t="n">
         <v>1.0076</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>1.0354</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>1.0059</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>1.0379</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="Q30" s="4" t="n">
-        <v>1.0086</v>
       </c>
       <c r="R30" s="4" t="n">
         <v>1.002</v>
@@ -2009,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.0085</v>
+        <v>1.0089</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.0043</v>
+        <v>1.0069</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.0166</v>
+        <v>1.0174</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>1</v>
@@ -2027,71 +2050,71 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 5 Years</t>
+          <t>Exclude High/Low - 5 Years</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>1.7024</v>
+        <v>1.6456</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.2575</v>
+        <v>1.212</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.2002</v>
+        <v>1.1724</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.0567</v>
+        <v>1.0494</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.1027</v>
+        <v>1.1002</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.087</v>
+        <v>1.098</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.0065</v>
+        <v>1.0023</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.0146</v>
+        <v>1.0154</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.0485</v>
+        <v>1.027</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.0082</v>
+        <v>1.0028</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.035</v>
+        <v>1.0045</v>
       </c>
       <c r="M31" s="4" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="O31" s="4" t="n">
         <v>1.0022</v>
       </c>
-      <c r="N31" s="4" t="n">
-        <v>1.0004</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>1.0211</v>
-      </c>
       <c r="P31" s="4" t="n">
-        <v>1.0036</v>
+        <v>1.004</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.0076</v>
+        <v>1.0073</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.002</v>
+        <v>1.0008</v>
       </c>
       <c r="S31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.0089</v>
+        <v>1</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.0069</v>
+        <v>1</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.0174</v>
+        <v>1.0139</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>1</v>
@@ -2103,71 +2126,71 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Exclude High/Low - 5 Years</t>
+          <t>Average - 10 Years</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>1.6456</v>
+        <v>1.7774</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.212</v>
+        <v>1.2539</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.1724</v>
+        <v>1.1801</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.0494</v>
+        <v>1.053</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.1002</v>
+        <v>1.0646</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.098</v>
+        <v>1.0554</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.0023</v>
+        <v>1.0248</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.0154</v>
+        <v>1.019</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.027</v>
+        <v>1.0351</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.0028</v>
+        <v>1.016</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.0045</v>
+        <v>1.0387</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.0004</v>
+        <v>1.0056</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.0034</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.0022</v>
+        <v>1.0104</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.004</v>
+        <v>1.0106</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.0073</v>
+        <v>1.0152</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.0008</v>
+        <v>1.006</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1</v>
+        <v>1.003</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>1</v>
+        <v>1.0085</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1</v>
+        <v>1.0043</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.0139</v>
+        <v>1.0166</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>1</v>
@@ -2179,71 +2202,71 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Average - 10 Years</t>
+          <t>Weighted Average - 10 Years</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1.7774</v>
+        <v>1.7371</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.2539</v>
+        <v>1.2877</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.1801</v>
+        <v>1.1886</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.053</v>
+        <v>1.0574</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.0646</v>
+        <v>1.0752</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.0554</v>
+        <v>1.0671</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.0248</v>
+        <v>1.0177</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.019</v>
+        <v>1.0231</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.0351</v>
+        <v>1.0519</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.016</v>
+        <v>1.0194</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.0387</v>
+        <v>1.0395</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.0056</v>
+        <v>1.0066</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.0034</v>
+        <v>1.003</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.0104</v>
+        <v>1.0167</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.0106</v>
+        <v>1.0116</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.0152</v>
+        <v>1.0149</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.006</v>
+        <v>1.0069</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.003</v>
+        <v>1.0045</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.0085</v>
+        <v>1.0089</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.0043</v>
+        <v>1.0069</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.0166</v>
+        <v>1.0174</v>
       </c>
       <c r="W33" s="4" t="n">
         <v>1</v>
@@ -2255,71 +2278,71 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 10 Years</t>
+          <t>Exclude High/Low - 10 Years</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>1.7371</v>
+        <v>1.7238</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.2877</v>
+        <v>1.2525</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.1886</v>
+        <v>1.1727</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.0574</v>
+        <v>1.0491</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.0752</v>
+        <v>1.0543</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.0671</v>
+        <v>1.0537</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.0177</v>
+        <v>1.013</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.0231</v>
+        <v>1.0154</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.0519</v>
+        <v>1.0312</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.0194</v>
+        <v>1.0105</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.0395</v>
+        <v>1.0274</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.0066</v>
+        <v>1.005</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.003</v>
+        <v>1.0015</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.0167</v>
+        <v>1.0075</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.0116</v>
+        <v>1.006</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.0149</v>
+        <v>1.0114</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.0069</v>
+        <v>1.0022</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.0045</v>
+        <v>1</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.0089</v>
+        <v>1</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.0069</v>
+        <v>1</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.0174</v>
+        <v>1.0139</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>1</v>
@@ -2331,59 +2354,59 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Exclude High/Low - 10 Years</t>
+          <t>Min - All Years</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>1.7238</v>
+        <v>1.0888</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.2525</v>
+        <v>0.8692</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.1727</v>
+        <v>0.9755</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.0491</v>
+        <v>0.9077</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.0543</v>
+        <v>0.9893</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1.0537</v>
+        <v>0.9714</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.013</v>
+        <v>0.9816</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.0154</v>
+        <v>0.9953</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.0312</v>
+        <v>0.9911</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.0105</v>
+        <v>0.9931</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.0274</v>
+        <v>0.9887</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.005</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>1.0015</v>
+        <v>0.9816</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.0075</v>
+        <v>1</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.006</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1.0114</v>
+        <v>1</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>1.0022</v>
+        <v>1</v>
       </c>
       <c r="S35" s="4" t="n">
         <v>1</v>
@@ -2392,10 +2415,10 @@
         <v>1</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1</v>
+        <v>0.9938</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>1.0139</v>
+        <v>1</v>
       </c>
       <c r="W35" s="4" t="n">
         <v>1</v>
@@ -2407,71 +2430,71 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Min - All Years</t>
+          <t>Max - All Years</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>1.0888</v>
+        <v>2.757</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.8692</v>
+        <v>1.5473</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.9755</v>
+        <v>1.391</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.9077</v>
+        <v>1.1423</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.9893</v>
+        <v>1.2221</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.9714</v>
+        <v>1.1527</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.9816</v>
+        <v>1.1441</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.9953</v>
+        <v>1.0716</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0.9911</v>
+        <v>1.1016</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.9931</v>
+        <v>1.0832</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.9887</v>
+        <v>1.179</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.9816</v>
+        <v>1.0401</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>1</v>
+        <v>1.0436</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>1</v>
+        <v>1.0532</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1</v>
+        <v>1.0529</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>1</v>
+        <v>1.0309</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>1</v>
+        <v>1.018</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>1</v>
+        <v>1.0424</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>0.9938</v>
+        <v>1.0234</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>1</v>
+        <v>1.0359</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>1</v>
@@ -2483,144 +2506,141 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max - All Years</t>
+          <t>CV - 10 Years</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2.757</v>
+        <v>0.2694</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1.5473</v>
+        <v>0.1768</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1.391</v>
+        <v>0.1051</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.1423</v>
+        <v>0.0465</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.2221</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1.1527</v>
+        <v>0.0599</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.1441</v>
+        <v>0.0442</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1.0716</v>
+        <v>0.0266</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1016</v>
+        <v>0.0374</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1.0832</v>
+        <v>0.0262</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>1.179</v>
+        <v>0.061</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1.03</v>
+        <v>0.0142</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1.0401</v>
+        <v>0.0147</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>1.0436</v>
+        <v>0.0146</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>1.0532</v>
+        <v>0.0166</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1.0529</v>
+        <v>0.0175</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>1.0309</v>
+        <v>0.0112</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1.018</v>
+        <v>0.0073</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>1.0424</v>
+        <v>0.0188</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>1.0234</v>
+        <v>0.013</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>1.0359</v>
+        <v>0.0178</v>
       </c>
       <c r="W37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" s="4" t="n">
-        <v>1.0119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CV - 10 Years</t>
+          <t>CV - 3 Years</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>0.2694</v>
+        <v>0.1604</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.1768</v>
+        <v>0.1345</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.1051</v>
+        <v>0.0574</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.0465</v>
+        <v>0.0355</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0934</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.0599</v>
+        <v>0.0606</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0442</v>
+        <v>0.0164</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.0266</v>
+        <v>0.0221</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.0374</v>
+        <v>0.0488</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.0262</v>
+        <v>0.0072</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.061</v>
+        <v>0.0985</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0008</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.0147</v>
+        <v>0.0001</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0035</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.0166</v>
+        <v>0.0028</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.0175</v>
+        <v>0.0101</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0.0112</v>
+        <v>0.0037</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.0073</v>
+        <v>0</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>0.0188</v>
+        <v>0</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0036</v>
       </c>
       <c r="V38" s="4" t="n">
         <v>0.0178</v>
@@ -2632,68 +2652,68 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CV - 3 Years</t>
+          <t>CV - 5 Years</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>0.1604</v>
+        <v>0.3284</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.1345</v>
+        <v>0.2103</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.1316</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.0355</v>
+        <v>0.0556</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.074</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0164</v>
+        <v>0.0136</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.0221</v>
+        <v>0.0254</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.0393</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.0134</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.0985</v>
+        <v>0.0762</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.0162</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>0.0035</v>
+        <v>0.0187</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0.0028</v>
+        <v>0.0049</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>0.0101</v>
+        <v>0.0089</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.0032</v>
       </c>
       <c r="S39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>0</v>
+        <v>0.0188</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.0036</v>
+        <v>0.013</v>
       </c>
       <c r="V39" s="4" t="n">
         <v>0.0178</v>
@@ -2705,71 +2725,71 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CV - 5 Years</t>
+          <t>Slope - 10 Years</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>0.3284</v>
+        <v>-0.0158</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.2103</v>
+        <v>-0.024</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.1316</v>
+        <v>-0.007</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0556</v>
+        <v>-0.001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0149</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.074</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0136</v>
+        <v>-0.0053</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.0254</v>
+        <v>-0.0023</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.0393</v>
+        <v>-0.0002</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.0134</v>
+        <v>-0.0048</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.0762</v>
+        <v>0.0008</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.0162</v>
+        <v>0.0002</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.0004</v>
+        <v>-0.0019</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.0187</v>
+        <v>-0.001</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.0049</v>
+        <v>-0.0039</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>0.0089</v>
+        <v>-0.0029</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>0.0032</v>
+        <v>-0.0026</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0</v>
+        <v>-0.0026</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>0.0188</v>
+        <v>-0.0042</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.013</v>
+        <v>-0.0064</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.0178</v>
+        <v>-0.0069</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0</v>
@@ -2778,68 +2798,68 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Slope - 10 Years</t>
+          <t>Slope - 3 Years</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>-0.0158</v>
+        <v>0.1182</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>-0.024</v>
+        <v>-0.0058</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>-0.007</v>
+        <v>-0.059</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>-0.001</v>
+        <v>0.0077</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.0149</v>
+        <v>0.0447</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0505</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.0053</v>
+        <v>0.0124</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-0.0023</v>
+        <v>-0.0199</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>-0.0002</v>
+        <v>0.0481</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-0.0048</v>
+        <v>-0.0072</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.0016</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>-0.0019</v>
+        <v>0</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-0.001</v>
+        <v>0.003</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>-0.0039</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>-0.0029</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>-0.0026</v>
+        <v>0.0013</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-0.0026</v>
+        <v>0</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-0.0042</v>
+        <v>0</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-0.0064</v>
+        <v>0.0031</v>
       </c>
       <c r="V41" s="4" t="n">
         <v>-0.0069</v>
@@ -2851,68 +2871,68 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Slope - 3 Years</t>
+          <t>Slope - 5 Years</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>0.1182</v>
+        <v>-0.2685</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.0058</v>
+        <v>-0.1238</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.059</v>
+        <v>-0.0886</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.0077</v>
+        <v>-0.0277</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.0153</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.0505</v>
+        <v>0.0123</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0063</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-0.0199</v>
+        <v>-0.0108</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.0481</v>
+        <v>0.0149</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-0.0072</v>
+        <v>-0.0044</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0016</v>
+        <v>0.0152</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="O42" s="4" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="Q42" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="P42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="R42" s="4" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="S42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>0</v>
+        <v>-0.0042</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>0.0031</v>
+        <v>-0.0064</v>
       </c>
       <c r="V42" s="4" t="n">
         <v>-0.0069</v>
@@ -2921,472 +2941,453 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Slope - 5 Years</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>-0.2685</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>-0.1238</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>-0.0886</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>-0.0277</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0.0153</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0.0063</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>-0.0108</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>0.0149</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>-0.0044</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>-0.0033</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>-0.0021</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R43" s="4" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="S43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="4" t="n">
-        <v>-0.0042</v>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>-0.0064</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>-0.0069</v>
-      </c>
-      <c r="W43" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Selected LDFs</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>11-23</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>23-35</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>35-47</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>59-71</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>83-95</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>95-107</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>107-119</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>119-131</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>131-143</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>143-155</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>155-167</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>179-191</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>191-203</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>203-215</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>215-227</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>239-251</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>251-263</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr">
+        <is>
+          <t>263-275</t>
+        </is>
+      </c>
+      <c r="X44" s="5" t="inlineStr">
+        <is>
+          <t>275-287</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Selected LDFs</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>11-23</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>23-35</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>35-47</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>59-71</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>83-95</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>95-107</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>107-119</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>119-131</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>131-143</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>143-155</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>155-167</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>167-179</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>179-191</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>191-203</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>203-215</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>215-227</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>227-239</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>239-251</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>251-263</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr">
-        <is>
-          <t>263-275</t>
-        </is>
-      </c>
-      <c r="X45" s="5" t="inlineStr">
-        <is>
-          <t>275-287</t>
-        </is>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.0085</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>1.6456</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>1.212</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>1.1724</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1.0494</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>1.1002</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>1.098</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>1.0023</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>1.0154</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>1.0028</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>1.0004</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>1.0022</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>1.004</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>1.0073</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>1.0008</v>
-      </c>
-      <c r="S46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1.0139</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.3284, high volatility). Outliers present: max=2.757, min=1.0888. Exclude top/bottom per protocol for CV&gt;0.20. 5-yr trim (1.6456) &lt; 5-yr weighted (1.7024), suggesting recent large variance. Early maturity incurred development typically lower than paid; compare paid 2.5525 vs incurred 1.6456 (60% lower, expected). Use 5-yr trim with downward asymmetric conservatism applied implicitly.</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.2103). Outlier handling: max=1.5473, min=0.8692. Exclude 1 high, 1 low per protocol. Trim=1.2120 balances: 3-yr=1.0596 (recent slowdown), 5-yr weighted=1.2575 (older data influence). Diagnostic: paid_to_incurred ratio rising gradually, case reserves stabilizing. Select 5-yr trim (1.2120) for baseline; reflects developing incurred position.</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.1316). Moderate volatility. Trim=1.1724, simple=1.1874, weighted=1.2002. Convergence present but wide: 10yr trim=1.1727 nearly matches 5yr. 3yr trend downward (1.0798) suggests case reserve influence or slower settlement. Diagnostic: check paid (1.1437) vs incurred; paid &lt; incurred as expected in early development. Select 1.1724 for conservative early-maturity incurred.</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0556). Tight convergence: 5yr trim=1.0494, 10yr trim=1.0491, within ±0.1%. All high/low exclusions minimal (max=1.1423, min=0.9077). Slope_5yr=-0.0277 (gentle decline). Early-to-mid transition; incurred still developing but slower. Select 1.0494.</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0773). Moderate CV triggers caution. Trim=1.1002, simple=1.1071, weighted=1.1027. 5-yr vs 3-yr divergence: 5yr=1.1002, 3yr=1.1226, ~2% apart. Trend signal: slope_5yr=0.0153 (upward), slope_3yr=0.0447 (accelerating). Case reserve diagnostic likely supporting modest LDF increase. Select 1.1002 with monitoring for severity trends.</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0740). Trend check: slope_5yr=0.0123 (weak), slope_3yr=-0.0505 (negative). Averages: trim=1.0980, simple=1.0836, weighted=1.0870. 3-yr (1.1022) vs 5-yr (1.0980) show modest acceleration downward recently. Bayesian anchoring to 5-yr trim: 1.0980, reflecting settled incurred position near paid convergence.</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0136, very low). Tight convergence: trim=1.0023, weighted=1.0065, simple=1.0076. Slope near zero. Mid-to-late maturity; incurred and paid converge. Many diagonals show min=0.9816, max=1.1441, but recent values 1.00-1.01. Select 1.0023 for low late-stage incurred development.</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0254). Slight elevation vs prior. Trim=1.0154, weighted=1.0146, simple=1.0207. Slope_5yr=-0.0108 (slight decline). Mid-maturity 95-107 months; sparse recent data. Use 5-yr trim; incurred reserve releases moderately. Select 1.0154.</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0393). Moderate CV with upward signal. Trim=1.0270, weighted=1.0485, simple=1.0354. Divergence: 5-yr (1.0270) vs 3-yr (1.0389) +1% recent uptick. Slope_5yr=0.0149 (positive). Case reserve emergence likely; select 5-yr trim (1.0270) with acknowledgment of recent strength.</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0134, tight). Convergence: trim=1.0028, weighted=1.0082, simple=1.0059. Slope_5yr=-0.0044 (flat). 3-yr (1.0002) much lower, suggesting recent favorable development or closure slowdown. Use 5-yr trim (1.0028) for baseline; sparse data caution increases at this maturity.</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0762, elevated for this range). Indicates outlier variability: max=1.1790, min=0.9887. Exclude 1 high, 1 low. Trim=1.0045 vs weighted=1.0350, significant difference. Recent 3-yr (1.0586) higher. Slope_5yr=0.0152 (positive trend). At 131-143 months, incurred development slowing; select 1.0045 for conservatism.</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0162, low). Extreme convergence zone: trim=1.0004, weighted=1.0022, simple=1.0033. Slope near zero. Late maturity; minimal incremental incurred expected. Select 1.0004, essentially 1.0 for practical purposes.</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0004, near-zero). All averages 1.00-1.0030. Slope zero. Tail zone; incurred claims essentially final. Select 1.0001.</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0187). Slight elevation from prior; trim=1.0022, weighted=1.0211, simple=1.0100. Older data (10-yr) shows 1.0167; recent 3-yr very close to trim at 1.0020. Tail factor; minimal recent incurred activity. Select 1.0022.</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0049). Trim=1.0040, weighted=1.0036, simple=1.0047. All tight within ±0.1%. Slope_5yr=-0.0021 (flat). Sparse tail; select 1.0040.</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0089). Trim=1.0073, weighted=1.0076, simple=1.0086. Slight uptick vs prior. Very sparse (2-3 diagonals). Slope=0.0030 (weak positive). Select 1.0073 as upper end of tight tail band.</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0032, very low). Trim=1.0008, all others 1.0020-1.0069. Slope=0.0012 (flat). Ultra-sparse tail (1-2 recent data points). Select 1.0008 for conservative tail LDF.</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0, zero variance). All averages exactly 1.0 or within 0.0001. At 215-227 months (19 years), incurred claims fully closed. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0188). Averages: trim=1.0000, weighted=1.0089, simple=1.0085. Min=1.0, max=1.0424. Sparse (2 diagonals). Select 1.0000 as most credible tail assumption; incurred tail effectively settled.</t>
-        </is>
-      </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0130). All recent diagonals show 1.0 or marginal variation (max=1.0234). Extreme sparsity (1-2 diagonals). Select 1.0000 for tail.</t>
-        </is>
-      </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0178). Final tail observations: trim=1.0139, weighted=1.0174, simple=1.0166. All recent values cluster 1.01-1.02. Sparse but consistent signal. Select 1.0139 as final LDF before curve fit; tail completion.</t>
-        </is>
-      </c>
-      <c r="W47" s="3" t="inlineStr">
-        <is>
-          <t>[CUTOFF] CUTOFF at 263 months: CV=0.0, indicating only 1 data point or identical values. Incurred triangle complete by 263 months. Beyond this, apply tail curve (constant 1.0 or minimal decay). No explicit LDF selected; tail initiated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>1.6800 selected. High variance (CV_5yr=0.33, CV_3yr=0.16) with meaningful 3yr vs 5yr divergence (1.489 vs 1.702). The 3yr window is depressed by AY2020 (1.785) and AY2022 (1.226), while the 5yr picks up higher recent years (2018: 2.299, 2019: 2.757). Incurred severity is rising strongly in recent origin years (2022: ~2774 at age 35, 2023: ~5419 at age 23), and case reserves at age 11 are elevated and growing (2023: 607K, 2024: 535K), consistent with delayed case development requiring a higher factor. Paid-to-incurred ratios at 11 months are declining in recent years (2023: 0.38, 2024: 0.40), confirming large unreleased case reserves. No convergence — averages diverge over 14%. Asymmetric conservatism applied: movement upward from 5yr weighted (1.702) is credible given severity trend, but early maturity warrants Bayesian anchoring. Splitting the difference between 5yr VW and the 10yr VW (1.737), blending toward 1.68 acknowledges the recent severity signal while capping volatility at early maturity. All-weighted = 1.614 but this is dragged down by older low-severity AYs.</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>1.2000 selected. CV_5yr=0.21 (high), CV_3yr=0.13. Recent AYs: 2020=0.983, 2021=1.224, 2022=0.972. The 3yr weighted (1.054) is heavily distorted by the two sub-1.0 factors (2020 and 2022), which are anomalous — sub-1.0 incurred LDFs at 23-35 months are possible (case reserve reductions) but require corroboration. The 5yr weighted (1.258) includes the strong 2018 and 2019 factors (1.429 and 1.547) and is more credible. Incurred severity progression confirms ongoing development in this range. The all-year weighted = 1.189 and 10yr = 1.288. Given the recent two-year depression in factors (potentially case reserve reductions in 2020 COVID period and 2022), treating these as partially transient and selecting near the midpoint of 5yr VW and all-year VW. Asymmetric conservatism applied (downward movement from 5yr, move 30-50% of gap): 5yr = 1.258, all = 1.189, gap from 5yr to selected = 0.058. Selection of 1.200 reflects modest conservatism, staying above the anomalous 3yr average.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>1.1650 selected. CV_5yr=0.13, CV_3yr=0.057 (low-moderate). 3yr VW=1.095, 5yr VW=1.200, 10yr VW=1.189, all VW=1.153. Recent AYs trend lower: 2020=1.058, 2021=1.032, 2022 has no 35-47 factor yet. The 3yr is materially below the 5yr (gap ~10.5%). Incurred severity shows heterogeneous development in this range — some AYs resolve quickly, others don't. Applying partial convergence weighting: 5yr VW (1.200) has meaningful CV suggesting more weight on 5yr vs 3yr. Mid-maturity range, relaxed asymmetric conservatism. Selected as blend: 60% on 5yr (1.200) + 40% on 3yr (1.095) = ~1.158, rounded up slightly to 1.165 for conservative bias at this still-early maturity stage.</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>1.0490 selected. CV_5yr=0.056, CV_3yr=0.036 (both low). All averages converge well: 3yr VW=1.023, 5yr VW=1.057, 10yr VW=1.057, all VW=1.049. The 3yr appears slightly low (1.023) due to AY2020 (1.010), otherwise factors are stable in the 1.04-1.14 range for most AYs. Partial convergence between 5yr and all-year (within ~1%). 5yr VW of 1.057 is consistent with all-year. Selection of 1.049 follows the volume-weighted all-year average which best captures the central tendency in a stable column with moderate data.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1.0900 selected. CV_5yr=0.077, CV_3yr=0.093 (moderate). 3yr VW=1.117, 5yr VW=1.103, 10yr VW=1.075, all VW=1.074. Recent trend is slightly upward — 2019=1.222, 2020=1.010, while 2017=1.133 and 2018=1.013. The 3yr and 5yr are elevated relative to all-year, indicating recent LDFs are running higher. The slope over 3yr is positive (0.045). However, the 2019 factor (1.222) is the highest recent point, and 2020 (1.010) follows up as a potentially COVID-affected low. Incurred severity in recent AYs for this maturity range is elevated. Select near the 5yr VW (1.103), dampened slightly toward the all-year (1.074), reflecting trending but with asymmetric conservatism on the upside movement. Selection of 1.090 represents approximately 60% weight on the 5yr VW.</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1.0750 selected. CV_5yr=0.074, CV_3yr=0.061. 3yr VW=1.090, 5yr VW=1.087, 10yr VW=1.067, all VW=1.046. The 3yr and 5yr averages are consistent with each other and notably above the 10yr/all-year, indicating a regime shift toward higher development in recent years. Incurred severity data supports ongoing case reserve increases. Paid-to-incurred ratios in mid-maturity remain below benchmark in recent AYs (e.g., 2017: 0.844, 2018: 0.969, 2019: 0.921), suggesting case reserves remain active. 3yr slope is positive at 0.45 but recent 2 LDFs (2018: 1.027, 2019: not yet visible at 71-83) show some stabilization. Selection of 1.075 is approximately equal to the 5yr VW, supported by convergence of 3yr and 5yr, with slight dampening from 10yr.</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>1.0085 selected. CV_5yr=0.014 (low), CV_3yr=0.016. Very stable column. 3yr VW=1.009, 5yr VW=1.007, 10yr VW=1.018, all VW=1.022. Recent LDFs are low: 2017=1.032, 2016=1.000, 2018=N/A at this maturity. The convergence between 3yr and 5yr VW (within 0.2%) is strong. All-year is slightly higher due to older AYs. Selection follows 5yr VW closely. No trend signal, low CV — stable development at this maturity.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>1.0150 selected. CV_5yr=0.025, CV_3yr=0.022 (low). 3yr VW=1.010, 5yr VW=1.013, 10yr VW=1.023, all VW=1.020. Recent factors are low (2016: 1.001, 2015: 1.003) while older AYs (2007: 1.072) pull up the all-year. The 5yr and 3yr averages converge around 1.010-1.015. Selection at 1.015 is slightly above the 5yr VW to account for the possibility that recent very-low factors in 2015-2016 understate long-run development, consistent with the 10yr average of 1.023. Incurred severity at this maturity shows ongoing small increases in some AYs.</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>1.0380 selected. CV_5yr=0.039, CV_3yr=0.049 (low-moderate). 3yr VW=1.063, 5yr VW=1.049, 10yr VW=1.052, all VW=1.037. Recent factors include 2015: 1.096 (notably high, driven by case reserve increases visible in the 2015 case reserve data). 2016: N/A, 2014: 1.021. The 3yr is elevated due to 2015's 1.096 factor. The 5yr and 10yr converge around 1.049-1.052 and are most credible. Selection of 1.038 follows the all-year weighted which best reflects central tendency excluding the 2015 outlier influence, consistent with stable mid-late development.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>1.0075 selected. CV_5yr=0.013, CV_3yr=0.007 (very low). All averages converge tightly: 3yr VW=1.000, 5yr VW=1.008, 10yr VW=1.019, all VW=1.017. The 3yr is pinned to 1.000 by three consecutive 1.000 factors for AYs 2013-2015. The 5yr and 10yr are slightly higher. Convergence override does not fully apply since 3yr vs 5yr diverge by ~0.8pp. Selection at 1.0075, midpoint of the 3yr (1.000) and 5yr (1.008), reflecting the stable low-development pattern at this late maturity.</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1.0300 selected. CV_5yr=0.076, CV_3yr=0.099 (moderate). 3yr VW=1.053, 5yr VW=1.035, 10yr VW=1.040, all VW=1.033. The high CV is driven by AY2012 (1.179), which is a clear outlier (large reserve strengthening in one period). Excluding the outlier, 5yr ex-hi/lo = 1.005 which goes too far down. The all-year VW (1.033) and 5yr VW (1.035) converge nicely and represent credible central tendency. Selection follows 5yr/all-year convergence, reflecting normal case reserve fluctuation at this mature age.</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.0050 selected. CV_5yr=0.016 (very low). All averages converge: 3yr=1.000, 5yr VW=1.002, 10yr VW=1.007, all VW=1.005. Near-convergence across all windows (within 0.7pp). 5yr VW and all VW are essentially identical. Selection follows the all-year VW of 1.005, reflecting very small residual development at this maturity. Late maturity behavior consistent.</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>1.0050 selected. CV very low (3yr=0.000, 5yr=0.000). All averages essentially converge: 3yr=1.000, 5yr=1.000, all VW=1.005, 10yr=1.003. The all-year VW pulls slightly above 1.000 due to AY2001 (1.023) and AY2002 (1.040). Selection of 1.005 follows the all-year VW, which captures the full history of residual development at this late maturity stage.</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>1.0100 selected. CV low (3yr=0.004, 5yr=0.019). 3yr=1.002, 5yr VW=1.021, 10yr VW=1.017, all VW=1.017. Some variation across windows. At late maturity (167+ months), all-year window appropriate per guidelines. All-year VW of 1.017 and 10yr VW of 1.017 converge. Selection of 1.010 applies modest conservatism below the all-year (some recent AYs showing zero development confirms declining tail).</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>CUTOFF at 179 months: This is the last selected interval before the tail begins. CV is very low (5yr=0.005, 3yr=0.003). Averages: 3yr=1.001, 5yr VW=1.004, 10yr VW=1.012, all VW=1.012. Most recent AYs showing 1.000-1.005 range. Selection of 1.003 reflects the low recent development visible in the 3yr and 5yr averages, consistent with declining tail activity. The pattern at 179+ months is monotonically very small and converging to 1.000.</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] CUTOFF at 191 months: is_monotone_from_here=True, CV at this interval is near-zero (3yr=0.010, 5yr=0.009), factors are stable near 1.005-1.015 range but sparse. Only a few points remain in each column at this maturity, satisfying sparse data caution. Rejected further selection (191+) due to fewer than 5 credible data points per interval and near-zero incremental development. Tail curve fitting should commence from 191 months using the residual CDF. Minimum cutoff for Incurred Loss (48 months) is exceeded.</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>1.0050. Weighted-all and simple-all are both around 1.006-1.007. Recent 3-year and 5-year averages are 1.002-1.003. Very stable with nearly all factors at 1.000. A selection of 1.005 captures residual development.</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>1.0030. All averages show 1.003-1.005. Nearly all individual factors are 1.000. The simple/weighted averages across all periods are 1.003-1.005. Selected at 1.003.</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t>1.0050. Weighted-all is 1.009, simple-all is 1.009. The 3-year averages are 1.000. Several years show 1.000 and a few show 1.042 (2002). The weighted average gives more weight to larger observations. A conservative selection of 1.005 reflects modest development.</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>1.0050. Weighted-all is 1.007, simple-all is 1.004. Some factors at 1.000 and some at 1.023 (2001). A selection of 1.005 is consistent.</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>1.0150. The weighted-all and simple-all are both 1.017. The only observation is 2001 (1.014) and 2002 (1.036). With limited data at this age, 1.015 is reasonable, reflecting the central tendency of available factors.</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000. All averages show 1.000. Both available years (2001, 2002) show 1.000. Selected at 1.000.</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 275 months. Only one observation available (2001: 1.012). With a single data point at this age, the tail curve fitting is more appropriate than a direct LDF selection. Development beyond 275 months is sparse and a tail factor from an actuarial tail curve (e.g., inverse power or exponential) should be applied from 275 months to ultimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Curve Comparison</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Curve Comparison</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Starting Age</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Monotone</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Slope Breaks</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Params</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Tail Factor</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>LOO Std Dev</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Gap to Last</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Gap Flag</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>% of CDF</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>Materiality OK</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>+10% Reserve Delta</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>+20% Reserve Delta</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Starting Age</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Monotone</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Slope Breaks</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Params</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Tail Factor</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>LOO Std Dev</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Gap to Last</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>Gap Flag</t>
-        </is>
-      </c>
-      <c r="L50" s="6" t="inlineStr">
-        <is>
-          <t>% of CDF</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="inlineStr">
-        <is>
-          <t>Materiality OK</t>
-        </is>
-      </c>
-      <c r="N50" s="6" t="inlineStr">
-        <is>
-          <t>+10% Reserve Delta</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>+20% Reserve Delta</t>
-        </is>
+      <c r="A50" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>bondy</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.0027474184711859</v>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="n">
+        <v>0.1323533699663513</v>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>1213817.056821216</v>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>2225331.27083889</v>
       </c>
     </row>
     <row r="51">
@@ -3399,40 +3400,51 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0166</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>bondy</t>
+          <t>exp_dev_product</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>[0.23444059238507584, 0.7335764658174152]</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1.0139</v>
+        <v>1.008462582139825</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0.7951445871346084</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.00616397916586861</v>
+        <v>0.0004325761287872</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>0.4455594076149241</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L51" s="16" t="n">
+        <v>0.3704428138725135</v>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L51" s="16" t="n">
-        <v>0.6161254347557812</v>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N51" s="17" t="n">
-        <v>1217778.028490737</v>
+        <v>1207242.122368481</v>
       </c>
       <c r="O51" s="17" t="n">
-        <v>2232593.052233014</v>
+        <v>2213277.224342212</v>
       </c>
     </row>
     <row r="52">
@@ -3445,32 +3457,32 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0166</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>exp_dev_product</t>
+          <t>exp_dev_quick</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>[0.18888031380014414, 0.7009257203486053]</t>
+          <t>[0.23444059238507584, 0.7335764658174152]</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1.000360224231498</v>
+        <v>1.073794389778644</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.4421310131361682</v>
+        <v>0.7951445871346084</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.0009516299714606005</v>
+        <v>0.0004325761287872</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.4567196861998558</v>
+        <v>0.4455594076149241</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
@@ -3478,18 +3490,18 @@
         </is>
       </c>
       <c r="L52" s="16" t="n">
-        <v>0.01628093459639258</v>
+        <v>2.955051243775014</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>1234260.532534957</v>
+        <v>1133791.086618222</v>
       </c>
       <c r="O52" s="17" t="n">
-        <v>2262810.976314083</v>
+        <v>2078616.992133401</v>
       </c>
     </row>
     <row r="53">
@@ -3502,32 +3514,32 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0166</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>exp_dev_quick</t>
+          <t>exp_dev_quick_exact_last</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>[0.18888031380014414, 0.7009257203486053]</t>
+          <t>[0.23444059238507584, 0.7335764658174152]</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1.036794559106135</v>
+        <v>1.072256401496538</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.4421310131361682</v>
+        <v>0.7951445871346084</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.0009516299714606005</v>
+        <v>0.0004325761287872</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>0.4567196861998558</v>
+        <v>0.4455594076149241</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -3535,7 +3547,7 @@
         </is>
       </c>
       <c r="L53" s="16" t="n">
-        <v>1.579465519164238</v>
+        <v>2.899278950246448</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -3543,10 +3555,10 @@
         </is>
       </c>
       <c r="N53" s="17" t="n">
-        <v>1190886.981651649</v>
+        <v>1135417.337021705</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>2183292.799694683</v>
+        <v>2081598.451206464</v>
       </c>
     </row>
     <row r="54">
@@ -3559,51 +3571,42 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0166</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>exp_dev_quick_exact_last</t>
+          <t>mcclenahan</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>[0.18888031380014414, 0.7009257203486053]</t>
+          <t>{"r": 0.34194035}</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>4.305002369900423</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>0.4421310131361682</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>0.0009516299714606005</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>0.4567196861998558</v>
+        <v>1.000000000006545</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="n">
+        <v>2.899905898746657e-10</v>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L54" s="16" t="n">
-        <v>25.7698660424147</v>
-      </c>
-      <c r="M54" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N54" s="17" t="n">
-        <v>286807.0762793422</v>
+        <v>1217458.507983714</v>
       </c>
       <c r="O54" s="17" t="n">
-        <v>525812.973178789</v>
+        <v>2232007.264636807</v>
       </c>
     </row>
     <row r="55">
@@ -3616,10 +3619,10 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0166</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -3627,7 +3630,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1.0278</v>
+        <v>1.006</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3638,7 @@
         </is>
       </c>
       <c r="L55" s="16" t="n">
-        <v>1.208342335212693</v>
+        <v>0.2635705920394596</v>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
@@ -3643,10 +3646,10 @@
         </is>
       </c>
       <c r="N55" s="17" t="n">
-        <v>1201308.759570688</v>
+        <v>1210197.324047402</v>
       </c>
       <c r="O55" s="17" t="n">
-        <v>2202399.392546259</v>
+        <v>2218695.094086893</v>
       </c>
     </row>
     <row r="56">
@@ -3659,10 +3662,10 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.0178</v>
+        <v>0.0166</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3670,7 +3673,7 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1.02799321</v>
+        <v>1.006009</v>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
@@ -3678,7 +3681,7 @@
         </is>
       </c>
       <c r="L56" s="16" t="n">
-        <v>1.216412257368116</v>
+        <v>0.2639625490662615</v>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
@@ -3686,10 +3689,10 @@
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>1201082.97513634</v>
+        <v>1210186.497329228</v>
       </c>
       <c r="O56" s="17" t="n">
-        <v>2201985.454416618</v>
+        <v>2218675.245103583</v>
       </c>
     </row>
     <row r="57"/>
@@ -3730,12 +3733,12 @@
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>exp_dev_product</t>
+          <t>bondy</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>Incurred loss triangle — expect medium-length tail, materially shorter than paid loss. Exponential product form selected for its ability to achieve rapid decay to 1.0 tail. At 263-month cutoff, cv_at_starting_age = 0.0178 (tight convergence), n_factors_in_fit = 21 (strong basis). Gap Rule hard requirement satisfied: gap_flag = False, gap_to_last_observed = 0.457 (within acceptable range for product form discretization). Fit quality: R² = 0.4421, LOO std dev = 0.000952 (acceptable; product method does not compute traditional R²). Tail factor = 1.00036, pct_of_cdf = 0.0163% (materiality anchor applies strongly). All exponential summation methods (exp_dev_quick, exp_dev_quick_exact_last) rejected due to gap_flag = True (gap = 0.4567, disconnects from last selected LDF). Modified Bondy variants acceptable but inferior: tail = 1.0278-1.0280, less consistent with empirical convergence pattern. Product form avoids overshooting the tail and maintains mathematical rigor. Sensitivity analysis: ±10% reserve delta ≈ ±1.23M, indicating moderate reserve impact; tail material for incurred loss but immaterial by percentage of CDF. Selection represents best balance of fit quality, convergence characteristics, and materiality.</t>
+          <t>Incurred loss triangle — expect medium tail length, longer than Reported Count and shorter than Paid Loss. The cutoff is set at 179 months (interval 179-191) with is_monotone_from_here=False, cv_at_starting_age=0.0166 (acceptable/low), slope_sign_changes=7 across 15 fitted factors, and n_factors_in_fit=15. The non-monotone pattern and 7 slope sign changes indicate structural irregularities in the late-age incurred development, likely reflecting case reserve adjustments that produce a choppy pattern rather than smooth decay. The min_selected_ldf=1.000, max_selected_ldf=1.053, avg_selected_ldf=1.012 confirm that selected LDFs at the cutoff are small but not negligible. Gap Rule (hard requirement): All exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) have gap_flag=True with gap_to_last_observed=0.446. This is a decisive rejection — the fitted exponential curve at the starting age extrapolates to approximately 1.073, while the last selected LDF is approximately 1.003 (Bondy value). The magnitude of the gap (0.446 on the factor minus 1 scale) reflects that the exponential fit is being driven upward by the irregular development pattern at early fitted ages, making it an inappropriate anchor for the tail. All three exponential methods are disqualified by the Gap Rule. Remaining valid candidates after Gap Rule: bondy (tail=1.003, gap_flag=False), modified_bondy_double_dev (tail=1.006, gap_flag=False), modified_bondy_square_ratio (tail=1.006, gap_flag=False), and mcclenahan (tail~1.000, gap_flag=False). The mcclenahan method is designed for count triangles and is inappropriate for incurred loss dollar triangles — rejected on triangle type grounds. The modified_bondy_double_dev and modified_bondy_square_ratio methods yield tail=1.006, representing 2x the last factor increment; however, given the irregular, non-monotone incurred development with slope sign changes, doubling the last factor introduces an upward adjustment not supported by the data pattern. The bondy method (tail=1.003) directly applies the last stable observed factor as the tail, which is the most defensible choice when the empirical development is irregular and a smooth curve cannot be anchored without violating the Gap Rule. Fit quality: R² is not applicable to Bondy variants (no regression fit performed); LOO std dev for bondy=0.00275, within acceptable range; no residual pattern concerns since no curve is being extrapolated. Anchor Rule: The materiality anchor applies — pct_of_cdf=0.132% and materiality_ok=False, indicating the tail is immaterial relative to total CDF. With a tail of 1.003 and such low materiality, additional precision in the curve method provides no meaningful reserve benefit. Sensitivity: +10% tail delta = $1.21M, -10% = -$1.48M, confirming the tail is small relative to total reserves. Prior selection: No prior selections available for year-over-year comparison. Environmental considerations: ULAE not separately identified in the context; no excess layer or construction defect segmentation noted. No cross-application from paid loss or count tails. Conclusion: bondy is selected as the only curve method that satisfies the Gap Rule, is appropriate for a dollar triangle, and is supported by the materiality anchor given the immaterial tail size.</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr"/>
@@ -3748,12 +3751,12 @@
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>exp_dev_quick</t>
+          <t>exp_dev_quick_exact_last</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>Exponential decay with tail factor 1.0367 selected for incurred loss, balancing conservative closure with observed gap pattern. Diagnostics: R² = 0.442 reflects moderate but legitimate fit to a triangle with early volatility (11-35 CV = 0.27-0.33, min/max outliers) that stabilizes in mid-range (47-83 CV = 0.05-0.07) and deep tail (83-263 CV &lt; 0.02). LOO std dev = 0.0010 confirms tight cross-validation stability despite moderate R² (typical for incurred loss with IBNR noise). Gap to last observed (0.457 months) is defensible: exp_dev_quick bridges between selected LDFs (1.0139 at 263 months) and ultimate closure without aggressive stretch. Alternative exp_dev_quick_exact_last (tail_factor=4.31) produces outsized reserve impact (25.8% of CDF), unjustified by observed gap. Materiality check not passed for exact_last variant supports this restraint. Exponential form is more transparent than Bondy and avoids Skurnick's weak R² (0.459). Selection reflects the observed pattern: early claim discovery, mid-term reserve adequacy, and orderly long-tail closure.</t>
+          <t>exp_dev_quick_exact_last is selected for incurred loss. The incurred triangle shows persistent — if irregular — development well beyond the 179-month cutoff, with selected LDFs still running at 1.0380 (107-119), 1.0300 (131-143), and 1.0150 (251-263) before tapering. A pure exponential decay with anchoring to the last observed LDF (exact_last variant) is the most appropriate form: it captures the gradual convergence to unity while not overcorrecting from early volatile factors. The R² of 0.795 across 15 fitting points is reasonable for an incurred triangle of this length and volatility profile. The LOO stability is tight (range 1.073–1.075, std dev 0.00043), indicating the curve is not sensitive to individual data points — an important confidence check given the non-monotone post-cutoff pattern. The gap flag (True) is acknowledged: the exponential curve projects a first factor materially above the last observed selected LDF, which reflects the non-smooth pattern in the selected LDFs rather than a calibration failure per se. The exact_last anchor variant mitigates this by pinning the curve to the observed data at the starting age, producing a tail of 1.072 versus 1.074 for the unconstrained version — a modest but meaningful improvement in continuity. The Bondy variants (1.003–1.006) and McClenahan (essentially 1.000) are too conservative: the selected LDFs beyond 179 months contain real development in multiple intervals that those methods cannot capture. The exp_dev_product (1.008) and Bondy are pulled down by the preponderance of near-1.000 factors in the late tail while underweighting the larger intermediate factors. The exp_dev_quick_exact_last tail of 1.072 is material (pct_of_CDF ~2.9%) but defensible given the long, bumpy incurred development pattern observed in this book.</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr"/>
@@ -3771,7 +3774,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A48:O48"/>
     <mergeCell ref="A58:D58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3915,10 +3918,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
+      <c r="A2" s="3" t="n">
+        <v>2001</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>3.2124</v>
@@ -3991,10 +3992,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="A3" s="3" t="n">
+        <v>2002</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2.5494</v>
@@ -4064,10 +4063,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="A4" s="3" t="n">
+        <v>2003</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2.4837</v>
@@ -4134,10 +4131,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="A5" s="3" t="n">
+        <v>2004</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>2.4368</v>
@@ -4201,10 +4196,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="A6" s="3" t="n">
+        <v>2005</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>2.0311</v>
@@ -4265,10 +4258,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="A7" s="3" t="n">
+        <v>2006</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>2.4565</v>
@@ -4326,10 +4317,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>2007</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2.1908</v>
@@ -4384,10 +4373,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+      <c r="A9" s="3" t="n">
+        <v>2008</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1.829</v>
@@ -4439,10 +4426,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>2009</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>3.246</v>
@@ -4491,10 +4476,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>2010</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>2.7631</v>
@@ -4540,10 +4523,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A12" s="3" t="n">
+        <v>2011</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>2.3046</v>
@@ -4586,10 +4567,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A13" s="3" t="n">
+        <v>2012</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>2.7856</v>
@@ -4629,10 +4608,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A14" s="3" t="n">
+        <v>2013</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>2.3011</v>
@@ -4669,10 +4646,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A15" s="3" t="n">
+        <v>2014</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>1.7931</v>
@@ -4706,10 +4681,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="A16" s="3" t="n">
+        <v>2015</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>2.2204</v>
@@ -4740,10 +4713,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="A17" s="3" t="n">
+        <v>2016</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>3.3152</v>
@@ -4771,10 +4742,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
+      <c r="A18" s="3" t="n">
+        <v>2017</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1.7371</v>
@@ -4799,10 +4768,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="A19" s="3" t="n">
+        <v>2018</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>2.8751</v>
@@ -4824,10 +4791,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="A20" s="3" t="n">
+        <v>2019</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>2.6745</v>
@@ -4846,10 +4811,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="A21" s="3" t="n">
+        <v>2020</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>2.5535</v>
@@ -4865,10 +4828,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="A22" s="3" t="n">
+        <v>2021</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>1.9981</v>
@@ -4881,10 +4842,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="A23" s="3" t="n">
+        <v>2022</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>2.4294</v>
@@ -4894,216 +4853,283 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="A24" s="3" t="n">
+        <v>2023</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>3.2653</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Averages</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>11-23</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>23-35</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>35-47</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>59-71</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83-95</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>95-107</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>107-119</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>119-131</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>131-143</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>143-155</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>155-167</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>179-191</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>191-203</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>203-215</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>215-227</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>239-251</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>251-263</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>263-275</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>275-287</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Averages</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11-23</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>23-35</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>35-47</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>59-71</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>83-95</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>95-107</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>107-119</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>119-131</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>131-143</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>143-155</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>155-167</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>167-179</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>179-191</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>191-203</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>203-215</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>215-227</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>227-239</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>239-251</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>251-263</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>263-275</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>275-287</t>
-        </is>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Average - 3 Years</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>2.5643</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1.3021</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1.1244</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1.0997</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1.1264</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1.1635</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.0508</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1.0106</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1.0665</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>1.0124</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1.0223</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>1.0161</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>1.0013</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>1.0106</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>1.0147</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>1.0018</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.0057</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>1.0076</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>1.0039</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Average - 3 Years</t>
+          <t>Weighted Average - 3 Years</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2.5643</v>
+        <v>2.6286</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.3021</v>
+        <v>1.2671</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.1244</v>
+        <v>1.1327</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.0997</v>
+        <v>1.1082</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.1264</v>
+        <v>1.1286</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.1635</v>
+        <v>1.1298</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.0508</v>
+        <v>1.0426</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.0106</v>
+        <v>1.0116</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.0665</v>
+        <v>1.0982</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.0124</v>
+        <v>1.0133</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.0223</v>
+        <v>1.022</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.0161</v>
+        <v>1.0138</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.0013</v>
+        <v>1.0016</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.0022</v>
+        <v>1.0023</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.0106</v>
+        <v>1.0193</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.0147</v>
+        <v>1.0109</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.0038</v>
+        <v>1.0029</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.0018</v>
+        <v>1.0017</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.0034</v>
+        <v>1.0043</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.0057</v>
+        <v>1.0062</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.0076</v>
+        <v>1.0074</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>1.0039</v>
@@ -5112,74 +5138,74 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 3 Years</t>
+          <t>Average - 5 Years</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2.6286</v>
+        <v>2.5842</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.2671</v>
+        <v>1.428</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.1327</v>
+        <v>1.1749</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.1082</v>
+        <v>1.0924</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.1286</v>
+        <v>1.119</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.1298</v>
+        <v>1.1215</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.0426</v>
+        <v>1.0311</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.0116</v>
+        <v>1.013</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.0982</v>
+        <v>1.0423</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.0133</v>
+        <v>1.0086</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.022</v>
+        <v>1.0195</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.0138</v>
+        <v>1.0201</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.0016</v>
+        <v>1.0068</v>
       </c>
       <c r="O29" s="4" t="n">
+        <v>1.0081</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>1.0096</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>1.0127</v>
+      </c>
+      <c r="R29" s="4" t="n">
         <v>1.0023</v>
       </c>
-      <c r="P29" s="4" t="n">
-        <v>1.0193</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>1.0109</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>1.0029</v>
-      </c>
       <c r="S29" s="4" t="n">
-        <v>1.0017</v>
+        <v>1.0043</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1</v>
+        <v>1.0024</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.0043</v>
+        <v>1.0044</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0057</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.0074</v>
+        <v>1.0076</v>
       </c>
       <c r="X29" s="4" t="n">
         <v>1.0039</v>
@@ -5188,74 +5214,74 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Average - 5 Years</t>
+          <t>Weighted Average - 5 Years</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2.5842</v>
+        <v>2.6232</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.428</v>
+        <v>1.4224</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.1749</v>
+        <v>1.1999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.0924</v>
+        <v>1.0978</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.119</v>
+        <v>1.1192</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.1215</v>
+        <v>1.107</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.0311</v>
+        <v>1.0328</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.013</v>
+        <v>1.0132</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.0423</v>
+        <v>1.0645</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.0086</v>
+        <v>1.0083</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.0195</v>
+        <v>1.0189</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.0201</v>
+        <v>1.0175</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.0068</v>
+        <v>1.0134</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.0081</v>
+        <v>1.0143</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.0096</v>
+        <v>1.0156</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.0127</v>
+        <v>1.0115</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.0023</v>
+        <v>1.0021</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.0043</v>
+        <v>1.0047</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.0024</v>
+        <v>1.0025</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.0044</v>
+        <v>1.0054</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.0057</v>
+        <v>1.0062</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.0076</v>
+        <v>1.0074</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>1.0039</v>
@@ -5264,74 +5290,74 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 5 Years</t>
+          <t>Exclude High/Low - 5 Years</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2.6232</v>
+        <v>2.5525</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.4224</v>
+        <v>1.4435</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.1999</v>
+        <v>1.1437</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.0978</v>
+        <v>1.0734</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.1192</v>
+        <v>1.1077</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.107</v>
+        <v>1.1033</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.0328</v>
+        <v>1.0214</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.0132</v>
+        <v>1.0106</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.0645</v>
+        <v>1.0246</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.0083</v>
+        <v>1.0044</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.0189</v>
+        <v>1.0136</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.0175</v>
+        <v>1.0167</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.0134</v>
+        <v>1.0017</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.0143</v>
+        <v>1.0045</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.0156</v>
+        <v>1.0063</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.0115</v>
+        <v>1.0124</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.0021</v>
+        <v>1.0012</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.0047</v>
+        <v>1.0018</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.0025</v>
+        <v>1</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.0054</v>
+        <v>1.0037</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0074</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.0074</v>
+        <v>1.0076</v>
       </c>
       <c r="X31" s="4" t="n">
         <v>1.0039</v>
@@ -5340,71 +5366,71 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Exclude High/Low - 5 Years</t>
+          <t>Average - 10 Years</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2.5525</v>
+        <v>2.4862</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.4435</v>
+        <v>1.3735</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.1437</v>
+        <v>1.2026</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.0734</v>
+        <v>1.0882</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.1077</v>
+        <v>1.0725</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.1033</v>
+        <v>1.0796</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.0214</v>
+        <v>1.0255</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.0106</v>
+        <v>1.0202</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.0246</v>
+        <v>1.0366</v>
       </c>
       <c r="K32" s="4" t="n">
+        <v>1.0266</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>1.0204</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>1.0185</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>1.0099</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>1.0114</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>1.0158</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>1.0084</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>1.0099</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>1.0024</v>
+      </c>
+      <c r="U32" s="4" t="n">
         <v>1.0044</v>
       </c>
-      <c r="L32" s="4" t="n">
-        <v>1.0136</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>1.0167</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>1.0017</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>1.0063</v>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>1.0124</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>1.0012</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>1.0037</v>
-      </c>
       <c r="V32" s="4" t="n">
-        <v>1.0074</v>
+        <v>1.0057</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>1.0076</v>
@@ -5416,74 +5442,74 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Average - 10 Years</t>
+          <t>Weighted Average - 10 Years</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2.4862</v>
+        <v>2.482</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.3735</v>
+        <v>1.3913</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.2026</v>
+        <v>1.2249</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.0882</v>
+        <v>1.0874</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.0725</v>
+        <v>1.0861</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.0796</v>
+        <v>1.0846</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.0255</v>
+        <v>1.0256</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.0202</v>
+        <v>1.0254</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.0366</v>
+        <v>1.0547</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.0266</v>
+        <v>1.0353</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.0204</v>
+        <v>1.0254</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.0185</v>
+        <v>1.0215</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.0099</v>
+        <v>1.0137</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.0114</v>
+        <v>1.0156</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.012</v>
+        <v>1.0163</v>
       </c>
       <c r="Q33" s="4" t="n">
         <v>1.0158</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.0084</v>
+        <v>1.0087</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.0099</v>
+        <v>1.013</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.0024</v>
+        <v>1.0025</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.0044</v>
+        <v>1.0054</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.0057</v>
+        <v>1.0062</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.0076</v>
+        <v>1.0074</v>
       </c>
       <c r="X33" s="4" t="n">
         <v>1.0039</v>
@@ -5492,74 +5518,74 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 10 Years</t>
+          <t>Exclude High/Low - 10 Years</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2.482</v>
+        <v>2.4762</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.3913</v>
+        <v>1.3658</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.2249</v>
+        <v>1.1864</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.0874</v>
+        <v>1.08</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.0861</v>
+        <v>1.064</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.0846</v>
+        <v>1.063</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.0256</v>
+        <v>1.0205</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.0254</v>
+        <v>1.015</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.0547</v>
+        <v>1.0286</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.0353</v>
+        <v>1.0217</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.0254</v>
+        <v>1.0184</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.0215</v>
+        <v>1.0169</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.0137</v>
+        <v>1.0087</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.0156</v>
+        <v>1.0104</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.0163</v>
+        <v>1.011</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.0158</v>
+        <v>1.0157</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.0087</v>
+        <v>1.0063</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.013</v>
+        <v>1.0054</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.0025</v>
+        <v>1</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.0054</v>
+        <v>1.0037</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0074</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.0074</v>
+        <v>1.0076</v>
       </c>
       <c r="X34" s="4" t="n">
         <v>1.0039</v>
@@ -5568,74 +5594,74 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Exclude High/Low - 10 Years</t>
+          <t>Min - All Years</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2.4762</v>
+        <v>1.7371</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.3658</v>
+        <v>1.0595</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.1864</v>
+        <v>1.0272</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0101</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.064</v>
+        <v>0.9974</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1.063</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.0205</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.015</v>
+        <v>0.9986</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.0286</v>
+        <v>0.9939</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.0217</v>
+        <v>0.9981</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.0184</v>
+        <v>1</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.0169</v>
+        <v>1.0001</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>1.0087</v>
+        <v>1</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.0104</v>
+        <v>1</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.011</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1.0157</v>
+        <v>1</v>
       </c>
       <c r="R35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="4" t="n">
         <v>1.0063</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>1.0074</v>
-      </c>
-      <c r="W35" s="4" t="n">
-        <v>1.0076</v>
       </c>
       <c r="X35" s="4" t="n">
         <v>1.0039</v>
@@ -5644,74 +5670,74 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Min - All Years</t>
+          <t>Max - All Years</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>1.7371</v>
+        <v>3.3152</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1.0595</v>
+        <v>1.7497</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1.0272</v>
+        <v>1.4653</v>
       </c>
       <c r="E36" s="4" t="n">
+        <v>1.2312</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1.2153</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.2914</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.0911</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1.0807</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1.1378</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>1.0922</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>1.0565</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>1.0497</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>1.0289</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>1.0301</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>1.0307</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>1.0327</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>1.0383</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>1.0121</v>
+      </c>
+      <c r="U36" s="4" t="n">
         <v>1.0101</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>0.9974</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>0.9903999999999999</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>0.9986</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>0.9939</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>0.9981</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="V36" s="4" t="n">
-        <v>1</v>
+        <v>1.0096</v>
       </c>
       <c r="W36" s="4" t="n">
-        <v>1.0063</v>
+        <v>1.009</v>
       </c>
       <c r="X36" s="4" t="n">
         <v>1.0039</v>
@@ -5720,144 +5746,141 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max - All Years</t>
+          <t>CV - 10 Years</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>3.3152</v>
+        <v>0.2259</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1.7497</v>
+        <v>0.1904</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1.4653</v>
+        <v>0.1076</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.2312</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.2153</v>
+        <v>0.0625</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1.2914</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.0911</v>
+        <v>0.0308</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1.0807</v>
+        <v>0.0238</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1.1378</v>
+        <v>0.044</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1.0922</v>
+        <v>0.0327</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>1.0565</v>
+        <v>0.0201</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1.0497</v>
+        <v>0.02</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1.0289</v>
+        <v>0.0116</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>1.0301</v>
+        <v>0.012</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>1.0307</v>
+        <v>0.0116</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1.0327</v>
+        <v>0.0124</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>1.027</v>
+        <v>0.0108</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1.0383</v>
+        <v>0.0151</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>1.0121</v>
+        <v>0.0054</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>1.0101</v>
+        <v>0.0051</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>1.0096</v>
+        <v>0.005</v>
       </c>
       <c r="W37" s="4" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="X37" s="4" t="n">
-        <v>1.0039</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CV - 10 Years</t>
+          <t>CV - 3 Years</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>0.2259</v>
+        <v>0.2513</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.1904</v>
+        <v>0.2467</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.1076</v>
+        <v>0.0502</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.1057</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0721</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.1012</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0308</v>
+        <v>0.0403</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.004</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.044</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.0327</v>
+        <v>0.0153</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.0201</v>
+        <v>0.0294</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0226</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0017</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.012</v>
+        <v>0.0033</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0159</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0103</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0.0108</v>
+        <v>0.0033</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.0151</v>
+        <v>0.0032</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>0.0054</v>
+        <v>0</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.0051</v>
+        <v>0.0058</v>
       </c>
       <c r="V38" s="4" t="n">
         <v>0.005</v>
@@ -5869,68 +5892,68 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CV - 3 Years</t>
+          <t>CV - 5 Years</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>0.2513</v>
+        <v>0.1774</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.2467</v>
+        <v>0.2103</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0.0502</v>
+        <v>0.1004</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.1057</v>
+        <v>0.0759</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.0721</v>
+        <v>0.0522</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.1012</v>
+        <v>0.0961</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0403</v>
+        <v>0.0391</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.004</v>
+        <v>0.0112</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0566</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.0153</v>
+        <v>0.0121</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.0294</v>
+        <v>0.0237</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.0226</v>
+        <v>0.0235</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.0017</v>
+        <v>0.0123</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>0.0033</v>
+        <v>0.0108</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0.0159</v>
+        <v>0.0114</v>
       </c>
       <c r="Q39" s="4" t="n">
         <v>0.0103</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>0.0033</v>
+        <v>0.0031</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.0032</v>
+        <v>0.0069</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0051</v>
       </c>
       <c r="V39" s="4" t="n">
         <v>0.005</v>
@@ -5942,141 +5965,141 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CV - 5 Years</t>
+          <t>Slope - 10 Years</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>0.1774</v>
+        <v>0.0629</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.2103</v>
+        <v>0.0049</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.1004</v>
+        <v>-0.01</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0759</v>
+        <v>0.0019</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0522</v>
+        <v>0.0148</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.0961</v>
+        <v>0.015</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0391</v>
+        <v>0.0041</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.0112</v>
+        <v>-0.0045</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.0566</v>
+        <v>0.0037</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.0121</v>
+        <v>-0.0068</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.0237</v>
+        <v>-0.0001</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.002</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.0123</v>
+        <v>-0.0015</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.0108</v>
+        <v>-0.0014</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.0114</v>
+        <v>-0.0019</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>0.0103</v>
+        <v>-0.0013</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.0069</v>
+        <v>-0.006</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>0.0054</v>
+        <v>-0.0012</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.0051</v>
+        <v>-0.0032</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.005</v>
+        <v>-0.0037</v>
       </c>
       <c r="W40" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Slope - 10 Years</t>
+          <t>Slope - 3 Years</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>0.0629</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.0049</v>
+        <v>-0.0604</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.0563</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.0019</v>
+        <v>-0.0235</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.0148</v>
+        <v>0.0539</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.015</v>
+        <v>-0.04</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0041</v>
+        <v>0.0182</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-0.0045</v>
+        <v>0.0024</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.0689</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-0.0068</v>
+        <v>-0.0111</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>-0.0001</v>
+        <v>-0.0051</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.002</v>
+        <v>0.021</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>-0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-0.0014</v>
+        <v>0.0027</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>-0.0019</v>
+        <v>-0.0145</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>-0.0013</v>
+        <v>0.0075</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>-0.0035</v>
+        <v>0.0002</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>-0.006</v>
+        <v>0.0028</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-0.0032</v>
+        <v>-0.0051</v>
       </c>
       <c r="V41" s="4" t="n">
         <v>-0.0037</v>
@@ -6088,68 +6111,68 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Slope - 3 Years</t>
+          <t>Slope - 5 Years</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.1057</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.0604</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0563</v>
+        <v>-0.0368</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0235</v>
+        <v>0.0014</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.0539</v>
+        <v>0.0158</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.04</v>
+        <v>0.0287</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0182</v>
+        <v>0.0186</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.0024</v>
+        <v>-0.0028</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.0689</v>
+        <v>0.0317</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-0.0111</v>
+        <v>0.0009</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>-0.0051</v>
+        <v>-0.0005</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.021</v>
+        <v>0.0036</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.0016</v>
+        <v>-0.0052</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.0027</v>
+        <v>-0.0028</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>-0.0145</v>
+        <v>-0.0022</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>0.0075</v>
+        <v>0.004</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>0.0028</v>
+        <v>-0.0021</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>0</v>
+        <v>-0.0012</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>-0.0051</v>
+        <v>-0.0032</v>
       </c>
       <c r="V42" s="4" t="n">
         <v>-0.0037</v>
@@ -6158,472 +6181,453 @@
         <v>0.0027</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Slope - 5 Years</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>0.1057</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>-0.09320000000000001</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>-0.0368</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0.0158</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0.0186</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>-0.0022</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R43" s="4" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="S43" s="4" t="n">
-        <v>-0.0021</v>
-      </c>
-      <c r="T43" s="4" t="n">
-        <v>-0.0012</v>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>-0.0032</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>-0.0037</v>
-      </c>
-      <c r="W43" s="4" t="n">
-        <v>0.0027</v>
-      </c>
-    </row>
-    <row r="44"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Selected LDFs</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>11-23</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>23-35</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>35-47</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>59-71</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>83-95</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>95-107</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>107-119</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>119-131</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>131-143</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>143-155</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>155-167</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>179-191</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>191-203</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>203-215</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>215-227</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>239-251</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>251-263</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr">
+        <is>
+          <t>263-275</t>
+        </is>
+      </c>
+      <c r="X44" s="5" t="inlineStr">
+        <is>
+          <t>275-287</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Selected LDFs</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>11-23</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>23-35</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>35-47</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>59-71</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>83-95</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>95-107</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>107-119</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>119-131</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>131-143</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>143-155</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>155-167</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>167-179</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>179-191</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>191-203</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>203-215</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>215-227</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>227-239</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>239-251</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>251-263</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr">
-        <is>
-          <t>263-275</t>
-        </is>
-      </c>
-      <c r="X45" s="5" t="inlineStr">
-        <is>
-          <t>275-287</t>
-        </is>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>1.007</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>2.5525</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>1.4224</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>1.1437</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1.0734</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>1.1077</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>1.1033</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>1.0214</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>1.0106</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>1.0246</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>1.0044</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>1.0136</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>1.0017</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>1.0063</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>1.0124</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>1.0012</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="S46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="U46" s="4" t="n">
-        <v>1.0074</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1.0076</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Exclude high/low from 5-year (CV=0.1774, within 0.10-0.20 range). 5-year avg_exclude_high_low=2.5525 balances outlier risk (max=3.3152, min=1.7371) with recent volatility (3-year=2.6286, 5-year=2.5525). Early maturity: apply downward asymmetric conservatism to 5-year avg, move 40% of gap to prior (implicit baseline 2.60). Selection 2.5525 is closest match without excessive recent outlier influence.</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>5-year volume-weighted average (CV=0.2103, within exclusion zone). High CV triggers outlier analysis: max=1.7497, min=1.0595. Weighted 5-year (1.4224) balances volume exposure better than simple average (1.4280). Recent 3-year (1.3021) shows acceleration downward, but 5-year weighted captures stability. Apply Bayesian anchoring with 50% credibility on recent trend.</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.1004, outlier caution applied). Exclude single high/low per protocol. Max=1.4653 shows outlier influence; trimmed average 1.1437 removes this. Recent trend 3-year (1.1244) very close, within ±2% confirms convergence. Hold at 1.1437 for early-maturity stability.</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0759, below 0.10 threshold). Averages converge: 5-yr excl h/l=1.0734, 10-yr excl h/l=1.0800, within ±1%. No evidence of trending. Simple average 1.0924 vs trimmed 1.0734; trimmed is more credible given max=1.2312. Select 1.0734.</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0522). Convergence check: 5-yr excl h/l=1.1077, 10-yr excl h/l=1.0640 diverge by &gt;3%, indicating recent uptick. 3-year=1.1264 &gt; 5-year, 3yr vs 5yr divergence ~3.5% triggers use of 5-year (1.1077) with downward caution. Data quality: slope_5yr=0.0158 (modest positive trend), slope_3yr=0.0539 (stronger). Mix signals; hold 5-year.</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0961, within caution range but trending evaluation needed). Slope_3yr=-0.04, slope_5yr=0.0287 indicate oscillation around trend. Incurred severity diagnostic shows rising (+2-5% p.a. trend), consistent with modest LDF increase. Select trimmed 5-year (1.1033) for conservatism; paid severity growth supports this.</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0391, low volatility). Tight convergence: weighted_5yr=1.0328, 10yr=1.0205, within ±1%. Trimmed 5-yr (1.0214) is midpoint of convergence band. No outliers (max=1.0911, min=1.0). Maturity 83-95 months: use standard 5-year average.</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0112, very tight). All averages cluster: 5-yr simple=1.0130, 5-yr trim=1.0106, within ±0.2%. Convergence override applies; select at lower end (1.0106) for conservatism, reflecting mid-maturity behavior where paid stabilizes.</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0566). Slope_5yr=0.0317 (positive) indicates modest trend. Paid_severity diagnostic and paid_to_incurred behavior support stable mid-range development. 5-yr trim (1.0246) &gt; 10-yr (1.0286), but 3-yr high (1.0665) suggests recent environment shift upward. Blend 75% 5yr + 25% 3yr effect: ~1.032. Conservative selection 1.0246.</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0121, convergence zone). All averages within ±1%: weighted_5yr=1.0083, simple_5yr=1.0086, trim_5yr=1.0044. Lower end of tight band selected for mature development. Minimal slope (0.0009) confirms stability.</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0237). Slight elevation vs prior columns. Slope_5yr=-0.0005 (flat), slope_3yr=-0.0051 (slight decline). 5-yr trim=1.0136 vs 10yr=1.0184; 3yr=1.0220. Recent uptick in 3yr suggests case reserve movement or severity increase. Select 1.0136 for baseline, monitoring case reserve behavior.</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0235). Very low LDFs indicate tail approach. 5-yr trim=1.0017, simple=1.0068, within convergence. Slope_5yr=-0.0052 confirms modest decline toward 1.0. At 143-155 months (late maturity), apply sparse-data caution: limit to 5-year, weight toward lower end. Select 1.0017.</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0108, tight). Converged: all averages 1.0045-1.0143. Slope flat. This interval shows monotonic decay beginning; LDFs stabilizing near 1.0. Select convergence midpoint (1.0045) for tail stability.</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0114). Convergence: 5yr trim=1.0063, all within ±1%. Slope_5yr=-0.0022 confirms gentle decline. At 167-179 months, continuing late-stage development; CVs remain low. Select 1.0063.</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0103). Slight uptick vs prior, 5yr trim=1.0124 &gt; previous. Slope_5yr=0.0040 (positive). Incurred severity may show case strengthening. All 5-year averages (weighted, simple, trim) converge within ±1% at 1.0063-1.0156. Select 1.0124 as midpoint.</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0031, very low). Tight convergence: trim=1.0012, weighted=1.0021, simple=1.0023. Slope_5yr=0.0040 minimal positive. Late tail development; sparse data caution applies (very few recent diagonals). Select 1.0012 as lower bound of tight cluster.</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0069, low). Averages cluster: trim=1.0018, weighted=1.0047, simple=1.0043. Slope negative (-0.0021). Late-maturity sparse data zone; most diagonal diagonals have &lt;5 points. Use 5-year trim (1.0012) conservatively, though recent (2-3 years) show 1.0018-1.0054 range. Select 1.0018.</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0054). Lowest values in tail approach; trim=1.0000, weighted=1.0025. Many diagonals converge to exactly 1.0 (min=1.0, max=1.0121). At 215-227 months (19 years), very limited development expected. Select 1.0000 reflecting paid claims closure.</t>
-        </is>
-      </c>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0054, essentially flat). All averages 1.0 or near-1.0. Trim=1.0000, weighted=1.0054. Sparse recent data (3-4 diagonals only). Select 1.0037 (simple 5yr) as slight hedge for ongoing development in sparse tail.</t>
-        </is>
-      </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0050). Very sparse tail data; only 2-3 diagonals. Averages: trim=1.0074, simple=1.0057, weighted=1.0062. Slope_5yr=-0.0032 (flat). Select 1.0074 as upper bound to reflect uncertainty in ultra-sparse data; tail factor stabilizes here.</t>
-        </is>
-      </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>5-year avg_exclude_high_low (CV=0.0019, near-zero variance). Extremely sparse: only 2 recent diagonals. All averages 1.0074-1.0076. Slope zero. This is the effective cutoff for credible paid LDF selection; beyond this, curve fitting is required. Select 1.0076 as final explicit selection.</t>
-        </is>
-      </c>
-      <c r="W47" s="3" t="inlineStr">
-        <is>
-          <t>[CUTOFF] CUTOFF at 263 months: Only 1-2 final diagonals with LDF data (cv=0.0019, essentially zero). Beyond this point, CV=NaN indicates insufficient data. Tail curve should begin here with standard tail assumptions (e.g., exponential decay or constant LDF 1.00). Paid triangle shows complete development by 250+ months; ultimate factors applied via tail curve. No explicit LDF selected; curve fitting initiated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2.5500 selected. High variance (CV_5yr=0.18, CV_3yr=0.25), 24 data points. 3yr VW=2.629, 5yr VW=2.623, 10yr VW=2.482, all VW=2.457. Notably, 3yr and 5yr VW are nearly identical (within 0.3%), providing a strong convergence signal at the recent range. This near-convergence at the 3yr/5yr level takes priority over the lower all-year average (which is pulled down by older, lower-severity AYs from 2007-2013). Recent AYs: 2022=2.429, 2021=1.998, 2020=2.554, 2019=2.675, 2018=2.875. Incurred severity trending strongly upward in the 2022-2024 period (age-11 severity: 2022=2659, 2023=3569, 2024=3477), supporting elevated early-age paid LDFs. Paid-to-incurred at age 11 is low and declining (2023: 0.377, 2024: 0.399), indicating large remaining case reserves and substantial future paid development. 3yr/5yr convergence override applies: midpoint ~2.626 selected, then modest Asymmetric Conservatism applied (AY2021's 1.998 is an outlier pulling 3yr down slightly). Selection of 2.550 represents the convergence midpoint dampened by ~3% to account for the variance in the recent window and one potentially anomalous low point (2021=1.998).</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>1.3800 selected. CV_5yr=0.21, CV_3yr=0.25 (high). 3yr VW=1.267, 5yr VW=1.422, 10yr VW=1.391, all VW=1.344. Wide divergence between 3yr and 5yr (&gt;15%). Recent AYs: 2020=1.180, 2021=1.666, 2022=1.060. AY2022 (1.060) and AY2020 (1.180) are anomalously low, pulling the 3yr average down. AY2019 (1.750) is the highest recent observation and may represent a large-loss AY. Incurred severity at age 23 rising sharply (2023: 5419). The 5yr and 10yr averages (1.422 and 1.391) are more credible than the 3yr. CV&gt;0.20 triggers outlier exclusion: the 5yr ex-hi/lo = 1.444. With the recent 3yr average suppressed by COVID-era and post-COVID anomalies, and the 5yr/10yr converging near 1.39-1.44, select near 1.380. This is the midpoint between 10yr VW (1.391) and all VW (1.344), reflecting a modest downward adjustment from the 5yr for the spike in 2019 while staying well above the 3yr anomaly.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>1.1800 selected. CV_5yr=0.10, CV_3yr=0.050 (low to moderate). 3yr VW=1.133, 5yr VW=1.200, 10yr VW=1.225, all VW=1.180. Moderate divergence between 3yr and 5yr (~5.6%). Recent AYs: 2020=1.121, 2021=1.070, with 2019=1.183 and 2018=1.374. AY2018 (1.374) is notably high (large case reserve emergence). 5yr includes the 2018 spike while 3yr does not. The all-year VW (1.180) falls squarely between 3yr and 5yr and is the most balanced estimate. At mid-early maturity, Bayesian anchoring to the all-year central estimate is appropriate. Selection of 1.180 equals the all-year VW, reflecting a stable central tendency that is consistent with the 10yr VW (1.225) discounted slightly for the likelihood that 2018 was an outlier AY.</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>1.0800 selected. CV_5yr=0.076 (moderate). 3yr VW=1.108, 5yr VW=1.098, 10yr VW=1.087, all VW=1.104. Recent AYs: 2020=1.011, 2019=1.231, 2018=1.058 — the 3yr is partially elevated by 2019's high factor. The 5yr and 10yr converge near 1.087-1.098. All-year VW = 1.104. Slope over 3yr is negative (-0.024) suggesting recent softening. Selection of 1.080 is slightly below the converging 5yr/10yr range, reflecting the recent declining trend in this column (2020: 1.011) while recognizing that 2020 may be partially COVID-suppressed. The all-year at 1.104 provides an upper bound; the 3yr at 1.108 is modestly inflated by the 2019 spike.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1.1100 selected. CV_5yr=0.052, CV_3yr=0.072 (low). 3yr VW=1.129, 5yr VW=1.119, 10yr VW=1.086, all VW=1.077. 3yr and 5yr converge tightly (within 0.9%), both materially above the 10yr (gap ~3.3%). This constitutes partial convergence of the recent windows. The 3yr/5yr convergence at 1.12-1.13 suggests a level shift upward in recent paid development at 59-71 months, consistent with rising incurred severity in recent AYs. Incurred severity at age 59 in 2019 was ~5927, 2018 ~7067 — confirming elevated loss environment. Convergence override of the 3yr/5yr midpoint (1.124) applies; partial discount toward 5yr VW for conservatism yields 1.110.</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1.1150 selected. CV_5yr=0.096, CV_3yr=0.101 (moderate). 3yr VW=1.130, 5yr VW=1.107, 10yr VW=1.085, all VW=1.059. Notable upward trend in recent years: 2019 not yet visible at 71-83, 2018: 1.060, 2017: 1.291, 2016: 1.140. The 3yr is elevated by the 2017 spike (1.291); the 5yr VW (1.107) is more balanced. At mid maturity (71-83 months), paid LDFs should be converging with incurred. The corresponding incurred 71-83 selection is 1.075. Paid being higher than incurred here is consistent with the paid-to-incurred ratios still below 1.0 in recent AYs (2019: 0.921, 2018: 0.969 at age 71). Selection of 1.115 is between 5yr VW (1.107) and 3yr VW (1.130), reflecting credible ongoing development. CV&gt;0.10 triggers outlier exclusion consideration — 5yr ex-hi/lo = 1.103 confirms the 5yr VW is reasonable.</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>1.0300 selected. CV_5yr=0.039, CV_3yr=0.040 (low). 3yr VW=1.043, 5yr VW=1.033, 10yr VW=1.026, all VW=1.026. 3yr and 5yr are consistent. All averages converge within ~1.7%, with the 5yr and 10yr/all bracketed around 1.026-1.043. Selection of 1.030 follows the 5yr VW as the primary reference, reflecting stable mid-maturity development. The corresponding incurred 83-95 selection (1.009) being lower than paid (1.030) is consistent with ongoing paid development exceeding incurred at this stage.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>1.0130 selected. CV_5yr=0.011, CV_3yr=0.004 (very low). All averages converge tightly: 3yr=1.011, 5yr VW=1.013, 10yr VW=1.025, all VW=1.021. The 3yr and 5yr are near-identical (convergence override applies). Selection follows the 5yr VW of 1.013, reflecting stable, low paid development at this late maturity. The 10yr and all-year are slightly higher due to older AYs. No trend signal.</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>1.0550 selected. CV_5yr=0.057, CV_3yr=0.065 (low). 3yr VW=1.098, 5yr VW=1.065, 10yr VW=1.055, all VW=1.039. Recent AYs: 2015 had a very high factor (1.138) and 2014 had 1.062 — the 3yr is elevated by 2015's spike which reflects large case reserve emergence visible in the diagnostics (2015 case reserves at age 107 = 129K). 5yr and 10yr converge around 1.055-1.065. All-year at 1.039 may be slightly low due to older well-reserved AYs. Selection of 1.055 follows the 10yr VW as a balanced estimate that discounts the 2015 spike while staying above the all-year.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>1.0100 selected. CV_5yr=0.012, CV_3yr=0.015 (very low). All averages converge tightly: 3yr=1.012, 5yr VW=1.008, 10yr VW=1.035, all VW=1.028. The 3yr and 5yr converge at 1.008-1.012. The 10yr and all-year are higher due to older AYs with more material development. Selection of 1.010 follows the midpoint of 3yr and 5yr convergence zone, reflecting stable low development at this maturity. AY2015's factor at 119-131 is not yet visible but prior factors support this range.</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1.0100 selected. CV_5yr=0.024 (low). 3yr=1.022, 5yr VW=1.019, 10yr VW=1.025, all VW=1.023. All averages converge tightly within 0.6pp. Convergence override applies — select midpoint of converged band (~1.021). Slight downward adjustment to 1.010 for the observation that the most recent AYs with data at this maturity (2013: 1.000, 2012: 1.057, 2011: 1.010) show declining development. The 5yr ex-hi/lo = 1.014 confirms the moderate level.</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.0150 selected. CV_5yr=0.024 (low). 3yr=1.016, 5yr VW=1.018, 10yr VW=1.022, all VW=1.021. Near-full convergence across all windows (within 0.6pp). Convergence override applies: select midpoint of converged band = 1.015-1.022. Selection of 1.015 reflects the lower end of the convergence zone consistent with the recent 3yr average, which has the most recent information.</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>1.0100 selected. CV very low (3yr=0.002, 5yr=0.012). All averages converge: 3yr=1.001, 5yr VW=1.013, 10yr VW=1.010, all VW=1.015. The 10yr and all-year converge at 1.010-1.015. The 3yr is near-zero reflecting recent zero-development AYs. Selection at 1.010 follows the 10yr VW, which best captures the central long-run development level at this mature age, acknowledging that near-term zero factors may understate long-run tail.</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>1.0075 selected. CV_5yr=0.011 (very low). All averages converge tightly: 3yr=1.002, 5yr VW=1.014, 10yr VW=1.016, all VW=1.016. The 5yr/10yr/all converge around 1.014-1.016. The 3yr is lower due to recent zero-development AYs. Selection of 1.0075 is below the 5yr to reflect recent declining activity while acknowledging the structural development in the all-year average.</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>1.0025 selected. CV very low. All averages near 1.000-1.020. 3yr=1.019, 5yr VW=1.016, 10yr VW=1.016, all VW=1.016. Most recent AYs showing 1.000 factors. Selection of 1.003 reflects modest residual development, acknowledging that several recent AYs have reached finality at this maturity while older AYs showed more development.</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] CUTOFF at 191 months: is_monotone_from_here=True for paid loss. CV at 191+ months is near-zero throughout (3yr=0.010, 5yr=0.010). Factors are stable at 1.000-1.010 range with only a few observations per column. Fewer than 5 credible data points remain in each interval beyond 191 months. Paid loss minimum cutoff is 60 months — this is well exceeded at 191 months. Tail curve fitting commences from 191 months. The sparse data caution (fewer observations per column increasing, near-zero development) combined with the convergence of all averages to 1.000 confirms this as the appropriate cutoff.</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>1.0080. Weighted-all is 1.009 and simple-all is 1.008. CV is very low. Most factors at or near 1.000. A selection of 1.008 is consistent with the all-period average.</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>1.0100. Weighted-all is 1.013 and simple-all is 1.010. Some development continues — 2001 (1.038), 2002 (1.016). CV is 0.015. A selection of 1.010 reflects the simple-all average.</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t>1.0020. Weighted-all and simple-all are both 1.002-1.002. Only a few observations (2001: 1.000, 2002: 1.012). Very sparse. A selection of 1.002 is minimal, reflecting near-flat development at this age.</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>1.0050. Weighted-all is 1.005, simple-all is 1.004. Observations: 2001 (1.007), 2002 (1.010). CV is very low. A selection of 1.005 is consistent.</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>1.0070. Weighted-all and simple-all are 1.006-1.008. Observations: 2001 (1.007), 2002 (1.010). A selection of 1.007 is consistent with observed values.</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>1.0070. Only one observation at 263-275 (2001: 1.006) and one at 275-287 (2001: 1.004). The weighted/simple-all averages are 1.007-1.008. A selection of 1.007 uses the available averages.</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 275 months. Only a single observation is available (2001: 1.004), making any direct selection unreliable. At 275+ months the data is exhausted and a tail curve should take over. The tail factor from 275 months to ultimate should be estimated using an actuarial decay curve fitted to the 191-275 interval pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Curve Comparison</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Curve Comparison</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Starting Age</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Monotone</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Slope Breaks</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Params</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Tail Factor</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>LOO Std Dev</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Gap to Last</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Gap Flag</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>% of CDF</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>Materiality OK</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>+10% Reserve Delta</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>+20% Reserve Delta</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Starting Age</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Monotone</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Slope Breaks</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Params</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Tail Factor</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>LOO Std Dev</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Gap to Last</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>Gap Flag</t>
-        </is>
-      </c>
-      <c r="L50" s="6" t="inlineStr">
-        <is>
-          <t>% of CDF</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="inlineStr">
-        <is>
-          <t>Materiality OK</t>
-        </is>
-      </c>
-      <c r="N50" s="6" t="inlineStr">
-        <is>
-          <t>+10% Reserve Delta</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>+20% Reserve Delta</t>
-        </is>
+      <c r="A50" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>bondy</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.0018988689108528</v>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="n">
+        <v>0.0457086061120271</v>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>586926.196534507</v>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>1076031.360313259</v>
       </c>
     </row>
     <row r="51">
@@ -6636,40 +6640,51 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>bondy</t>
+          <t>exp_dev_product</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>[0.37618754584223774, 0.7142152441807408]</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1.0076</v>
+        <v>1.008476092201377</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0.8646676831962343</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.001609140429361431</v>
+        <v>0.0003442309091015</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>1.173812454157762</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L51" s="16" t="n">
+        <v>0.1538870708219017</v>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L51" s="16" t="n">
-        <v>0.1464192003159683</v>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N51" s="17" t="n">
-        <v>613364.1866572797</v>
+        <v>583448.1516973302</v>
       </c>
       <c r="O51" s="17" t="n">
-        <v>1124501.008871675</v>
+        <v>1069654.944778442</v>
       </c>
     </row>
     <row r="52">
@@ -6682,32 +6697,32 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>exp_dev_product</t>
+          <t>exp_dev_quick</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>[0.20792962302447238, 0.7541951669319769]</t>
+          <t>[0.37618754584223774, 0.7142152441807408]</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1.002260711076896</v>
+        <v>1.089124740547863</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.645676665757689</v>
+        <v>0.8646676831962343</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.002048767522202492</v>
+        <v>0.0003442309091015</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.344570376975528</v>
+        <v>1.173812454157762</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
@@ -6715,18 +6730,18 @@
         </is>
       </c>
       <c r="L52" s="16" t="n">
-        <v>0.043831154665005</v>
+        <v>1.478403564867371</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>616631.7282973453</v>
+        <v>540244.3724948019</v>
       </c>
       <c r="O52" s="17" t="n">
-        <v>1130491.50187847</v>
+        <v>990448.01624047</v>
       </c>
     </row>
     <row r="53">
@@ -6739,32 +6754,32 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>exp_dev_quick</t>
+          <t>exp_dev_quick_exact_last</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>[0.20792962302447238, 0.7541951669319769]</t>
+          <t>[0.37618754584223774, 0.7142152441807408]</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1.088551497193866</v>
+        <v>1.065906197640555</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.645676665757689</v>
+        <v>0.8646676831962343</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.002048767522202492</v>
+        <v>0.0003442309091015</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.344570376975528</v>
+        <v>1.173812454157762</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -6772,7 +6787,7 @@
         </is>
       </c>
       <c r="L53" s="16" t="n">
-        <v>1.556830991291813</v>
+        <v>1.121119012101884</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -6780,10 +6795,10 @@
         </is>
       </c>
       <c r="N53" s="17" t="n">
-        <v>567750.5897231847</v>
+        <v>552012.4691349864</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>1040876.081159174</v>
+        <v>1012022.860080801</v>
       </c>
     </row>
     <row r="54">
@@ -6796,51 +6811,42 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>exp_dev_quick_exact_last</t>
+          <t>mcclenahan</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>[0.20792962302447238, 0.7541951669319769]</t>
+          <t>{"r": 0.4816303}</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1.912889547134739</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>0.645676665757689</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>0.002048767522202492</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>1.344570376975528</v>
+        <v>1.000000024069098</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="n">
+        <v>4.41367860242018e-07</v>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L54" s="16" t="n">
-        <v>8.489967066583727</v>
-      </c>
-      <c r="M54" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N54" s="17" t="n">
-        <v>323084.9138161689</v>
+        <v>588393.4978637472</v>
       </c>
       <c r="O54" s="17" t="n">
-        <v>592322.3419963047</v>
+        <v>1078721.412750199</v>
       </c>
     </row>
     <row r="55">
@@ -6853,10 +6859,10 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -6864,7 +6870,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1.0152</v>
+        <v>1.005</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
@@ -6872,18 +6878,18 @@
         </is>
       </c>
       <c r="L55" s="16" t="n">
-        <v>0.2902275646153792</v>
+        <v>0.09114835085964421</v>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N55" s="17" t="n">
-        <v>608772.4137863219</v>
+        <v>585466.1811202466</v>
       </c>
       <c r="O55" s="17" t="n">
-        <v>1116082.758608252</v>
+        <v>1073354.665387116</v>
       </c>
     </row>
     <row r="56">
@@ -6896,10 +6902,10 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -6907,7 +6913,7 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1.01525776</v>
+        <v>1.00500625</v>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
@@ -6915,18 +6921,18 @@
         </is>
       </c>
       <c r="L56" s="16" t="n">
-        <v>0.2913106905228661</v>
+        <v>0.0912616152888482</v>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>608737.7795328349</v>
+        <v>585462.5401840508</v>
       </c>
       <c r="O56" s="17" t="n">
-        <v>1116019.262476854</v>
+        <v>1073347.990337424</v>
       </c>
     </row>
     <row r="57">
@@ -6939,10 +6945,10 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.005</v>
+        <v>0.0116</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -6955,10 +6961,10 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2.925113284388402</v>
+        <v>2.925113284388321</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0.4586476566909383</v>
+        <v>0.4586476566909384</v>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
@@ -6966,7 +6972,7 @@
         </is>
       </c>
       <c r="L57" s="16" t="n">
-        <v>11.34317722713168</v>
+        <v>10.76888692335164</v>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
@@ -6974,10 +6980,10 @@
         </is>
       </c>
       <c r="N57" s="17" t="n">
-        <v>211282.6733153686</v>
+        <v>201152.3844789788</v>
       </c>
       <c r="O57" s="17" t="n">
-        <v>387351.5677448362</v>
+        <v>368779.3715447933</v>
       </c>
     </row>
     <row r="58"/>
@@ -7018,12 +7024,12 @@
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>exp_dev_product</t>
+          <t>modified_bondy_double_dev</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>Paid loss triangle — expect materially longer tail than incurred loss. Exponential product form selected to achieve controlled decay across the extended tail period. At 263-month cutoff, cv_at_starting_age = 0.005 (extremely tight convergence), is_monotone_from_here = False (minor slope variations acceptable at tail), n_factors_in_fit = 21 (robust fitting basis across 24 accident years). Gap Rule hard requirement satisfied: gap_flag = False, gap_to_last_observed = 1.3446 (all exponential summation and Skurnick rejected: gap_flag = True). Fit quality: R² = 0.6457, LOO std dev = 0.002048 (reasonable fit; product form provides stable extrapolation). Tail factor = 1.00226, pct_of_cdf = 0.0438% (materiality anchor applies decisively). Bondy (tail = 1.0076) and Modified Bondy variants rejected as mathematically less rigorous for paid loss tail modeling; summation methods (exp_dev_quick tail = 1.0885) overestimate tail due to K=8 summation bias. Skurnick (tail = 2.925, pct_of_cdf = 11.34%) rejected due to: (1) gap_flag = True, (2) unrealistic tail magnitude inconsistent with observed decay. Product method avoids both gap disconnection and tail overshooting. Sensitivity analysis: ±10% reserve delta ≈ ±617K-754K, reflecting material tail contribution appropriate for paid loss. Selection balances empirical fit, convergence, and actuarial conservatism.</t>
+          <t>Paid loss triangle — expect materially longer tail than incurred loss. The cutoff is set at 191 months (interval 191-203) with is_monotone_from_here=False, cv_at_starting_age=0.0116 (very low), slope_sign_changes=5 across 15 fitted factors, and n_factors_in_fit=15. The CV is excellent and the starting point is of high quality despite the non-monotone flag, indicating that residual paid development at this age is small but still present. min_selected_ldf=1.000, max_selected_ldf=1.031, avg_selected_ldf=1.016 confirm the late-age LDFs are very small. The last selected LDF at the cutoff is 1.0025 (191-203 interval cutoff reasoning confirms this). Gap Rule (hard requirement): All three exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) have gap_flag=True with gap_to_last_observed=1.174. This gap is extreme — the exponential curve fitted across 15 development periods extrapolates to approximately 1.089 at the starting age while the last selected LDF is 1.0025. The 1.174 gap value (on the factor minus 1 scale) renders all exponential methods categorically disqualified. While R²=0.865 for the exponential fit is above the 0.85 threshold (technically acceptable fit quality), the Gap Rule is a hard requirement that overrides fit quality — these methods are rejected. The skurnick method has gap_flag=False but produces a tail factor of 2.925, which is implausible for paid loss at 191 months of development; its R²=0.459 is also far below the 0.75 reject threshold. Skurnick is rejected on both R² and implausibility grounds. The mcclenahan method (tail~1.000) is designed for count triangles and is inappropriate for paid loss dollar triangles — rejected on triangle type grounds. Remaining valid candidates: bondy (tail=1.0025, materiality_ok=True, pct_of_cdf=0.046%), modified_bondy_double_dev (tail=1.005, materiality_ok=True, pct_of_cdf=0.091%), modified_bondy_square_ratio (tail=1.005, materiality_ok=True, pct_of_cdf=0.091%). All three Bondy variants pass the Gap Rule and have materiality_ok=True. Fit quality: No regression-based R² applies to Bondy variants; LOO std dev for bondy=0.00190, acceptable. Between the three Bondy variants: straight bondy (1.0025) is equal to the last observed factor — for paid loss, which characteristically runs a longer tail than incurred and has genuine residual payment patterns beyond 191 months, using exactly the last observed factor understates the likely residual tail. The modified_bondy_double_dev at 1.005 = 1 + 2*(1.0025-1) provides a small but reasonable incremental load that better reflects the expectation that paid losses continue to develop beyond the final observed age. This is consistent with the paid development data showing continuous small but positive factors through 275 months (factors at 203-215 through 263-275 all range from 1.002 to 1.010 in the selected LDFs). The modified_bondy_square_ratio yields an essentially identical tail (1.00500625 vs 1.005), so modified_bondy_double_dev is selected as the standard convention. Anchor Rule: The materiality anchor applies — pct_of_cdf=0.091% and materiality_ok=True confirm the tail is small relative to the CDF, which supports using a simple Bondy variant rather than requiring a curve fit. Sensitivity: +10% tail delta = $585K, -10% = -$716K — the tail is small but not negligible. The choice between bondy (1.0025) and modified_bondy_double_dev (1.005) represents a reserve difference of approximately $293K, which is immaterial but directionally appropriate given paid loss tail expectations. Prior selection: No prior selections available for year-over-year comparison. Environmental considerations: ULAE handling not separately noted; no excess layer segmentation identified. Paid loss tail selected independently from incurred and count measures. Conclusion: modified_bondy_double_dev is selected because it satisfies the Gap Rule, is appropriate for a paid dollar triangle, provides slightly more tail recognition than straight Bondy consistent with paid loss tail expectations, and is supported by the materiality anchor.</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr"/>
@@ -7036,12 +7042,12 @@
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>exp_dev_product</t>
+          <t>exp_dev_quick_exact_last</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Exponential decay with tail factor 1.0023 selected for the mature Workers Compensation paid loss triangle. Diagnostics support: R² = 0.646 indicates solid fit to observed decay pattern; LOO std dev = 0.0020 demonstrates excellent cross-validation stability with tight residuals. The smooth exponential form appropriately captures the pattern of diminishing development rates in the mid-tail (35-71 months, CV converging to 0.06), transitioning to near-flat deep tail (83+ months). Materiality check passed; tail factor yields ~0.04% of ultimate. Alternative exp_dev_quick_exact_last (tail_factor=1.91) produces excessive reserve impact (8.49% of CDF) and is overconservative. Bondy variants lack diagnostic transparency. Selection defends against both understating late IBNR and avoiding implausible tail stretch.</t>
+          <t>exp_dev_quick_exact_last is selected for paid loss. The paid triangle shows continued small but measurable development beyond the 191-month cutoff, with selected LDFs of 1.008, 1.010, 1.002, 1.005, 1.007, and 1.007 across successive intervals out to 275+ months. This is a long-tailed paid triangle where claiming finality at the cutoff would leave residual development unreserved. The exponential decay form with exact-last anchoring is appropriate: R² of 0.865 across 15 fitting points is the strongest goodness-of-fit among all parametric methods, and the LOO stability is excellent (range 1.088–1.090, std dev 0.00034), confirming the curve is robustly identified. The exact_last variant is preferred over the unconstrained exp_dev_quick because it anchors the curve to the last observed LDF (1.0025 at 179-191), reducing the gap discontinuity at the cutoff point and producing a tail of 1.066 versus 1.089. The gap flag (True, gap = 1.174) reflects that the raw exponential parameters project a curve starting above the observed last factor, but the exact_last adjustment corrects for this. The Bondy (1.003) and modified Bondy variants (1.005) are too conservative: they compress the tail well below what the long post-cutoff selected LDF sequence implies. The McClenahan produces essentially 1.000 — clearly insufficient. The Skurnick at 2.925 is implausible and disqualified. The exp_dev_product at 1.008 is closer to Bondy territory and likewise underweights the persistent development observed from 203 to 275 months. A tail factor of 1.066 represents ~1.1% of the CDF, which is material but appropriate for a paid loss triangle with demonstrated development out to the final diagonal.</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr"/>
@@ -7060,7 +7066,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A48:O48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7072,7 +7078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.7109375" customWidth="1" min="1" max="1"/>
@@ -7203,10 +7209,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
+      <c r="A2" s="3" t="n">
+        <v>2001</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1.0704</v>
@@ -7279,10 +7283,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="A3" s="3" t="n">
+        <v>2002</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>1.0344</v>
@@ -7352,10 +7354,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="A4" s="3" t="n">
+        <v>2003</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.0346</v>
@@ -7422,10 +7422,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="A5" s="3" t="n">
+        <v>2004</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>1.0591</v>
@@ -7489,10 +7487,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+      <c r="A6" s="3" t="n">
+        <v>2005</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>1.0232</v>
@@ -7553,10 +7549,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="A7" s="3" t="n">
+        <v>2006</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1.0386</v>
@@ -7614,10 +7608,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>2007</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>1.0434</v>
@@ -7672,10 +7664,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+      <c r="A9" s="3" t="n">
+        <v>2008</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1.0644</v>
@@ -7727,10 +7717,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>2009</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>1.0474</v>
@@ -7779,10 +7767,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>2010</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>1.0457</v>
@@ -7828,10 +7814,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A12" s="3" t="n">
+        <v>2011</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
@@ -7874,10 +7858,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A13" s="3" t="n">
+        <v>2012</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>1.0645</v>
@@ -7917,10 +7899,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A14" s="3" t="n">
+        <v>2013</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>1.028</v>
@@ -7957,10 +7937,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A15" s="3" t="n">
+        <v>2014</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>1.0456</v>
@@ -7994,10 +7972,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="A16" s="3" t="n">
+        <v>2015</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1.0328</v>
@@ -8028,10 +8004,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="A17" s="3" t="n">
+        <v>2016</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>1.0802</v>
@@ -8059,10 +8033,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
+      <c r="A18" s="3" t="n">
+        <v>2017</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1.1244</v>
@@ -8087,10 +8059,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="A19" s="3" t="n">
+        <v>2018</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>1.1233</v>
@@ -8112,10 +8082,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="A20" s="3" t="n">
+        <v>2019</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>1.1429</v>
@@ -8134,10 +8102,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="A21" s="3" t="n">
+        <v>2020</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>1.0604</v>
@@ -8153,10 +8119,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="A22" s="3" t="n">
+        <v>2021</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>1.1416</v>
@@ -8169,10 +8133,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="A23" s="3" t="n">
+        <v>2022</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>1.1414</v>
@@ -8182,149 +8144,216 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="A24" s="3" t="n">
+        <v>2023</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>1.1159</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Averages</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>11-23</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>23-35</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>35-47</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>59-71</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83-95</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>95-107</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>107-119</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>119-131</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>131-143</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>143-155</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>155-167</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>179-191</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>191-203</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>203-215</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>215-227</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>239-251</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>251-263</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>263-275</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>275-287</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Averages</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11-23</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>23-35</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>35-47</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>59-71</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>83-95</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>95-107</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>107-119</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>119-131</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>131-143</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>143-155</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>155-167</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>167-179</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>179-191</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>191-203</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>203-215</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>215-227</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>227-239</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>239-251</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>251-263</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>263-275</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>275-287</t>
-        </is>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Average - 3 Years</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1.0014</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Average - 3 Years</t>
+          <t>Weighted Average - 3 Years</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
@@ -8337,22 +8366,22 @@
         <v>1</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.0014</v>
+        <v>1.0013</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9988</v>
+        <v>0.9987</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9987</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.9961</v>
+        <v>0.9964</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>1</v>
@@ -8400,35 +8429,35 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 3 Years</t>
+          <t>Average - 5 Years</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1.133</v>
+        <v>1.1204</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.0013</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9993</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9992</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9964</v>
+        <v>0.9977</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>1</v>
@@ -8476,11 +8505,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Average - 5 Years</t>
+          <t>Weighted Average - 5 Years</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>1.1204</v>
+        <v>1.118</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1</v>
@@ -8492,13 +8521,13 @@
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="n">
         <v>0.9993</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>0.9992</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>1</v>
@@ -8552,35 +8581,35 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 5 Years</t>
+          <t>Exclude High/Low - 5 Years</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>1.118</v>
+        <v>1.133</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.0008</v>
+        <v>1</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9993</v>
+        <v>1</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.9977</v>
+        <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>1</v>
@@ -8628,35 +8657,35 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Exclude High/Low - 5 Years</t>
+          <t>Average - 10 Years</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>1.133</v>
+        <v>1.1009</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1</v>
+        <v>1.0069</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1</v>
+        <v>1.0009</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1</v>
+        <v>0.9988</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>1</v>
@@ -8704,17 +8733,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Average - 10 Years</t>
+          <t>Weighted Average - 10 Years</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1.1009</v>
+        <v>1.0962</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.0069</v>
+        <v>1.0073</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.0009</v>
+        <v>1.0008</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>1</v>
@@ -8732,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.9988</v>
+        <v>0.9989</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>1</v>
@@ -8780,35 +8809,35 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Weighted Average - 10 Years</t>
+          <t>Exclude High/Low - 10 Years</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>1.0962</v>
+        <v>1.1041</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.0073</v>
+        <v>1.0029</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.0008</v>
+        <v>1.0005</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>1</v>
@@ -8856,35 +8885,35 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Exclude High/Low - 10 Years</t>
+          <t>Min - All Years</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>1.1041</v>
+        <v>1</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.0029</v>
+        <v>1</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.0005</v>
+        <v>0.9979</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1</v>
+        <v>0.9952</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1</v>
+        <v>0.9963</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1</v>
+        <v>0.9883</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>1</v>
@@ -8932,35 +8961,35 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Min - All Years</t>
+          <t>Max - All Years</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>1</v>
+        <v>1.1429</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1</v>
+        <v>1.0459</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.9979</v>
+        <v>1.0045</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.9952</v>
+        <v>1.0041</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.9963</v>
+        <v>1.027</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>1.0251</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.9958</v>
+        <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0.9883</v>
+        <v>1</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>1</v>
@@ -9008,111 +9037,108 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max - All Years</t>
+          <t>CV - 10 Years</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>1.1429</v>
+        <v>0.0384</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1.0459</v>
+        <v>0.0145</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1.0045</v>
+        <v>0.0018</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.0041</v>
+        <v>0.002</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.027</v>
+        <v>0.0012</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1.0251</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>0.0013</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1</v>
+        <v>0.0037</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CV - 10 Years</t>
+          <t>CV - 3 Years</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>0.0384</v>
+        <v>0.013</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.0018</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.002</v>
+        <v>0.0024</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0021</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0013</v>
+        <v>0.0024</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.0068</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>0</v>
@@ -9157,35 +9183,35 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>CV - 3 Years</t>
+          <t>CV - 5 Years</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0316</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.0029</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.0021</v>
+        <v>0.0017</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.0019</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.0052</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
@@ -9230,35 +9256,35 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>CV - 5 Years</t>
+          <t>Slope - 10 Years</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>0.0316</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.0019</v>
+        <v>-0.0002</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0017</v>
+        <v>-0.0002</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0019</v>
+        <v>-0.0002</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.0052</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>0</v>
@@ -9303,35 +9329,35 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Slope - 10 Years</t>
+          <t>Slope - 3 Years</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.0128</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-0.0002</v>
+        <v>-0.0018</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.0002</v>
+        <v>-0.0021</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>0</v>
@@ -9376,35 +9402,35 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Slope - 3 Years</t>
+          <t>Slope - 5 Years</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>-0.0128</v>
+        <v>0.0027</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0</v>
+        <v>-0.0008</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.002</v>
+        <v>0.0004</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.0018</v>
+        <v>-0.0007</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.0021</v>
+        <v>-0.0008</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>-0.0058</v>
+        <v>-0.0023</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>0</v>
@@ -9446,479 +9472,355 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Slope - 5 Years</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>-0.0008</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>-0.0008</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Selected LDFs</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>11-23</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>23-35</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>35-47</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>59-71</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>83-95</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>95-107</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>107-119</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>119-131</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>131-143</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>143-155</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>155-167</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>179-191</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>191-203</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>203-215</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>215-227</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>239-251</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>251-263</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr">
+        <is>
+          <t>263-275</t>
+        </is>
+      </c>
+      <c r="X44" s="5" t="inlineStr">
+        <is>
+          <t>275-287</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Selected LDFs</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>11-23</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>23-35</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>35-47</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>59-71</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>83-95</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>95-107</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>107-119</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>119-131</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>131-143</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>143-155</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>155-167</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>167-179</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>179-191</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>191-203</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>203-215</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>215-227</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>227-239</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>239-251</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>251-263</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr">
-        <is>
-          <t>263-275</t>
-        </is>
-      </c>
-      <c r="X45" s="5" t="inlineStr">
-        <is>
-          <t>275-287</t>
-        </is>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>1.133</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>1.0004</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>3-year avg_exclude_high_low (CV=0.013, very low). Convergence override applies: all 3-year, 5-year, and 10-year averages extremely tight at 1.1041-1.1330. Weighted 3-yr=1.1330, simple 3-yr=1.1330, identical. Use 3-year (tighter recent history) given near-zero CV and perfect convergence. Reported counts show new claims activity (13% increase in early months).</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages within ±0.007 at 1.0000-1.0037. CV_3yr=0.0, CV_5yr=0.0. Perfect convergence override: select at convergence midpoint. Workers comp reported count development flat after 23-35 months; nearly all diagonals show 1.0. Slope all zero.</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0000-1.0009. CV_3yr=0.0, CV_5yr=0.0019. Convergence override applies. Min=0.9979, max=1.0045 show minimal variance. Select 1.0004 as midpoint; reported counts essentially fully matured by 35-47 months.</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages converge at 0.9999-1.0014. CV_3yr=0.0024, CV_5yr=0.0029 (near-zero). Perfect convergence at 1.0000. Min=0.9952, max=1.0041 show trivial variation. Select 1.0000 as convergence midpoint.</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 0.9987-1.0019. CV_3yr=0.0021, CV_5yr=0.0017. Tight convergence at 1.0000. Slope all near zero. Minimal reported count development expected; select 1.0000.</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0000-1.0015. CV_3yr=0.0, CV_5yr=0.0. Perfect convergence; all diagonals essentially 1.0. Min=1.0, max=1.0251. Select 1.0000 as convergence. Reported counts fully mature.</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 0.9986-1.0000. CV_3yr=0.0024, CV_5yr=0.0019. Convergence override; select 1.0000. Slope near zero. Reported counts approaching final levels; minimal reopenings expected at this maturity.</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 0.9999-1.0000. CV_3yr=0.0, CV_5yr=0.0. Perfect convergence; all observations at 1.0 (min=1.0, max=1.0). Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 0.9961-0.9977. CV_3yr=0.0068, CV_5yr=0.0052 (slightly elevated but still near-zero). Convergence at ~0.9970-1.0000. Slight downward trend (slope_5yr=-0.0023) indicates minimal closure or data rounding. Select 1.0000 for conservatism in tail.</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages exactly 1.0. CV_3yr=0.0, CV_5yr=0.0. Perfect convergence override; select 1.0000. Slope zero. All diagonals show 1.0 exactly; reported counts static.</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. Perfect convergence; select 1.0000. All diagonals 1.0.</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All diagonals 1.0. Perfect convergence override; select 1.0000.</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All data points exactly 1.0. Select 1.0000. Reported count maturity complete.</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All observations 1.0. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All diagonals 1.0; reported counts fully reported and closed. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All values 1.0. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All observations 1.0. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All data 1.0. Select 1.0000. Reported count tail complete.</t>
-        </is>
-      </c>
-      <c r="T47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All diagonals 1.0. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All data 1.0. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>Convergence: all averages 1.0. CV_3yr=0.0, CV_5yr=0.0. All observations 1.0. Select 1.0000.</t>
-        </is>
-      </c>
-      <c r="W47" s="3" t="inlineStr">
-        <is>
-          <t>All averages exactly 1.0. CV_3yr=0.0, CV_5yr=0.0. Reported count triangle fully matured; no further development expected. Last explicit selection 1.0000.</t>
-        </is>
-      </c>
-      <c r="X47" s="3" t="inlineStr">
-        <is>
-          <t>[CUTOFF] CUTOFF at 275 months: CV=NaN indicates insufficient data (likely &lt;2 observations). Reported count triangle complete by 251-263 months. All intervals from 11-23 through 263-275 months show reported count finalization (1.0). Tail curve not needed; reported counts are fully developed and reported by 263 months. Apply 1.0 for any remaining tail months as implied assumption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>1.0900 selected. CV_5yr=0.032, CV_3yr=0.013 (very low). All averages are well-defined and internally consistent: 3yr VW=1.133, 5yr VW=1.118, 10yr VW=1.096, all VW=1.062. A notable upward trend exists in the 11-23 column over recent years: 2017=1.124, 2018=1.123, 2019=1.143, 2020=1.060, 2021=1.142, 2022=1.141, 2023=1.116. The 3yr slope is negative (-0.013) and 5yr slope is positive (+0.003), suggesting the very recent AY2023 pulled the 3yr down from the plateau around 1.12-1.14 reached in 2017-2022. The 5yr VW (1.118) captures the sustained elevated period well. The 10yr VW (1.096) includes earlier lower-reporting years (2008-2010 were around 1.047-1.064). The all-year (1.062) is dragged down by 2011's 1.000, which appears anomalous (no new claims reported between 11 and 23 months for 2011). The 5yr/3yr divergence is ~1.5%, within the 3% Bayesian anchoring threshold — no regime change required. AY2023 at 1.116 confirms the factor remains in the 1.10-1.14 band. Selection of 1.090 reflects a modest conservatism below the 5yr VW (1.118), acknowledging the recent slight softening in 2023 (1.116) and 2020 (1.060 — potential COVID-related reporting delay). This is approximately midpoint of the 10yr VW (1.096) and 5yr VW (1.118).</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>1.0020 selected. CV_5yr=0.000, CV_3yr=0.000 (essentially zero). All averages across every window are 1.000 or 1.001-1.008: 3yr=1.000, 5yr=1.000, 10yr VW=1.007, all VW=1.003. Only 2 AYs show non-1.000 factors: 2001 (1.002), 2009 (1.004), 2014 (1.003), 2015 (1.016), 2016 (1.046). The 2016 factor of 1.046 is a clear outlier (most likely a small administrative re-opening of claims). Nearly all AYs in the last decade show exactly 1.000. The 10yr VW is 1.007 — driven by the 2016 outlier. Selection of 1.002 follows the all-year VW, acknowledging that very occasionally a small number of late-reported claims arrive between 23 and 35 months but the pattern is near-zero. Convergence override applies (all windows within 1.6% of each other with near-zero CV).</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000 selected. CV_5yr=0.002 (essentially zero). All averages converge tightly at 1.000: 3yr=1.000, 5yr=1.001, 10yr=1.001, all VW=1.000. The only non-1.000 factors in the triangle are 2001 (1.000 — barely rounds), 2004 (1.004), 2009 (1.000), 2013 (1.005). These are trivially small. Reported counts are fully developed by 35 months in virtually all AYs. Convergence override applies — full convergence to 1.000. Select 1.000.</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000 selected. CV_5yr=0.003 (essentially zero). All averages: 3yr=1.001, 5yr=1.000, all VW=1.000. Only minor non-1.000 factors in a handful of AYs (e.g., 2004: 1.002, 2013: 1.000, 2018: 1.004, 2017: 0.996). Both positive and negative deviations of &lt;0.5%. Fully converged — select 1.000.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000 selected. CV_5yr=0.002 (essentially zero). All averages at 0.999-1.002. Tiny deviations only. No systematic development beyond 47 months in reported counts. Select 1.000 — full convergence.</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] CUTOFF at 71 months: is_monotone_from_here=True. CV is 0.000 for all windows at 71+ months. All factors are 1.000 for virtually every AY from 71 months onward (with only trivial exceptions at earlier intervals). No credible or material development exists beyond 71 months for reported counts. Minimum cutoff for Reported Count is 48 months — this is exceeded. Tail factor for reported count should be 1.000 from 71 months onward. There are 5 intervals remaining (71-83 through 275-287) for tail curve fit, all of which will be 1.000.</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000. No meaningful development. All averages 1.000. Selected at 1.000.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000. Flat — all factors are exactly 1.000 across all periods. No development whatsoever.</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000. All factors are exactly 1.000 except 2015 (0.988 — a downward adjustment, likely closure). No upward development. Selected at 1.000.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000. All factors are 1.000 across all periods. No development.</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1.0000. All factors are 1.000 across all periods. No development.</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 143 months. From 35 months onward, reported count development is exactly 1.000 with no exceptions beyond rounding. The chain-ladder method adds no value beyond 143 months for this measure. A tail factor of 1.000 is appropriate from this point forward, or the count triangle can be considered fully mature at 35 months with a 1.000 tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Curve Comparison</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Curve Comparison</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Starting Age</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Monotone</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Slope Breaks</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Params</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Tail Factor</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>LOO Std Dev</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Gap to Last</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Gap Flag</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>% of CDF</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>Materiality OK</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>+10% Reserve Delta</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>+20% Reserve Delta</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Starting Age</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Monotone</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Slope Breaks</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Params</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Tail Factor</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>LOO Std Dev</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Gap to Last</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>Gap Flag</t>
-        </is>
-      </c>
-      <c r="L50" s="6" t="inlineStr">
-        <is>
-          <t>% of CDF</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="inlineStr">
-        <is>
-          <t>Materiality OK</t>
-        </is>
-      </c>
-      <c r="N50" s="6" t="inlineStr">
-        <is>
-          <t>+10% Reserve Delta</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>+20% Reserve Delta</t>
+      <c r="A50" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>bondy</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.0005020119305774999</v>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -9928,25 +9830,36 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>bondy</t>
+          <t>exp_dev_product</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>[0.09000000000000005, 0.022222222222222244]</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H51" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="I51" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>2.775557561562892e-17</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
@@ -9965,46 +9878,55 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>exp_dev_quick</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>[0.09000000000000005, 0.022222222222222244]</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1.000000000000006</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>2.775557561562892e-17</v>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>exp_dev_product</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>[0.1330000000000001, 0.05484084971070513]</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>8.326672684688674e-17</v>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="L52" s="16" t="n">
+        <v>6.022038536694959e-12</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>808.7423817918761</v>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>1482.694366618436</v>
       </c>
     </row>
     <row r="53">
@@ -10013,44 +9935,44 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>exp_dev_quick_exact_last</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>[0.09000000000000005, 0.022222222222222244]</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>1.000000000000006</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>2.775557561562892e-17</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>exp_dev_quick</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>[0.1330000000000001, 0.05484084971070513]</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>1.000000000011513</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>8.326672684688674e-17</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L53" s="16" t="n">
-        <v>8.626837512800163e-09</v>
+        <v>6.022038536694959e-12</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -10058,10 +9980,10 @@
         </is>
       </c>
       <c r="N53" s="17" t="n">
-        <v>779.2930970024056</v>
+        <v>808.7423817918761</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>1428.704011171074</v>
+        <v>1482.694366618436</v>
       </c>
     </row>
     <row r="54">
@@ -10070,55 +9992,32 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>modified_bondy_double_dev</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>exp_dev_quick_exact_last</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>[0.1330000000000001, 0.05484084971070513]</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>1.000000000011513</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>8.326672684688674e-17</v>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
-      </c>
-      <c r="L54" s="16" t="n">
-        <v>8.626837512800163e-09</v>
-      </c>
-      <c r="M54" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N54" s="17" t="n">
-        <v>779.2930970024056</v>
-      </c>
-      <c r="O54" s="17" t="n">
-        <v>1428.704011171074</v>
       </c>
     </row>
     <row r="55">
@@ -10127,18 +10026,18 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>modified_bondy_double_dev</t>
+          <t>modified_bondy_square_ratio</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
@@ -10161,166 +10060,132 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>skurnick</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>{"r": 0.61834694, "A": 16.25614305, "n": 3}</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>2.627988840124679</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0.06953720104774951</v>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>modified_bondy_square_ratio</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="L56" s="16" t="n">
+        <v>87.04720147609115</v>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>skurnick</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>{"r": 0.61834694, "A": 16.25614305, "n": 3}</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>2.627988840124679</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>0.06953720104774952</v>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L57" s="16" t="n">
-        <v>82.27557982963189</v>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N57" s="17" t="n">
-        <v>296.5359232554456</v>
-      </c>
-      <c r="O57" s="17" t="n">
-        <v>543.6491926349818</v>
-      </c>
-    </row>
-    <row r="58"/>
+      <c r="N56" s="17" t="n">
+        <v>307.7419391756284</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>564.1935551553188</v>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Tail Curve Selection</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Tail Curve Selection</t>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Additional Notes</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Reasoning</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Additional Notes</t>
-        </is>
-      </c>
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>Rules-Based AI Selection</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>mcclenahan</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>Reported count triangle — expect the shortest tail of all measures, materially shorter than incurred loss and paid loss. The cutoff is set at 71 months (interval 71-83) with is_monotone_from_here=True, cv_at_starting_age=0.0012 (essentially zero), slope_sign_changes=0, and n_factors_in_fit=5. This is an exceptional quality starting point: monotone declining LDFs, near-zero variance across accident years, and no structural breaks whatsoever. min_selected_ldf=0.9963, max_selected_ldf=1.027, avg_selected_ldf=1.002 at the cutoff confirm the last selected factors are extremely small and volatile around 1.000. The triangle shows complete practical development by age 71 months: from interval 35-47 onward all selected LDFs are 1.000, and the selected LDFs from 71-83 through 131-143 are all 1.000. Gap Rule: All methods have gap_flag=False. No methods are disqualified by the Gap Rule. Fit quality: The exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) all achieve R²=1.000 and LOO std dev=0.000 — a perfect fit, which is expected when fitting a series of factors that are essentially all 1.000. The tail from all exponential methods is 1.000 (to machine precision). Bondy variants also produce tail=1.000 since the last factor is 1.000. Skurnick produces a tail of 2.928 with R²=0.070 — far below the 0.75 reject threshold — and is rejected. Method preference: Per the framework's preference hierarchy, mcclenahan is the preferred method for count triangles (Reported Count and Closed Count), providing a synthetic incremental approach appropriate for the discrete nature of claim count development. All valid methods converge to tail=1.000 for this triangle, making the method choice consistent regardless of selection. The mcclenahan method is selected following the framework hierarchy for count triangles. Anchor Rule: Materiality anchor fully applies — pct_of_cdf is essentially zero (materiality_ok=True for exponential forms; the reported count triangle is fully developed at cutoff). Sensitivity: +/-10% sensitivity deltas are approximately $809 and -$988 respectively — negligible at this scale, confirming the tail is completely immaterial. The selection of tail=1.000 is empirically supported, theoretically expected for reported counts at 71 months of development, and consistent across all valid methods. Prior selection: No prior selections available for comparison. Environmental considerations: No ULAE, excess layer, or construction defect considerations apply to reported count triangles. This measure is selected independently from paid and incurred loss measures. Conclusion: mcclenahan is selected as the preferred method for count triangles per the framework hierarchy; the selection yields tail=1.000, consistent with all other valid methods and confirmed by the triangle's complete development pattern.</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>Rules-Based AI Selection</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>exp_dev_product</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>Reported count triangle — expect shortest tail of all measures, materially shorter than both paid and incurred loss. Exponential product form selected because reported counts have converged to 1.0 by 275-month cutoff. At cutoff: cv_at_starting_age = 0.0 (perfect convergence), all selected LDFs from 23 months onward = 1.0, n_factors_in_fit = 22 (full set across 24 accident years). Gap Rule satisfied: gap_flag = False (no disconnection). Fit quality: R² = 1.0 (perfect fit to convergence pattern), LOO std dev = 0.0 (zero residual variance); product form exactly reproduces empirical tail = 1.0. Tail factor = 1.0 (counts fully stabilized). Materiality anchor applies decisively: pct_of_cdf immaterial (tail unmaterial by definition for count triangles). McClenahan method not available in scenarios; exp_dev_product is superior alternative to Bondy (tail = 1.0 but mechanistic) because it provides regression-based fitting under the convergence assumption. Skurnick rejected: R² = 0.0695 (poor fit), tail = 2.628 (unrealistic; implies 163% inflation after stabilization—contradicts empirical data showing 1.0 factors from month 23 onward). Bondy acceptable but inferior: no statistical fit, no residual diagnostics. Selection reflects actuarial judgment that count triangles close out rapidly and tail is non-material; product form provides best-fit quantification of empirical convergence. Sensitivity immaterial: ±10% reserve delta &lt;1K (negligible).</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>Open-Ended AI Selection</t>
         </is>
       </c>
-      <c r="B62" s="21" t="inlineStr">
-        <is>
-          <t>exp_dev_quick</t>
-        </is>
-      </c>
-      <c r="C62" s="21" t="inlineStr">
-        <is>
-          <t>Exponential decay with tail factor 1.0 selected for reported count triangle, which exhibits near-complete closure by age 23 months. Diagnostics: R² = 1.0 and LOO std dev = 0.0 confirm perfect fit to the highly converged selected LDFs (all = 1.0 from 23+ months onward). Early development isolated to 11-23 months (CV = 0.013) reflects claim notification lag; all subsequent intervals converge to flat (CV &lt; 0.004 across mid and deep tail). Materiality check passed. All parametric curves yield tail_factor ~= 1.0 given the near-flat input; exponential form with perfect diagnostics is defensible and transparent. Bondy variants lack diagnostic output (NaN). Skurnick R² = 0.070 and tail_factor = 2.628 are inappropriate for a closed triangle. Selection reflects actuarial reality: reported count development is rapid early (claims notification) and effectively complete by 23 months in WC; tail risk is immaterial.</t>
-        </is>
-      </c>
-      <c r="D62" s="21" t="inlineStr"/>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>bondy</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>bondy is selected for reported count. The reported count triangle is essentially complete by 35 months: all selected LDFs from 35 months onward are 1.000, with only trivial movement at 23-35 (1.002) and the first interval (1.090 reflecting initial lag in claim registration). Beyond 71 months — the cutoff — there is no detectable development across any accident year. All exponential decay methods converge to a tail factor of effectively 1.000 (R²=1.0, LOO std dev=0.0 with zero residuals), confirming the parametric fit is uninformative — the data is flat by construction. Bondy likewise produces 1.000 with a tight LOO range (0.9998–1.002) and no slope sign changes. Any of the non-Skurnick methods would yield the same result, but Bondy is selected as the most transparent and convention-appropriate choice for a count triangle with demonstrated closure: it imposes minimal structure, requires no parametric assumptions, and will continue to produce 1.000 reliably as the triangle matures. The Skurnick method (tail = 2.628, R² = 0.070) is clearly spurious — its inverse power form is not appropriate for a count measure that is already fully developed — and is excluded. The implied tail of 1.000 correctly reflects that reported counts in this book close out within 3 years of accident year inception with no meaningful IBNR count tail.</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr"/>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
         <is>
           <t>User Selection</t>
         </is>
       </c>
-      <c r="B64" s="15" t="n"/>
-      <c r="C64" s="15" t="n"/>
-      <c r="D64" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="A58:D58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
+++ b/sample-data/sample-run/selections/Chain Ladder Selections - Tail.xlsx
@@ -3071,67 +3071,67 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1.165</v>
+        <v>1.125</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1.049</v>
+        <v>1.037</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1.09</v>
+        <v>1.105</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1.075</v>
+        <v>1.087</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.0085</v>
+        <v>1.015</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1.015</v>
+        <v>1.016</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.038</v>
+        <v>1.05</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1.0075</v>
+        <v>1.002</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>1.005</v>
+        <v>1.003</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>1.005</v>
+        <v>1.002</v>
       </c>
       <c r="O45" s="4" t="n">
         <v>1.01</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>1.003</v>
+        <v>1.005</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>1.01</v>
+        <v>1.009</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>1.005</v>
+        <v>1.006</v>
       </c>
       <c r="S45" s="4" t="n">
         <v>1.003</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>1.005</v>
+        <v>1.004</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>1.005</v>
+        <v>1.004</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>1.015</v>
+        <v>1.014</v>
       </c>
       <c r="W45" s="4" t="n">
         <v>1</v>
@@ -3145,117 +3145,117 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>1.6800 selected. High variance (CV_5yr=0.33, CV_3yr=0.16) with meaningful 3yr vs 5yr divergence (1.489 vs 1.702). The 3yr window is depressed by AY2020 (1.785) and AY2022 (1.226), while the 5yr picks up higher recent years (2018: 2.299, 2019: 2.757). Incurred severity is rising strongly in recent origin years (2022: ~2774 at age 35, 2023: ~5419 at age 23), and case reserves at age 11 are elevated and growing (2023: 607K, 2024: 535K), consistent with delayed case development requiring a higher factor. Paid-to-incurred ratios at 11 months are declining in recent years (2023: 0.38, 2024: 0.40), confirming large unreleased case reserves. No convergence — averages diverge over 14%. Asymmetric conservatism applied: movement upward from 5yr weighted (1.702) is credible given severity trend, but early maturity warrants Bayesian anchoring. Splitting the difference between 5yr VW and the 10yr VW (1.737), blending toward 1.68 acknowledges the recent severity signal while capping volatility at early maturity. All-weighted = 1.614 but this is dragged down by older low-severity AYs.</t>
+          <t>1.7000: cv_5yr=0.328 is very high (well above the 0.20 outlier-exclusion threshold), and the recency windows disagree in direction - weighted_3yr (1.4891) is actually below weighted_all (1.6135), while weighted_5yr (1.7024) and simple_5yr (1.784) sit well above it. This inconsistency is expected at the earliest, most volatile maturity (Section 9: outlier exclusion de-emphasized here). Selected close to the outlier-trimmed all-year average (avg_exclude_high_low_all=1.7265), balancing against the raw weighted_all figure. No prior exists, so no Bayesian anchoring was applied.</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>1.2000 selected. CV_5yr=0.21 (high), CV_3yr=0.13. Recent AYs: 2020=0.983, 2021=1.224, 2022=0.972. The 3yr weighted (1.054) is heavily distorted by the two sub-1.0 factors (2020 and 2022), which are anomalous — sub-1.0 incurred LDFs at 23-35 months are possible (case reserve reductions) but require corroboration. The 5yr weighted (1.258) includes the strong 2018 and 2019 factors (1.429 and 1.547) and is more credible. Incurred severity progression confirms ongoing development in this range. The all-year weighted = 1.189 and 10yr = 1.288. Given the recent two-year depression in factors (potentially case reserve reductions in 2020 COVID period and 2022), treating these as partially transient and selecting near the midpoint of 5yr VW and all-year VW. Asymmetric conservatism applied (downward movement from 5yr, move 30-50% of gap): 5yr = 1.258, all = 1.189, gap from 5yr to selected = 0.058. Selection of 1.200 reflects modest conservatism, staying above the anomalous 3yr average.</t>
+          <t>1.2200: cv_5yr=0.21 exceeds the outlier-exclusion threshold. weighted_3yr (1.054) is pulled down by two recent diagonals near or below 1.0 (2022=0.9715, 2020=0.9832), which is unusual for incurred development this early and would require diagnostic confirmation of decreasing case reserve adequacy before being trusted at full weight - that confirmation is not clearly present. Selected near the outlier-trimmed 5-year average (avg_exclude_high_low_5yr=1.212), rejecting the low 3-year figure per Section 11 (incurred LDFs should not select below 1.000, and the raw 3yr average is too close to that floor to be reliable).</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>1.1650 selected. CV_5yr=0.13, CV_3yr=0.057 (low-moderate). 3yr VW=1.095, 5yr VW=1.200, 10yr VW=1.189, all VW=1.153. Recent AYs trend lower: 2020=1.058, 2021=1.032, 2022 has no 35-47 factor yet. The 3yr is materially below the 5yr (gap ~10.5%). Incurred severity shows heterogeneous development in this range — some AYs resolve quickly, others don't. Applying partial convergence weighting: 5yr VW (1.200) has meaningful CV suggesting more weight on 5yr vs 3yr. Mid-maturity range, relaxed asymmetric conservatism. Selected as blend: 60% on 5yr (1.200) + 40% on 3yr (1.095) = ~1.158, rounded up slightly to 1.165 for conservative bias at this still-early maturity stage.</t>
+          <t>1.1250: weighted_3yr (1.0948) is 8.8% below weighted_5yr (1.2002), exceeding the &gt;5% divergence threshold, driven by a genuine multi-year decline (2019=1.15, 2020=1.058, 2021=1.03) versus older, higher years (2015=1.33, 2018=1.39) - consistent with faster claims resolution over time. Weighted roughly 70% toward the 3-year figure and 30% toward the 5-year figure (1.0948*0.7+1.2002*0.3=1.1265), rounded to 1.1250, since diagnostic support is only indirect (not a full 75-100% shift).</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.0490 selected. CV_5yr=0.056, CV_3yr=0.036 (both low). All averages converge well: 3yr VW=1.023, 5yr VW=1.057, 10yr VW=1.057, all VW=1.049. The 3yr appears slightly low (1.023) due to AY2020 (1.010), otherwise factors are stable in the 1.04-1.14 range for most AYs. Partial convergence between 5yr and all-year (within ~1%). 5yr VW of 1.057 is consistent with all-year. Selection of 1.049 follows the volume-weighted all-year average which best captures the central tendency in a stable column with moderate data.</t>
+          <t>1.0370: weighted_3yr (1.0233) vs weighted_5yr (1.0567) diverge 3.16%, in the 3-5% band. Blended 60% 5yr / 40% 3yr per Section 6 (0.6*1.0567+0.4*1.0233=1.0367), rounded to 1.0370.</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>1.0900 selected. CV_5yr=0.077, CV_3yr=0.093 (moderate). 3yr VW=1.117, 5yr VW=1.103, 10yr VW=1.075, all VW=1.074. Recent trend is slightly upward — 2019=1.222, 2020=1.010, while 2017=1.133 and 2018=1.013. The 3yr and 5yr are elevated relative to all-year, indicating recent LDFs are running higher. The slope over 3yr is positive (0.045). However, the 2019 factor (1.222) is the highest recent point, and 2020 (1.010) follows up as a potentially COVID-affected low. Incurred severity in recent AYs for this maturity range is elevated. Select near the 5yr VW (1.103), dampened slightly toward the all-year (1.074), reflecting trending but with asymmetric conservatism on the upside movement. Selection of 1.090 represents approximately 60% weight on the 5yr VW.</t>
+          <t>1.1050: weighted_3yr (1.1167) and weighted_5yr (1.1027) closely agree (1.25% apart) and both exceed the all-year average (1.0736) by ~3%, mirroring the same rise observed in the Paid Loss triangle at this interval - cross-view (paid/incurred) correlation supports treating this as a real, moderate upward move. Selected near weighted_5yr.</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.0750 selected. CV_5yr=0.074, CV_3yr=0.061. 3yr VW=1.090, 5yr VW=1.087, 10yr VW=1.067, all VW=1.046. The 3yr and 5yr averages are consistent with each other and notably above the 10yr/all-year, indicating a regime shift toward higher development in recent years. Incurred severity data supports ongoing case reserve increases. Paid-to-incurred ratios in mid-maturity remain below benchmark in recent AYs (e.g., 2017: 0.844, 2018: 0.969, 2019: 0.921), suggesting case reserves remain active. 3yr slope is positive at 0.45 but recent 2 LDFs (2018: 1.027, 2019: not yet visible at 71-83) show some stabilization. Selection of 1.075 is approximately equal to the 5yr VW, supported by convergence of 3yr and 5yr, with slight dampening from 10yr.</t>
+          <t>1.0870: This is a late-maturity column, but weighted_3yr (1.0898) and weighted_5yr (1.087) agree tightly and both sit ~4% above weighted_all (1.0457) - and this matches the analogous Paid Loss selection at 71-83 (1.088), giving cross-view confirmation of a genuine, ongoing severity trend rather than noise. Selected the 5-year weighted average.</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>1.0085 selected. CV_5yr=0.014 (low), CV_3yr=0.016. Very stable column. 3yr VW=1.009, 5yr VW=1.007, 10yr VW=1.018, all VW=1.022. Recent LDFs are low: 2017=1.032, 2016=1.000, 2018=N/A at this maturity. The convergence between 3yr and 5yr VW (within 0.2%) is strong. All-year is slightly higher due to older AYs. Selection follows 5yr VW closely. No trend signal, low CV — stable development at this maturity.</t>
+          <t>1.0150: Low variance (cv_3yr=0.016, cv_5yr=0.014). weighted_all (1.0221) sits modestly above the recency windows (1.0065-1.0085); per late-maturity guidance (prefer all-year absent a structural break), selected a blend closer to the midpoint.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>1.0150 selected. CV_5yr=0.025, CV_3yr=0.022 (low). 3yr VW=1.010, 5yr VW=1.013, 10yr VW=1.023, all VW=1.020. Recent factors are low (2016: 1.001, 2015: 1.003) while older AYs (2007: 1.072) pull up the all-year. The 5yr and 3yr averages converge around 1.010-1.015. Selection at 1.015 is slightly above the 5yr VW to account for the possibility that recent very-low factors in 2015-2016 understate long-run development, consistent with the 10yr average of 1.023. Incurred severity at this maturity shows ongoing small increases in some AYs.</t>
+          <t>1.0160: weighted_all (1.0195), weighted_5yr (1.0146), weighted_3yr (1.0098) are closely converged (within ~1%). Selected the midpoint.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.0380 selected. CV_5yr=0.039, CV_3yr=0.049 (low-moderate). 3yr VW=1.063, 5yr VW=1.049, 10yr VW=1.052, all VW=1.037. Recent factors include 2015: 1.096 (notably high, driven by case reserve increases visible in the 2015 case reserve data). 2016: N/A, 2014: 1.021. The 3yr is elevated due to 2015's 1.096 factor. The 5yr and 10yr converge around 1.049-1.052 and are most credible. Selection of 1.038 follows the all-year weighted which best reflects central tendency excluding the 2015 outlier influence, consistent with stable mid-late development.</t>
+          <t>1.0500: weighted_5yr (1.0485) is modestly above weighted_all (1.037), a mild uptick that is consistent (not diverging materially, 1.4%) between the 3-year (1.0629) and 5-year windows. Selected near the 5-year weighted average.</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1.0075 selected. CV_5yr=0.013, CV_3yr=0.007 (very low). All averages converge tightly: 3yr VW=1.000, 5yr VW=1.008, 10yr VW=1.019, all VW=1.017. The 3yr is pinned to 1.000 by three consecutive 1.000 factors for AYs 2013-2015. The 5yr and 10yr are slightly higher. Convergence override does not fully apply since 3yr vs 5yr diverge by ~0.8pp. Selection at 1.0075, midpoint of the 3yr (1.000) and 5yr (1.008), reflecting the stable low-development pattern at this late maturity.</t>
+          <t>1.0020: weighted_3yr (0.9997) is essentially at unity with very low cv_3yr (0.007), and avg_exclude_high_low_5yr (1.0028) confirms a similar level. Per Section 11 (late maturity, incurred can go as low as 0.995-1.000 with multi-year confirmation), the low, consistent multi-year reading supports a selection at/just above 1.000 rather than defaulting higher; selected 1.0020 to stay safely at or above unity.</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.0300 selected. CV_5yr=0.076, CV_3yr=0.099 (moderate). 3yr VW=1.053, 5yr VW=1.035, 10yr VW=1.040, all VW=1.033. The high CV is driven by AY2012 (1.179), which is a clear outlier (large reserve strengthening in one period). Excluding the outlier, 5yr ex-hi/lo = 1.005 which goes too far down. The all-year VW (1.033) and 5yr VW (1.035) converge nicely and represent credible central tendency. Selection follows 5yr/all-year convergence, reflecting normal case reserve fluctuation at this mature age.</t>
+          <t>1.0100: cv_3yr=0.099 is near the 0.10 outlier-exclusion threshold, and avg_exclude_high_low_5yr (1.0045) is materially lower than the raw weighted_5yr (1.035), indicating a single elevated diagonal (2012=1.179) is inflating the untrimmed averages. Selected close to the outlier-trimmed figure.</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.0050 selected. CV_5yr=0.016 (very low). All averages converge: 3yr=1.000, 5yr VW=1.002, 10yr VW=1.007, all VW=1.005. Near-convergence across all windows (within 0.7pp). 5yr VW and all VW are essentially identical. Selection follows the all-year VW of 1.005, reflecting very small residual development at this maturity. Late maturity behavior consistent.</t>
+          <t>1.0030: Very low variance (cv_3yr=0.0008); weighted_all (1.0053), weighted_5yr (1.0022), weighted_3yr (1.0004) are tightly converged. Selected the midpoint.</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.0050 selected. CV very low (3yr=0.000, 5yr=0.000). All averages essentially converge: 3yr=1.000, 5yr=1.000, all VW=1.005, 10yr=1.003. The all-year VW pulls slightly above 1.000 due to AY2001 (1.023) and AY2002 (1.040). Selection of 1.005 follows the all-year VW, which captures the full history of residual development at this late maturity stage.</t>
+          <t>1.0020: Convergence Override - cv_3yr=0.0001 and cv_5yr=0.0004 indicate near-total agreement across all averaging windows (weighted_all=1.0054, weighted_5yr=1.0004, weighted_3yr=0.9999). Selected the midpoint of the converged band.</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>1.0100 selected. CV low (3yr=0.004, 5yr=0.019). 3yr=1.002, 5yr VW=1.021, 10yr VW=1.017, all VW=1.017. Some variation across windows. At late maturity (167+ months), all-year window appropriate per guidelines. All-year VW of 1.017 and 10yr VW of 1.017 converge. Selection of 1.010 applies modest conservatism below the all-year (some recent AYs showing zero development confirms declining tail).</t>
+          <t>1.0100: weighted_3yr (1.002) sits below weighted_5yr (1.0211) and weighted_all (1.0167), reflecting a mild recent stabilization at this depth. Selected a blended value between the recent and longer-term figures.</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>CUTOFF at 179 months: This is the last selected interval before the tail begins. CV is very low (5yr=0.005, 3yr=0.003). Averages: 3yr=1.001, 5yr VW=1.004, 10yr VW=1.012, all VW=1.012. Most recent AYs showing 1.000-1.005 range. Selection of 1.003 reflects the low recent development visible in the 3yr and 5yr averages, consistent with declining tail activity. The pattern at 179+ months is monotonically very small and converging to 1.000.</t>
+          <t>1.0050: Low variance (cv_3yr=0.003, cv_5yr=0.005); weighted_all (1.0116), weighted_5yr (1.0036), weighted_3yr (1.0009) converge toward a flat, near-unity pattern typical of this maturity. Selected between the recent and all-year figures.</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>[CUTOFF] CUTOFF at 191 months: is_monotone_from_here=True, CV at this interval is near-zero (3yr=0.010, 5yr=0.009), factors are stable near 1.005-1.015 range but sparse. Only a few points remain in each column at this maturity, satisfying sparse data caution. Rejected further selection (191+) due to fewer than 5 credible data points per interval and near-zero incremental development. Tail curve fitting should commence from 191 months using the residual CDF. Minimum cutoff for Incurred Loss (48 months) is exceeded.</t>
+          <t>1.0090: weighted_all (1.0149), weighted_5yr (1.0076), weighted_3yr (1.0066) are closely aligned; selected between the all-year and recency-weighted figures. This is the last interval selected before the tail cutoff - cv_5yr=0.0089, low and stable, giving a credible endpoint for observed development consistent with the Paid Loss cutoff at the same age for internal consistency.</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>1.0050. Weighted-all and simple-all are both around 1.006-1.007. Recent 3-year and 5-year averages are 1.002-1.003. Very stable with nearly all factors at 1.000. A selection of 1.005 captures residual development.</t>
+          <t>[CUTOFF] CUTOFF at 215 months (well beyond the 48-month Incurred Loss minimum). Beyond this point, cv_5yr values stay very low (0.0-0.0188) and factors sit in a tight band around 1.0 (0.9938-1.0174) with only noise-level slope changes rather than a structural break. 7 intervals remain (203-215 through 275-287) for tail curve fitting, comfortably meeting the ≥3-5 requirement, and the cutoff aligns with the Paid Loss cutoff at the same maturity for internal consistency between the two loss triangles. The final column (275-287) has only a single accident-year observation, confirming this region is better extrapolated via curve fit than hand-selected.</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1.0030. All averages show 1.003-1.005. Nearly all individual factors are 1.000. The simple/weighted averages across all periods are 1.003-1.005. Selected at 1.003.</t>
+          <t>1.003 selected. Weighted_all (1.0045) reflects one modest outlier against several years at 1.0; avg_exclude_high_low_all is exactly 1.0. Selection is set slightly above unity to retain a small allowance for residual movement.</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>1.0050. Weighted-all is 1.009, simple-all is 1.009. The 3-year averages are 1.000. Several years show 1.000 and a few show 1.042 (2002). The weighted average gives more weight to larger observations. A conservative selection of 1.005 reflects modest development.</t>
+          <t>1.004 selected. Similar pattern to the prior interval — weighted_all (1.0089) is driven by one year (2007: 1.0424) against a mostly flat pattern (avg_exclude_high_low_all 1.0). A small positive factor is retained given the observed variability of loss development at very late durations.</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>1.0050. Weighted-all is 1.007, simple-all is 1.004. Some factors at 1.000 and some at 1.023 (2001). A selection of 1.005 is consistent.</t>
+          <t>1.004 selected, similar rationale to the prior interval — weighted_all (1.0069) reflects one elevated factor against an otherwise flat pattern (avg_exclude_high_low_all 1.0).</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>1.0150. The weighted-all and simple-all are both 1.017. The only observation is 2001 (1.014) and 2002 (1.036). With limited data at this age, 1.015 is reasonable, reflecting the central tendency of available factors.</t>
+          <t>1.014 selected, matching weighted_all (1.0174) and avg_exclude_high_low_all (1.0139) reasonably closely; this interval shows more consistent development across the (few) mature origin years than the immediately preceding intervals.</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>1.0000. All averages show 1.000. Both available years (2001, 2002) show 1.000. Selected at 1.000.</t>
+          <t>1.000 selected. Both available origin years at this maturity (2001 and 2002) show exactly 1.0, indicating claims are fully settled/incurred by this point for this book. This is the last interval selected directly from data with at least two corroborating observations.</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>[CUTOFF] Cutoff at 275 months. Only one observation available (2001: 1.012). With a single data point at this age, the tail curve fitting is more appropriate than a direct LDF selection. Development beyond 275 months is sparse and a tail factor from an actuarial tail curve (e.g., inverse power or exponential) should be applied from 275 months to ultimate.</t>
+          <t>[CUTOFF] Cutoff at 287: only a single origin year (2001) has data at this maturity (factor 1.0119), which is insufficient to validate a standalone selection. A fitted tail curve is more appropriate than extrapolating a one-point observation for the remaining runout.</t>
         </is>
       </c>
     </row>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -3365,29 +3365,20 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>1.003</v>
+        <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0027474184711859</v>
+        <v>0</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L50" s="16" t="n">
-        <v>0.1323533699663513</v>
-      </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
-      </c>
-      <c r="N50" s="17" t="n">
-        <v>1213817.056821216</v>
-      </c>
-      <c r="O50" s="17" t="n">
-        <v>2225331.27083889</v>
       </c>
     </row>
     <row r="51">
@@ -3400,10 +3391,10 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -3412,20 +3403,20 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>[0.23444059238507584, 0.7335764658174152]</t>
+          <t>[0.14493165655872692, 0.7882500550451723]</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1.008462582139825</v>
+        <v>1.00364829414809</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.7951445871346084</v>
+        <v>0.5866585483674849</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.0004325761287872</v>
+        <v>0.0020596943484693</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.4455594076149241</v>
+        <v>0.5550683434412731</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
@@ -3433,7 +3424,7 @@
         </is>
       </c>
       <c r="L51" s="16" t="n">
-        <v>0.3704428138725135</v>
+        <v>0.1524473463304896</v>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
@@ -3441,10 +3432,10 @@
         </is>
       </c>
       <c r="N51" s="17" t="n">
-        <v>1207242.122368481</v>
+        <v>1168567.978999015</v>
       </c>
       <c r="O51" s="17" t="n">
-        <v>2213277.224342212</v>
+        <v>2142374.628164854</v>
       </c>
     </row>
     <row r="52">
@@ -3457,10 +3448,10 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -3469,20 +3460,20 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>[0.23444059238507584, 0.7335764658174152]</t>
+          <t>[0.14493165655872692, 0.7882500550451723]</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1.073794389778644</v>
+        <v>1.102012179889305</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.7951445871346084</v>
+        <v>0.5866585483674849</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.0004325761287872</v>
+        <v>0.0020596943484693</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.4455594076149241</v>
+        <v>0.5550683434412731</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
@@ -3490,7 +3481,7 @@
         </is>
       </c>
       <c r="L52" s="16" t="n">
-        <v>2.955051243775014</v>
+        <v>3.742604112847028</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
@@ -3498,10 +3489,10 @@
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>1133791.086618222</v>
+        <v>1064263.426595017</v>
       </c>
       <c r="O52" s="17" t="n">
-        <v>2078616.992133401</v>
+        <v>1951149.615424193</v>
       </c>
     </row>
     <row r="53">
@@ -3514,10 +3505,10 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -3526,20 +3517,20 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>[0.23444059238507584, 0.7335764658174152]</t>
+          <t>[0.14493165655872692, 0.7882500550451723]</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1.072256401496538</v>
+        <v>1.102012179889305</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.7951445871346084</v>
+        <v>0.5866585483674849</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.0004325761287872</v>
+        <v>0.0020596943484693</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>0.4455594076149241</v>
+        <v>0.5550683434412731</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -3547,7 +3538,7 @@
         </is>
       </c>
       <c r="L53" s="16" t="n">
-        <v>2.899278950246448</v>
+        <v>3.742604112847028</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -3555,10 +3546,10 @@
         </is>
       </c>
       <c r="N53" s="17" t="n">
-        <v>1135417.337021705</v>
+        <v>1064263.426595017</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>2081598.451206464</v>
+        <v>1951149.615424193</v>
       </c>
     </row>
     <row r="54">
@@ -3571,10 +3562,10 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -3583,11 +3574,11 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>{"r": 0.34194035}</t>
+          <t>{"r": 0.46986667}</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1.000000000006545</v>
+        <v>1.000000013302294</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
@@ -3595,7 +3586,7 @@
         </is>
       </c>
       <c r="L54" s="16" t="n">
-        <v>2.899905898746657e-10</v>
+        <v>5.587283237821102e-07</v>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
@@ -3603,10 +3594,10 @@
         </is>
       </c>
       <c r="N54" s="17" t="n">
-        <v>1217458.507983714</v>
+        <v>1172831.24311709</v>
       </c>
       <c r="O54" s="17" t="n">
-        <v>2232007.264636807</v>
+        <v>2150190.612381332</v>
       </c>
     </row>
     <row r="55">
@@ -3619,10 +3610,10 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -3630,26 +3621,17 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1.006</v>
+        <v>1</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L55" s="16" t="n">
-        <v>0.2635705920394596</v>
-      </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
-      </c>
-      <c r="N55" s="17" t="n">
-        <v>1210197.324047402</v>
-      </c>
-      <c r="O55" s="17" t="n">
-        <v>2218695.094086893</v>
       </c>
     </row>
     <row r="56">
@@ -3662,10 +3644,10 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3673,26 +3655,17 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1.006009</v>
+        <v>1</v>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L56" s="16" t="n">
-        <v>0.2639625490662615</v>
-      </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
-      </c>
-      <c r="N56" s="17" t="n">
-        <v>1210186.497329228</v>
-      </c>
-      <c r="O56" s="17" t="n">
-        <v>2218675.245103583</v>
       </c>
     </row>
     <row r="57"/>
@@ -3728,7 +3701,7 @@
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>Rules-Based AI Selection</t>
+          <t>Framework AI Selection</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
@@ -3738,7 +3711,7 @@
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>Incurred loss triangle — expect medium tail length, longer than Reported Count and shorter than Paid Loss. The cutoff is set at 179 months (interval 179-191) with is_monotone_from_here=False, cv_at_starting_age=0.0166 (acceptable/low), slope_sign_changes=7 across 15 fitted factors, and n_factors_in_fit=15. The non-monotone pattern and 7 slope sign changes indicate structural irregularities in the late-age incurred development, likely reflecting case reserve adjustments that produce a choppy pattern rather than smooth decay. The min_selected_ldf=1.000, max_selected_ldf=1.053, avg_selected_ldf=1.012 confirm that selected LDFs at the cutoff are small but not negligible. Gap Rule (hard requirement): All exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) have gap_flag=True with gap_to_last_observed=0.446. This is a decisive rejection — the fitted exponential curve at the starting age extrapolates to approximately 1.073, while the last selected LDF is approximately 1.003 (Bondy value). The magnitude of the gap (0.446 on the factor minus 1 scale) reflects that the exponential fit is being driven upward by the irregular development pattern at early fitted ages, making it an inappropriate anchor for the tail. All three exponential methods are disqualified by the Gap Rule. Remaining valid candidates after Gap Rule: bondy (tail=1.003, gap_flag=False), modified_bondy_double_dev (tail=1.006, gap_flag=False), modified_bondy_square_ratio (tail=1.006, gap_flag=False), and mcclenahan (tail~1.000, gap_flag=False). The mcclenahan method is designed for count triangles and is inappropriate for incurred loss dollar triangles — rejected on triangle type grounds. The modified_bondy_double_dev and modified_bondy_square_ratio methods yield tail=1.006, representing 2x the last factor increment; however, given the irregular, non-monotone incurred development with slope sign changes, doubling the last factor introduces an upward adjustment not supported by the data pattern. The bondy method (tail=1.003) directly applies the last stable observed factor as the tail, which is the most defensible choice when the empirical development is irregular and a smooth curve cannot be anchored without violating the Gap Rule. Fit quality: R² is not applicable to Bondy variants (no regression fit performed); LOO std dev for bondy=0.00275, within acceptable range; no residual pattern concerns since no curve is being extrapolated. Anchor Rule: The materiality anchor applies — pct_of_cdf=0.132% and materiality_ok=False, indicating the tail is immaterial relative to total CDF. With a tail of 1.003 and such low materiality, additional precision in the curve method provides no meaningful reserve benefit. Sensitivity: +10% tail delta = $1.21M, -10% = -$1.48M, confirming the tail is small relative to total reserves. Prior selection: No prior selections available for year-over-year comparison. Environmental considerations: ULAE not separately identified in the context; no excess layer or construction defect segmentation noted. No cross-application from paid loss or count tails. Conclusion: bondy is selected as the only curve method that satisfies the Gap Rule, is appropriate for a dollar triangle, and is supported by the materiality anchor given the immaterial tail size.</t>
+          <t>Bondy selected, tail factor = 1.0000. Triangle type: Incurred Loss — expected to carry a medium-length tail, longer than Reported Count but shorter than Paid Loss; confirmed here since the Incurred selected LDFs reach unity (1.0000) by the last several observed intervals (e.g., 263-275 = 1.0000), well before Paid Loss's still-developing pattern at the same ages. Cutoff is 215 months (well beyond the 48-month Incurred Loss minimum). Diagnostics at the starting age show cv_at_starting_age=0.0 and the last selected LDF exactly at unity, so all three non-fitted candidates (bondy, modified_bondy_double_dev, modified_bondy_square_ratio) converge to the identical tail factor of 1.0 — the selection is robust to which simple heuristic is applied, which is itself strong evidence the pattern has genuinely flattened rather than an artifact of one method's assumptions. The exponential curve fits (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) were rejected on two independent grounds: fit quality (R²=0.587, below the 0.75 minimum reject threshold) and the hard Gap Rule (gap_to_last_observed=0.555, far above the 0.005 threshold — fitted values near 1.10 at the starting age versus observed factors at/near 1.0000). McClenahan (tail≈1.0000000133, materiality_ok=True, pct_of_cdf≈5.6e-7%) is numerically indistinguishable from Bondy but is the framework's preferred form for count triangles, not incurred dollar measures, so Bondy — which reads the tail directly off the fully-converged empirical pattern with no synthetic fitting needed — is the more transparent and defensible choice for this case. Skurnick was not offered as a scenario for this measure. Anchor Rule satisfied decisively via materiality: the tail is effectively 1.0000 (immaterial % of CDF), consistent with claims at this maturity being substantially reserved/closed. No meaningful reserve sensitivity attaches to this tail choice given the factor is at unity.</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr"/>
@@ -3751,12 +3724,12 @@
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>exp_dev_quick_exact_last</t>
+          <t>mcclenahan</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>exp_dev_quick_exact_last is selected for incurred loss. The incurred triangle shows persistent — if irregular — development well beyond the 179-month cutoff, with selected LDFs still running at 1.0380 (107-119), 1.0300 (131-143), and 1.0150 (251-263) before tapering. A pure exponential decay with anchoring to the last observed LDF (exact_last variant) is the most appropriate form: it captures the gradual convergence to unity while not overcorrecting from early volatile factors. The R² of 0.795 across 15 fitting points is reasonable for an incurred triangle of this length and volatility profile. The LOO stability is tight (range 1.073–1.075, std dev 0.00043), indicating the curve is not sensitive to individual data points — an important confidence check given the non-monotone post-cutoff pattern. The gap flag (True) is acknowledged: the exponential curve projects a first factor materially above the last observed selected LDF, which reflects the non-smooth pattern in the selected LDFs rather than a calibration failure per se. The exact_last anchor variant mitigates this by pinning the curve to the observed data at the starting age, producing a tail of 1.072 versus 1.074 for the unconstrained version — a modest but meaningful improvement in continuity. The Bondy variants (1.003–1.006) and McClenahan (essentially 1.000) are too conservative: the selected LDFs beyond 179 months contain real development in multiple intervals that those methods cannot capture. The exp_dev_product (1.008) and Bondy are pulled down by the preponderance of near-1.000 factors in the late tail while underweighting the larger intermediate factors. The exp_dev_quick_exact_last tail of 1.072 is material (pct_of_CDF ~2.9%) but defensible given the long, bumpy incurred development pattern observed in this book.</t>
+          <t>McClenahan tail curve (tail factor ~1.0000000133, r=0.470) selected. Incurred Loss LDFs are already essentially flat by the 215-month cutoff -- selected factors from 179 months onward run 1.002-1.014 with no consistent directional trend (slope_sign_changes=12 in the raw averages), and case-reserve adequacy at this maturity means little further incurred development is expected. McClenahan's geometric decay model converges cleanly to unity and is explicitly confirmed immaterial (materiality_ok=True, pct_of_cdf effectively 0%), matching the triangle's observed near-total flattening. Bondy independently corroborates this with an identical ~1.0 tail factor, reinforcing that a de minimis tail is the right shape here. The exponential decay alternatives (exp_dev_quick/exact_last/product) are less credible: R^2 is only 0.587, loo_max/min show meaningful instability, and gap_flag=True with a sizable gap_to_last_observed (0.555) indicates the fitted curve does not connect smoothly to the empirical tail, producing an inflated 1.10 factor unsupported by the actual data. No Skurnick fit was available for this measure. Given the mature, flattened incurred pattern and confirmed immateriality, McClenahan's smooth convergence to unity is the most defensible selection, consistent with an incurred triangle where case reserves have already captured essentially all of ultimate by this age.</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr"/>
@@ -6311,67 +6284,67 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2.55</v>
+        <v>2.5525</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1.18</v>
+        <v>1.145</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1.11</v>
+        <v>1.125</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1.115</v>
+        <v>1.088</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.03</v>
+        <v>1.029</v>
       </c>
       <c r="I45" s="4" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="Q45" s="4" t="n">
         <v>1.013</v>
       </c>
-      <c r="J45" s="4" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>1.015</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v>1.0025</v>
-      </c>
-      <c r="Q45" s="4" t="n">
-        <v>1.015</v>
-      </c>
       <c r="R45" s="4" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="S45" s="4" t="n">
         <v>1.008</v>
       </c>
-      <c r="S45" s="4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="T45" s="4" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
       <c r="U45" s="4" t="n">
         <v>1.005</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>1.007</v>
+        <v>1.006</v>
       </c>
       <c r="W45" s="4" t="n">
         <v>1.007</v>
@@ -6385,117 +6358,117 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2.5500 selected. High variance (CV_5yr=0.18, CV_3yr=0.25), 24 data points. 3yr VW=2.629, 5yr VW=2.623, 10yr VW=2.482, all VW=2.457. Notably, 3yr and 5yr VW are nearly identical (within 0.3%), providing a strong convergence signal at the recent range. This near-convergence at the 3yr/5yr level takes priority over the lower all-year average (which is pulled down by older, lower-severity AYs from 2007-2013). Recent AYs: 2022=2.429, 2021=1.998, 2020=2.554, 2019=2.675, 2018=2.875. Incurred severity trending strongly upward in the 2022-2024 period (age-11 severity: 2022=2659, 2023=3569, 2024=3477), supporting elevated early-age paid LDFs. Paid-to-incurred at age 11 is low and declining (2023: 0.377, 2024: 0.399), indicating large remaining case reserves and substantial future paid development. 3yr/5yr convergence override applies: midpoint ~2.626 selected, then modest Asymmetric Conservatism applied (AY2021's 1.998 is an outlier pulling 3yr down slightly). Selection of 2.550 represents the convergence midpoint dampened by ~3% to account for the variance in the recent window and one potentially anomalous low point (2021=1.998).</t>
+          <t>2.5525: cv_5yr=0.177 falls in the 0.10-0.20 band, so the single highest and lowest 5-year LDFs were excluded (avg_exclude_high_low_5yr=2.5525) rather than using the raw weighted average. Early-maturity variance is naturally high (Section 9) so outlier exclusion is applied lightly. 3yr (2.6286) and 5yr (2.6232) weighted averages agree closely and both sit above the all-year average (2.4566), consistent with a genuine upward trend in early paid development corroborated by rising paid_severity_incr in recent accident years (e.g. 2016-2019 severities several times the 2001-2010 level). No prior selection exists so no Bayesian anchoring was applied.</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>1.3800 selected. CV_5yr=0.21, CV_3yr=0.25 (high). 3yr VW=1.267, 5yr VW=1.422, 10yr VW=1.391, all VW=1.344. Wide divergence between 3yr and 5yr (&gt;15%). Recent AYs: 2020=1.180, 2021=1.666, 2022=1.060. AY2022 (1.060) and AY2020 (1.180) are anomalously low, pulling the 3yr average down. AY2019 (1.750) is the highest recent observation and may represent a large-loss AY. Incurred severity at age 23 rising sharply (2023: 5419). The 5yr and 10yr averages (1.422 and 1.391) are more credible than the 3yr. CV&gt;0.20 triggers outlier exclusion: the 5yr ex-hi/lo = 1.444. With the recent 3yr average suppressed by COVID-era and post-COVID anomalies, and the 5yr/10yr converging near 1.39-1.44, select near 1.380. This is the midpoint between 10yr VW (1.391) and all VW (1.344), reflecting a modest downward adjustment from the 5yr for the spike in 2019 while staying well above the 3yr anomaly.</t>
+          <t>1.3400: cv_5yr=0.21 (&gt;0.20) with 3yr and 5yr weighted averages diverging sharply (1.2671 vs 1.4224) driven by a single low recent diagonal (2022=1.0595) skewing the 3-year window. Given this instability rather than a clean trend, selected near the more stable all-year/10-year trimmed averages (weighted_all=1.3437, avg_exclude_high_low_10yr=1.3658) rather than chasing either extreme window.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>1.1800 selected. CV_5yr=0.10, CV_3yr=0.050 (low to moderate). 3yr VW=1.133, 5yr VW=1.200, 10yr VW=1.225, all VW=1.180. Moderate divergence between 3yr and 5yr (~5.6%). Recent AYs: 2020=1.121, 2021=1.070, with 2019=1.183 and 2018=1.374. AY2018 (1.374) is notably high (large case reserve emergence). 5yr includes the 2018 spike while 3yr does not. The all-year VW (1.180) falls squarely between 3yr and 5yr and is the most balanced estimate. At mid-early maturity, Bayesian anchoring to the all-year central estimate is appropriate. Selection of 1.180 equals the all-year VW, reflecting a stable central tendency that is consistent with the 10yr VW (1.225) discounted slightly for the likelihood that 2018 was an outlier AY.</t>
+          <t>1.1450: cv_5yr=0.10 triggers single high/low exclusion (avg_exclude_high_low_5yr=1.1437). 3yr (1.1327) sits below 5yr (1.1999), an 5.6% divergence, but lacks clear diagnostic confirmation (no matching severity or closure-rate signal at this maturity), so treated with skepticism per the no-diagnostic-support rule and selected near the outlier-trimmed 5-year average rather than fully weighting the 3-year window.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.0800 selected. CV_5yr=0.076 (moderate). 3yr VW=1.108, 5yr VW=1.098, 10yr VW=1.087, all VW=1.104. Recent AYs: 2020=1.011, 2019=1.231, 2018=1.058 — the 3yr is partially elevated by 2019's high factor. The 5yr and 10yr converge near 1.087-1.098. All-year VW = 1.104. Slope over 3yr is negative (-0.024) suggesting recent softening. Selection of 1.080 is slightly below the converging 5yr/10yr range, reflecting the recent declining trend in this column (2020: 1.011) while recognizing that 2020 may be partially COVID-suppressed. The all-year at 1.104 provides an upper bound; the 3yr at 1.108 is modestly inflated by the 2019 spike.</t>
+          <t>1.1000: Convergence Override applies - weighted_all (1.1038), simple_all (1.1009), weighted_5yr (1.0978), weighted_3yr (1.1082) are all within a ~1.4% band. Selected the midpoint of the converged band.</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>1.1100 selected. CV_5yr=0.052, CV_3yr=0.072 (low). 3yr VW=1.129, 5yr VW=1.119, 10yr VW=1.086, all VW=1.077. 3yr and 5yr converge tightly (within 0.9%), both materially above the 10yr (gap ~3.3%). This constitutes partial convergence of the recent windows. The 3yr/5yr convergence at 1.12-1.13 suggests a level shift upward in recent paid development at 59-71 months, consistent with rising incurred severity in recent AYs. Incurred severity at age 59 in 2019 was ~5927, 2018 ~7067 — confirming elevated loss environment. Convergence override of the 3yr/5yr midpoint (1.124) applies; partial discount toward 5yr VW for conservatism yields 1.110.</t>
+          <t>1.1250: 3yr (1.1286) and 5yr (1.1192) weighted averages closely agree and both exceed the all-year average (1.0774) by 4.5%, a diagnostic-confirmed upward trend (rising paid severity in recent accident years). Blended 60% 3yr / 40% 5yr per the 3-5% divergence band, landing at 1.1252, rounded to 1.1250.</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.1150 selected. CV_5yr=0.096, CV_3yr=0.101 (moderate). 3yr VW=1.130, 5yr VW=1.107, 10yr VW=1.085, all VW=1.059. Notable upward trend in recent years: 2019 not yet visible at 71-83, 2018: 1.060, 2017: 1.291, 2016: 1.140. The 3yr is elevated by the 2017 spike (1.291); the 5yr VW (1.107) is more balanced. At mid maturity (71-83 months), paid LDFs should be converging with incurred. The corresponding incurred 71-83 selection is 1.075. Paid being higher than incurred here is consistent with the paid-to-incurred ratios still below 1.0 in recent AYs (2019: 0.921, 2018: 0.969 at age 71). Selection of 1.115 is between 5yr VW (1.107) and 3yr VW (1.130), reflecting credible ongoing development. CV&gt;0.10 triggers outlier exclusion consideration — 5yr ex-hi/lo = 1.103 confirms the 5yr VW is reasonable.</t>
+          <t>1.0880: This is a late-maturity column (72+ mo) where recency is normally de-emphasized, but the upward move (weighted_5yr=1.107 vs weighted_all=1.0591, a 4.5% gap) is corroborated cross-view by paid_severity_incr trending up across multiple diagonals, treated as an ongoing inflationary signal (Section 13) rather than a one-time blip. Weighted 60% toward the 5-year average and 40% toward all-year to balance late-maturity caution against the confirmed trend.</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>1.0300 selected. CV_5yr=0.039, CV_3yr=0.040 (low). 3yr VW=1.043, 5yr VW=1.033, 10yr VW=1.026, all VW=1.026. 3yr and 5yr are consistent. All averages converge within ~1.7%, with the 5yr and 10yr/all bracketed around 1.026-1.043. Selection of 1.030 follows the 5yr VW as the primary reference, reflecting stable mid-maturity development. The corresponding incurred 83-95 selection (1.009) being lower than paid (1.030) is consistent with ongoing paid development exceeding incurred at this stage.</t>
+          <t>1.0290: cv_3yr=0.04, cv_5yr=0.04, low variance and reasonable agreement across windows (weighted_all=1.026, weighted_5yr=1.0328, weighted_3yr=1.0426). Selected a value near the all-year/5-year midpoint, consistent with late-maturity preference for the longer window absent a structural break.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>1.0130 selected. CV_5yr=0.011, CV_3yr=0.004 (very low). All averages converge tightly: 3yr=1.011, 5yr VW=1.013, 10yr VW=1.025, all VW=1.021. The 3yr and 5yr are near-identical (convergence override applies). Selection follows the 5yr VW of 1.013, reflecting stable, low paid development at this late maturity. The 10yr and all-year are slightly higher due to older AYs. No trend signal.</t>
+          <t>1.0170: cv_3yr=0.004 (very low), weighted_all (1.0208), weighted_5yr (1.0132), and weighted_3yr (1.0116) sit within ~1% of each other - effectively converged. Selected the midpoint.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.0550 selected. CV_5yr=0.057, CV_3yr=0.065 (low). 3yr VW=1.098, 5yr VW=1.065, 10yr VW=1.055, all VW=1.039. Recent AYs: 2015 had a very high factor (1.138) and 2014 had 1.062 — the 3yr is elevated by 2015's spike which reflects large case reserve emergence visible in the diagnostics (2015 case reserves at age 107 = 129K). 5yr and 10yr converge around 1.055-1.065. All-year at 1.039 may be slightly low due to older well-reserved AYs. Selection of 1.055 follows the 10yr VW as a balanced estimate that discounts the 2015 spike while staying above the all-year.</t>
+          <t>1.0450: Late-maturity column with few contributing accident years at this depth (sparse-data caution applies). weighted_3yr (1.0982) is notably above weighted_all (1.0394), largely reflecting a single high recent diagonal (2015=1.1378) rather than a broad-based trend. Anchored primarily to the all-year average with a modest upward nudge rather than following the thin recent window.</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1.0100 selected. CV_5yr=0.012, CV_3yr=0.015 (very low). All averages converge tightly: 3yr=1.012, 5yr VW=1.008, 10yr VW=1.035, all VW=1.028. The 3yr and 5yr converge at 1.008-1.012. The 10yr and all-year are higher due to older AYs with more material development. Selection of 1.010 follows the midpoint of 3yr and 5yr convergence zone, reflecting stable low development at this maturity. AY2015's factor at 119-131 is not yet visible but prior factors support this range.</t>
+          <t>1.0200: weighted_all (1.0282) sits above weighted_5yr (1.0083) and weighted_3yr (1.0133) - the elevated all-year figure reflects older-year spikes (e.g. 2007=1.05, 2012=1.0565) not repeated recently. Blended toward the more current, lower-variance recent windows, cv_5yr=0.012 (low).</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.0100 selected. CV_5yr=0.024 (low). 3yr=1.022, 5yr VW=1.019, 10yr VW=1.025, all VW=1.023. All averages converge tightly within 0.6pp. Convergence override applies — select midpoint of converged band (~1.021). Slight downward adjustment to 1.010 for the observation that the most recent AYs with data at this maturity (2013: 1.000, 2012: 1.057, 2011: 1.010) show declining development. The 5yr ex-hi/lo = 1.014 confirms the moderate level.</t>
+          <t>1.0210: Converged across windows - weighted_all (1.0226), weighted_5yr (1.0189), weighted_3yr (1.022) all within ~0.4%. Selected the midpoint; cv_5yr=0.024 confirms low volatility at this depth.</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.0150 selected. CV_5yr=0.024 (low). 3yr=1.016, 5yr VW=1.018, 10yr VW=1.022, all VW=1.021. Near-full convergence across all windows (within 0.6pp). Convergence override applies: select midpoint of converged band = 1.015-1.022. Selection of 1.015 reflects the lower end of the convergence zone consistent with the recent 3yr average, which has the most recent information.</t>
+          <t>1.0180: weighted_all (1.0211), weighted_5yr (1.0175), weighted_3yr (1.0138) show a mild downward drift toward recent years, consistent with normal decay at this maturity. Selected between the all-year and 5-year averages.</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.0100 selected. CV very low (3yr=0.002, 5yr=0.012). All averages converge: 3yr=1.001, 5yr VW=1.013, 10yr VW=1.010, all VW=1.015. The 10yr and all-year converge at 1.010-1.015. The 3yr is near-zero reflecting recent zero-development AYs. Selection at 1.010 follows the 10yr VW, which best captures the central long-run development level at this mature age, acknowledging that near-term zero factors may understate long-run tail.</t>
+          <t>1.0080: weighted_3yr (1.0016) is markedly lower than weighted_5yr (1.0134) and weighted_all (1.0151), consistent with the expected flattening of development toward 1.0 at this deep maturity (&gt;150 months). Selected between the 3-year and 5-year figures, giving weight to the natural decay pattern rather than the noisier all-year mean.</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>1.0075 selected. CV_5yr=0.011 (very low). All averages converge tightly: 3yr=1.002, 5yr VW=1.014, 10yr VW=1.016, all VW=1.016. The 5yr/10yr/all converge around 1.014-1.016. The 3yr is lower due to recent zero-development AYs. Selection of 1.0075 is below the 5yr to reflect recent declining activity while acknowledging the structural development in the all-year average.</t>
+          <t>1.0090: Same flattening pattern as the prior column - weighted_3yr (1.0023) well below weighted_all (1.0156)/weighted_5yr (1.0143). Selected a value between the recent and longer-term averages, consistent with continued monotonic decay toward unity.</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>1.0025 selected. CV very low. All averages near 1.000-1.020. 3yr=1.019, 5yr VW=1.016, 10yr VW=1.016, all VW=1.016. Most recent AYs showing 1.000 factors. Selection of 1.003 reflects modest residual development, acknowledging that several recent AYs have reached finality at this maturity while older AYs showed more development.</t>
+          <t>1.0170: weighted_all (1.0163), weighted_5yr (1.0156), weighted_3yr (1.0193) are tightly converged (within 0.3%). Selected the midpoint.</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>[CUTOFF] CUTOFF at 191 months: is_monotone_from_here=True for paid loss. CV at 191+ months is near-zero throughout (3yr=0.010, 5yr=0.010). Factors are stable at 1.000-1.010 range with only a few observations per column. Fewer than 5 credible data points remain in each interval beyond 191 months. Paid loss minimum cutoff is 60 months — this is well exceeded at 191 months. Tail curve fitting commences from 191 months. The sparse data caution (fewer observations per column increasing, near-zero development) combined with the convergence of all averages to 1.000 confirms this as the appropriate cutoff.</t>
+          <t>1.0130: weighted_all (1.0158), weighted_5yr (1.0115), weighted_3yr (1.0109) are closely aligned; selected between the all-year and recency-weighted figures. This is the last interval selected before the tail cutoff - cv_5yr=0.0103, low and stable, supporting a credible endpoint for observed development.</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>1.0080. Weighted-all is 1.009 and simple-all is 1.008. CV is very low. Most factors at or near 1.000. A selection of 1.008 is consistent with the all-period average.</t>
+          <t>[CUTOFF] CUTOFF at 215 months (well beyond the 60-month Paid Loss minimum). From this point on, cv_5yr values are extremely low (0.0031-0.0069, all &lt;0.01) and factors hover in a tight ±1.5% band around 1.0 (1.0021-1.0087) with residual noise-level slope-sign changes rather than a structural break. 7 intervals remain (203-215 through 275-287) for tail curve fitting, comfortably meeting the ≥3-5 requirement. The final column (275-287) has only a single accident-year observation (2001) and cv is undefined, confirming this region is better handled by curve extrapolation than by hand-selection.</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1.0100. Weighted-all is 1.013 and simple-all is 1.010. Some development continues — 2001 (1.038), 2002 (1.016). CV is 0.015. A selection of 1.010 reflects the simple-all average.</t>
+          <t>1.008 selected, near weighted_all (1.013) and 10yr (1.013); this interval is influenced by one larger factor (2001: 1.0383) against several near-unity years, so the selection sits below the mean-driven averages to avoid overweighting the single outlier.</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>1.0020. Weighted-all and simple-all are both 1.002-1.002. Only a few observations (2001: 1.000, 2002: 1.012). Very sparse. A selection of 1.002 is minimal, reflecting near-flat development at this age.</t>
+          <t>1.003 selected, consistent with weighted_all (1.0025) and 5yr/10yr (1.0025). Development is now very minor and highly consistent.</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>1.0050. Weighted-all is 1.005, simple-all is 1.004. Observations: 2001 (1.007), 2002 (1.010). CV is very low. A selection of 1.005 is consistent.</t>
+          <t>1.005 selected, matching weighted_all, 5yr, and 10yr averages (all 1.0054). Small, stable residual development.</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>1.0070. Weighted-all and simple-all are 1.006-1.008. Observations: 2001 (1.007), 2002 (1.010). A selection of 1.007 is consistent with observed values.</t>
+          <t>1.006 selected, matching weighted_all and other windows (all ~1.0062). Consistent minor tail development.</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>1.0070. Only one observation at 263-275 (2001: 1.006) and one at 275-287 (2001: 1.004). The weighted/simple-all averages are 1.007-1.008. A selection of 1.007 uses the available averages.</t>
+          <t>1.007 selected, matching the only two data points available (2001: 1.0063, 2002: 1.009) which are tightly clustered, giving reasonable confidence despite thin volume. This is the last interval selected directly from data before volume becomes too sparse for a credible standalone factor.</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>[CUTOFF] Cutoff at 275 months. Only a single observation is available (2001: 1.004), making any direct selection unreliable. At 275+ months the data is exhausted and a tail curve should take over. The tail factor from 275 months to ultimate should be estimated using an actuarial decay curve fitted to the 191-275 interval pattern.</t>
+          <t>[CUTOFF] Cutoff at 287: only a single origin year (2001) has data at this maturity, providing no cross-sectional credibility to validate a factor. Beyond this point, a fitted tail curve (e.g., inverse power or exponential decay) is more reliable than a one-observation direct selection for extrapolating the remaining runout.</t>
         </is>
       </c>
     </row>
@@ -6594,10 +6567,10 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -6605,10 +6578,10 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>1.0025</v>
+        <v>1.007</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0018988689108528</v>
+        <v>0.0013499999999999</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
@@ -6616,18 +6589,18 @@
         </is>
       </c>
       <c r="L50" s="16" t="n">
-        <v>0.0457086061120271</v>
+        <v>0.1232512805247559</v>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N50" s="17" t="n">
-        <v>586926.196534507</v>
+        <v>568471.2502831817</v>
       </c>
       <c r="O50" s="17" t="n">
-        <v>1076031.360313259</v>
+        <v>1042197.292185828</v>
       </c>
     </row>
     <row r="51">
@@ -6640,10 +6613,10 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -6652,20 +6625,20 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>[0.37618754584223774, 0.7142152441807408]</t>
+          <t>[0.2140432336831392, 0.8035651046893572]</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1.008476092201377</v>
+        <v>1.008897248476611</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.8646676831962343</v>
+        <v>0.8071956551489008</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.0003442309091015</v>
+        <v>0.0021954985319093</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1.173812454157762</v>
+        <v>1.338456766316861</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
@@ -6673,7 +6646,7 @@
         </is>
       </c>
       <c r="L51" s="16" t="n">
-        <v>0.1538870708219017</v>
+        <v>0.1563104011179415</v>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
@@ -6681,10 +6654,10 @@
         </is>
       </c>
       <c r="N51" s="17" t="n">
-        <v>583448.1516973302</v>
+        <v>567402.2304050699</v>
       </c>
       <c r="O51" s="17" t="n">
-        <v>1069654.944778442</v>
+        <v>1040237.422409289</v>
       </c>
     </row>
     <row r="52">
@@ -6697,10 +6670,10 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -6709,20 +6682,20 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>[0.37618754584223774, 0.7142152441807408]</t>
+          <t>[0.2140432336831392, 0.8035651046893572]</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1.089124740547863</v>
+        <v>1.189431158643499</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.8646676831962343</v>
+        <v>0.8071956551489008</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.0003442309091015</v>
+        <v>0.0021954985319093</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1.173812454157762</v>
+        <v>1.338456766316861</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
@@ -6730,7 +6703,7 @@
         </is>
       </c>
       <c r="L52" s="16" t="n">
-        <v>1.478403564867371</v>
+        <v>2.749553550268911</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
@@ -6738,10 +6711,10 @@
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>540244.3724948019</v>
+        <v>481280.942470029</v>
       </c>
       <c r="O52" s="17" t="n">
-        <v>990448.01624047</v>
+        <v>882348.3945283964</v>
       </c>
     </row>
     <row r="53">
@@ -6754,10 +6727,10 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -6766,20 +6739,20 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>[0.37618754584223774, 0.7142152441807408]</t>
+          <t>[0.2140432336831392, 0.8035651046893572]</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1.065906197640555</v>
+        <v>1.611794408656238</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.8646676831962343</v>
+        <v>0.8071956551489008</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.0003442309091015</v>
+        <v>0.0021954985319093</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1.173812454157762</v>
+        <v>1.338456766316861</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -6787,7 +6760,7 @@
         </is>
       </c>
       <c r="L53" s="16" t="n">
-        <v>1.121119012101884</v>
+        <v>6.312971074731332</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -6795,10 +6768,10 @@
         </is>
       </c>
       <c r="N53" s="17" t="n">
-        <v>552012.4691349864</v>
+        <v>355163.5034597442</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>1012022.860080801</v>
+        <v>651133.0896761864</v>
       </c>
     </row>
     <row r="54">
@@ -6811,10 +6784,10 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -6823,11 +6796,11 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>{"r": 0.4816303}</t>
+          <t>{"r": 0.59016633}</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1.000000024069098</v>
+        <v>1.000003153775093</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
@@ -6835,7 +6808,7 @@
         </is>
       </c>
       <c r="L54" s="16" t="n">
-        <v>4.41367860242018e-07</v>
+        <v>5.598704943614108e-05</v>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
@@ -6843,10 +6816,10 @@
         </is>
       </c>
       <c r="N54" s="17" t="n">
-        <v>588393.4978637472</v>
+        <v>572448.7436605766</v>
       </c>
       <c r="O54" s="17" t="n">
-        <v>1078721.412750199</v>
+        <v>1049489.36337772</v>
       </c>
     </row>
     <row r="55">
@@ -6859,10 +6832,10 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -6870,7 +6843,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1.005</v>
+        <v>1.014</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
@@ -6878,18 +6851,18 @@
         </is>
       </c>
       <c r="L55" s="16" t="n">
-        <v>0.09114835085964421</v>
+        <v>0.244503673637249</v>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N55" s="17" t="n">
-        <v>585466.1811202466</v>
+        <v>564546.8925396055</v>
       </c>
       <c r="O55" s="17" t="n">
-        <v>1073354.665387116</v>
+        <v>1035002.636322618</v>
       </c>
     </row>
     <row r="56">
@@ -6902,10 +6875,10 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -6913,7 +6886,7 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1.00500625</v>
+        <v>1.014049</v>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
@@ -6921,18 +6894,18 @@
         </is>
       </c>
       <c r="L56" s="16" t="n">
-        <v>0.0912616152888482</v>
+        <v>0.245345509960723</v>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>585462.5401840508</v>
+        <v>564519.6129922345</v>
       </c>
       <c r="O56" s="17" t="n">
-        <v>1073347.990337424</v>
+        <v>1034952.623819098</v>
       </c>
     </row>
     <row r="57">
@@ -6945,10 +6918,10 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.0116</v>
+        <v>0.0019</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -6972,7 +6945,7 @@
         </is>
       </c>
       <c r="L57" s="16" t="n">
-        <v>10.76888692335164</v>
+        <v>10.46123967490033</v>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
@@ -6980,10 +6953,10 @@
         </is>
       </c>
       <c r="N57" s="17" t="n">
-        <v>201152.3844789788</v>
+        <v>195702.0099325404</v>
       </c>
       <c r="O57" s="17" t="n">
-        <v>368779.3715447933</v>
+        <v>358787.0182096511</v>
       </c>
     </row>
     <row r="58"/>
@@ -7019,7 +6992,7 @@
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>Rules-Based AI Selection</t>
+          <t>Framework AI Selection</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
@@ -7029,7 +7002,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>Paid loss triangle — expect materially longer tail than incurred loss. The cutoff is set at 191 months (interval 191-203) with is_monotone_from_here=False, cv_at_starting_age=0.0116 (very low), slope_sign_changes=5 across 15 fitted factors, and n_factors_in_fit=15. The CV is excellent and the starting point is of high quality despite the non-monotone flag, indicating that residual paid development at this age is small but still present. min_selected_ldf=1.000, max_selected_ldf=1.031, avg_selected_ldf=1.016 confirm the late-age LDFs are very small. The last selected LDF at the cutoff is 1.0025 (191-203 interval cutoff reasoning confirms this). Gap Rule (hard requirement): All three exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) have gap_flag=True with gap_to_last_observed=1.174. This gap is extreme — the exponential curve fitted across 15 development periods extrapolates to approximately 1.089 at the starting age while the last selected LDF is 1.0025. The 1.174 gap value (on the factor minus 1 scale) renders all exponential methods categorically disqualified. While R²=0.865 for the exponential fit is above the 0.85 threshold (technically acceptable fit quality), the Gap Rule is a hard requirement that overrides fit quality — these methods are rejected. The skurnick method has gap_flag=False but produces a tail factor of 2.925, which is implausible for paid loss at 191 months of development; its R²=0.459 is also far below the 0.75 reject threshold. Skurnick is rejected on both R² and implausibility grounds. The mcclenahan method (tail~1.000) is designed for count triangles and is inappropriate for paid loss dollar triangles — rejected on triangle type grounds. Remaining valid candidates: bondy (tail=1.0025, materiality_ok=True, pct_of_cdf=0.046%), modified_bondy_double_dev (tail=1.005, materiality_ok=True, pct_of_cdf=0.091%), modified_bondy_square_ratio (tail=1.005, materiality_ok=True, pct_of_cdf=0.091%). All three Bondy variants pass the Gap Rule and have materiality_ok=True. Fit quality: No regression-based R² applies to Bondy variants; LOO std dev for bondy=0.00190, acceptable. Between the three Bondy variants: straight bondy (1.0025) is equal to the last observed factor — for paid loss, which characteristically runs a longer tail than incurred and has genuine residual payment patterns beyond 191 months, using exactly the last observed factor understates the likely residual tail. The modified_bondy_double_dev at 1.005 = 1 + 2*(1.0025-1) provides a small but reasonable incremental load that better reflects the expectation that paid losses continue to develop beyond the final observed age. This is consistent with the paid development data showing continuous small but positive factors through 275 months (factors at 203-215 through 263-275 all range from 1.002 to 1.010 in the selected LDFs). The modified_bondy_square_ratio yields an essentially identical tail (1.00500625 vs 1.005), so modified_bondy_double_dev is selected as the standard convention. Anchor Rule: The materiality anchor applies — pct_of_cdf=0.091% and materiality_ok=True confirm the tail is small relative to the CDF, which supports using a simple Bondy variant rather than requiring a curve fit. Sensitivity: +10% tail delta = $585K, -10% = -$716K — the tail is small but not negligible. The choice between bondy (1.0025) and modified_bondy_double_dev (1.005) represents a reserve difference of approximately $293K, which is immaterial but directionally appropriate given paid loss tail expectations. Prior selection: No prior selections available for year-over-year comparison. Environmental considerations: ULAE handling not separately noted; no excess layer segmentation identified. Paid loss tail selected independently from incurred and count measures. Conclusion: modified_bondy_double_dev is selected because it satisfies the Gap Rule, is appropriate for a paid dollar triangle, provides slightly more tail recognition than straight Bondy consistent with paid loss tail expectations, and is supported by the materiality anchor.</t>
+          <t>Modified Bondy (double deviation) selected, tail factor = 1.0140. Triangle type: Paid Loss — expected to carry the longest tail of the three measures (materially longer than Incurred, which is expected to be materially longer than Reported Count); this ordering is confirmed by the data (Paid tail 1.014 &gt; Incurred tail 1.000 &gt; Reported Count tail 1.000, with Paid the only measure still showing material development at the cutoff). Cutoff is 215 months (well beyond the 60-month Paid Loss minimum), leaving five more empirical selected intervals out to 287 months (1.008, 1.003, 1.005, 1.006, 1.007) before the triangle is physically truncated at 24 years of history — i.e., this is a genuinely open triangle, not a fully run-off one. Diagnostics at the starting age: cv_at_starting_age=0.0019 (very low, stable across accident years), is_monotone_from_here=False and slope_sign_changes=11 reflect noise from thin accident-year counts at the oldest ages rather than a structural break. All three exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) were rejected under the hard Gap Rule: gap_to_last_observed=1.338, far above the 0.005 threshold, because the fitted curve values (~1.19–1.61 at the starting age) are wildly disconnected from the last selected LDFs (~1.003–1.008) — the exponential fit is being pulled by high early-development factors and does not represent late-age behavior, despite a superficially acceptable R²=0.807. Skurnick was rejected on fit quality (R²=0.459, below the 0.75 minimum) and materiality (tail=2.925, 10.46% of CDF, materiality_ok=False) — a clearly unreasonable extrapolation. McClenahan (tail≈1.0000, materiality_ok=True, pct_of_cdf≈0.00006%) was rejected as inappropriate for a paid dollar measure: it is the framework's preferred form for count triangles, and asserting zero remaining tail directly contradicts the still-material ~0.5–0.8% per-period development visible in the last several empirical intervals. Between the two Bondy variants, plain Bondy (1.007) simply repeats the last observed factor and likely understates the true remaining tail given the still-declining-but-nonzero recent pattern; Modified Bondy (double deviation, 1.014) is the standard, more conservative convention for open/truncated paid triangles and is numerically almost identical to modified_bondy_square_ratio (1.01405), which was considered but not preferred (double-deviation form is more standard/interpretable). Anchor Rule satisfied via payment/closure data pattern: the last five selected factors show a slow, still-positive decay (not yet at unity), supporting a modest continued tail rather than an immediate cutoff to 1.000 or an extreme extrapolated value. Sensitivity: +/-10% and +/-20% perturbations of the tail move reserves by roughly +/-565K and +/-1.03M respectively, a moderate but manageable sensitivity given the tail factor's modest size (1.4% of CDF).</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr"/>
@@ -7042,12 +7015,12 @@
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>exp_dev_quick_exact_last</t>
+          <t>bondy</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>exp_dev_quick_exact_last is selected for paid loss. The paid triangle shows continued small but measurable development beyond the 191-month cutoff, with selected LDFs of 1.008, 1.010, 1.002, 1.005, 1.007, and 1.007 across successive intervals out to 275+ months. This is a long-tailed paid triangle where claiming finality at the cutoff would leave residual development unreserved. The exponential decay form with exact-last anchoring is appropriate: R² of 0.865 across 15 fitting points is the strongest goodness-of-fit among all parametric methods, and the LOO stability is excellent (range 1.088–1.090, std dev 0.00034), confirming the curve is robustly identified. The exact_last variant is preferred over the unconstrained exp_dev_quick because it anchors the curve to the last observed LDF (1.0025 at 179-191), reducing the gap discontinuity at the cutoff point and producing a tail of 1.066 versus 1.089. The gap flag (True, gap = 1.174) reflects that the raw exponential parameters project a curve starting above the observed last factor, but the exact_last adjustment corrects for this. The Bondy (1.003) and modified Bondy variants (1.005) are too conservative: they compress the tail well below what the long post-cutoff selected LDF sequence implies. The McClenahan produces essentially 1.000 — clearly insufficient. The Skurnick at 2.925 is implausible and disqualified. The exp_dev_product at 1.008 is closer to Bondy territory and likewise underweights the persistent development observed from 203 to 275 months. A tail factor of 1.066 represents ~1.1% of the CDF, which is material but appropriate for a paid loss triangle with demonstrated development out to the final diagonal.</t>
+          <t>Bondy tail curve (tail factor ~1.007) selected. The empirical Paid Loss tail is well-behaved into the 215-month cutoff, with the last several selected LDFs (1.003-1.017 across 179-275 months) forming a smooth, gently decaying, near-unity progression -- exactly the shape Bondy extrapolates by continuing the most recent observed decay ratio to convergence. Bondy shows no gap flag (clean continuity with the last observed factor) and CV at the starting age is very low (0.0019), confirming a stable base to extrapolate from. By contrast, the exponential decay family (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) all carry gap_flag=True with a large gap_to_last_observed (1.34), meaning the fitted curve jumps away from the empirical trend right at the cutoff -- a red flag for a discontinuous, likely overstated tail; exp_dev_quick_exact_last in particular produces an implausible 1.61 tail factor and 6.3% of CDF, far out of proportion to the thin residual development actually observed. Skurnick fits poorly (R^2=0.46) and produces a similarly inflated 2.93 tail factor with 10.5% of CDF, clearly not credible for a book already 215 months mature with LDFs near 1.01 or lower. McClenahan collapses to essentially 1.0000, implausibly assuming zero further development despite observed factors of 1.006-1.007 persisting through the latest diagonal -- too aggressive given the still-positive, non-zero empirical pattern. Bondy's smooth, low-materiality (0.12% of CDF), gap-free extrapolation of the actual recent decay is the most defensible choice for this paid triangle.</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr"/>
@@ -9602,13 +9575,13 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>1.09</v>
+        <v>1.118</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1</v>
+        <v>1.0005</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>1</v>
@@ -9632,6 +9605,36 @@
         <v>1</v>
       </c>
       <c r="L45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9643,62 +9646,112 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>1.0900 selected. CV_5yr=0.032, CV_3yr=0.013 (very low). All averages are well-defined and internally consistent: 3yr VW=1.133, 5yr VW=1.118, 10yr VW=1.096, all VW=1.062. A notable upward trend exists in the 11-23 column over recent years: 2017=1.124, 2018=1.123, 2019=1.143, 2020=1.060, 2021=1.142, 2022=1.141, 2023=1.116. The 3yr slope is negative (-0.013) and 5yr slope is positive (+0.003), suggesting the very recent AY2023 pulled the 3yr down from the plateau around 1.12-1.14 reached in 2017-2022. The 5yr VW (1.118) captures the sustained elevated period well. The 10yr VW (1.096) includes earlier lower-reporting years (2008-2010 were around 1.047-1.064). The all-year (1.062) is dragged down by 2011's 1.000, which appears anomalous (no new claims reported between 11 and 23 months for 2011). The 5yr/3yr divergence is ~1.5%, within the 3% Bayesian anchoring threshold — no regime change required. AY2023 at 1.116 confirms the factor remains in the 1.10-1.14 band. Selection of 1.090 reflects a modest conservatism below the 5yr VW (1.118), acknowledging the recent slight softening in 2023 (1.116) and 2020 (1.060 — potential COVID-related reporting delay). This is approximately midpoint of the 10yr VW (1.096) and 5yr VW (1.118).</t>
+          <t>1.1180: Selected the 5-year volume-weighted average. cv_5yr=0.032 is low (good credibility), and weighted_3yr (1.133) and weighted_5yr (1.118) agree closely (1.3% apart, below the 3% divergence threshold that would trigger a 3-year override), both clearly above the all-year average (1.0617). Individual factors show a gradual increase from the early 2000s (~1.03-1.07) to recent years (~1.11-1.14), a genuine, sustained shift toward faster early reporting rather than a one-off spike - supported by using the recency-weighted rather than all-year figure.</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>1.0020 selected. CV_5yr=0.000, CV_3yr=0.000 (essentially zero). All averages across every window are 1.000 or 1.001-1.008: 3yr=1.000, 5yr=1.000, 10yr VW=1.007, all VW=1.003. Only 2 AYs show non-1.000 factors: 2001 (1.002), 2009 (1.004), 2014 (1.003), 2015 (1.016), 2016 (1.046). The 2016 factor of 1.046 is a clear outlier (most likely a small administrative re-opening of claims). Nearly all AYs in the last decade show exactly 1.000. The 10yr VW is 1.007 — driven by the 2016 outlier. Selection of 1.002 follows the all-year VW, acknowledging that very occasionally a small number of late-reported claims arrive between 23 and 35 months but the pattern is near-zero. Convergence override applies (all windows within 1.6% of each other with near-zero CV).</t>
+          <t>1.0010: Convergence Override - weighted_all (1.0033), simple_all (1.0037), weighted_5yr (1.0), weighted_3yr (1.0), and avg_exclude_high_low_all (1.0018) are all within a very tight band (&lt;0.4% spread), with cv values near zero across all windows. Selected the midpoint of the converged band.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>1.0000 selected. CV_5yr=0.002 (essentially zero). All averages converge tightly at 1.000: 3yr=1.000, 5yr=1.001, 10yr=1.001, all VW=1.000. The only non-1.000 factors in the triangle are 2001 (1.000 — barely rounds), 2004 (1.004), 2009 (1.000), 2013 (1.005). These are trivially small. Reported counts are fully developed by 35 months in virtually all AYs. Convergence override applies — full convergence to 1.000. Select 1.000.</t>
+          <t>1.0005: Convergence Override - all averaging windows sit between 1.0 and 1.0009 (weighted_all=1.0004, weighted_5yr=1.0008, weighted_3yr=1.0), cv near zero. Selected the midpoint, reflecting the near-complete reporting of claim counts by this maturity.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.0000 selected. CV_5yr=0.003 (essentially zero). All averages: 3yr=1.001, 5yr=1.000, all VW=1.000. Only minor non-1.000 factors in a handful of AYs (e.g., 2004: 1.002, 2013: 1.000, 2018: 1.004, 2017: 0.996). Both positive and negative deviations of &lt;0.5%. Fully converged — select 1.000.</t>
+          <t>1.0000: Convergence Override - weighted_all (0.9998), weighted_5yr (1.0), weighted_3yr (1.0013) are all essentially at unity with near-zero CV. Reported counts are effectively fully developed by this maturity; selected 1.0000, consistent with reported-count development never needing a sub-1.000 factor at this stage absent claim count restatements (none observed in the diagnostics).</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>1.0000 selected. CV_5yr=0.002 (essentially zero). All averages at 0.999-1.002. Tiny deviations only. No systematic development beyond 47 months in reported counts. Select 1.000 — full convergence.</t>
+          <t>1.0000: All averaging windows converge at or just below/above unity (weighted_all=1.0019, weighted_5yr=0.9992, weighted_3yr=0.9987) with cv effectively zero. Selected 1.0000 as the stable, fully-converged reading; this is the last interval selected before the tail cutoff.</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>[CUTOFF] CUTOFF at 71 months: is_monotone_from_here=True. CV is 0.000 for all windows at 71+ months. All factors are 1.000 for virtually every AY from 71 months onward (with only trivial exceptions at earlier intervals). No credible or material development exists beyond 71 months for reported counts. Minimum cutoff for Reported Count is 48 months — this is exceeded. Tail factor for reported count should be 1.000 from 71 months onward. There are 5 intervals remaining (71-83 through 275-287) for tail curve fit, all of which will be 1.000.</t>
+          <t>[CUTOFF] CUTOFF at 83 months (comfortably beyond the 48-month Reported Count minimum). From 71-83 onward, factors are at or extremely close to 1.0 across every averaging window (cv_5yr=0.0 for nearly every remaining column) with no monotonic-decay concerns since there is essentially nothing left to develop - reported claim counts are fully emerged by this point in the data. 17 intervals remain (71-83 through 263-275) for tail curve fitting, far exceeding the ≥3-5 requirement. No structural breaks or diagnostic signals (claim closure, reopenings) suggest any further count development is needed beyond this point.</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>1.0000. No meaningful development. All averages 1.000. Selected at 1.000.</t>
+          <t>1.000 selected. The pattern is flat at 1.0 across all origin years (one minor exception at 2017: 0.9958). Claim counts are fully reported by this maturity for this book.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>1.0000. Flat — all factors are exactly 1.000 across all periods. No development whatsoever.</t>
+          <t>1.000 selected. All observed factors equal 1.0 with no exceptions in the data shown. No further count development expected.</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.0000. All factors are exactly 1.000 except 2015 (0.988 — a downward adjustment, likely closure). No upward development. Selected at 1.000.</t>
+          <t>1.000 selected. All factors equal 1.0 except a single small downward move (2015: 0.9883), likely a claim reclassification/consolidation rather than genuine late reporting. The flat pattern otherwise fully supports unity.</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1.0000. All factors are 1.000 across all periods. No development.</t>
+          <t>1.000 selected. All observed factors are exactly 1.0 — counts are fully reported and stable by this maturity.</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.0000. All factors are 1.000 across all periods. No development.</t>
+          <t>1.000 selected, consistent with a completely flat pattern (all factors 1.0) at this and later maturities.</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>[CUTOFF] Cutoff at 143 months. From 35 months onward, reported count development is exactly 1.000 with no exceptions beyond rounding. The chain-ladder method adds no value beyond 143 months for this measure. A tail factor of 1.000 is appropriate from this point forward, or the count triangle can be considered fully mature at 35 months with a 1.000 tail.</t>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development.</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>1.000 selected. Flat pattern continues with no observed development; this is the last maturity with reasonable cross-sectional support (multiple origin years) in the provided age-to-age data.</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>[CUTOFF] Cutoff at 275: reported claim counts have been completely flat at 1.000 for over a dozen consecutive intervals and only the oldest origin years (2001-2003) reach this maturity, leaving minimal volume to test. Given the count triangle is fully developed well before this point, a unity/flat tail assumption (rather than a fitted curve or further direct selection) is the appropriate way to close out the remaining maturities.</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9850,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>0</v>
@@ -9811,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0005020119305774999</v>
+        <v>0</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
@@ -9834,7 +9887,7 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
@@ -9846,24 +9899,24 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>[0.09000000000000005, 0.022222222222222244]</t>
+          <t>[0.059098020377258115, 0.06502718766576006]</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1</v>
+        <v>0.8433952958429027</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0</v>
+        <v>4.846335792489914e-13</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>2.775557561562892e-17</v>
+        <v>0.0589019796227419</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -9882,7 +9935,7 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>0</v>
@@ -9894,28 +9947,28 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>[0.09000000000000005, 0.022222222222222244]</t>
+          <t>[0.059098020377258115, 0.06502718766576006]</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1.000000000000006</v>
+        <v>1.000000000020209</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1</v>
+        <v>0.8433952958429027</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0</v>
+        <v>4.846335792489914e-13</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>2.775557561562892e-17</v>
+        <v>0.0589019796227419</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L52" s="16" t="n">
-        <v>6.022038536694959e-12</v>
+        <v>1.688579020483803e-08</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
@@ -9923,10 +9976,10 @@
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>808.7423817918761</v>
+        <v>788.8809125695841</v>
       </c>
       <c r="O52" s="17" t="n">
-        <v>1482.694366618436</v>
+        <v>1446.281673044238</v>
       </c>
     </row>
     <row r="53">
@@ -9939,7 +9992,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -9951,28 +10004,28 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>[0.09000000000000005, 0.022222222222222244]</t>
+          <t>[0.059098020377258115, 0.06502718766576006]</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1.000000000000006</v>
+        <v>1.000000000020209</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1</v>
+        <v>0.8433952958429027</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0</v>
+        <v>4.846335792489914e-13</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>2.775557561562892e-17</v>
+        <v>0.0589019796227419</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L53" s="16" t="n">
-        <v>6.022038536694959e-12</v>
+        <v>1.688579020483803e-08</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -9980,10 +10033,10 @@
         </is>
       </c>
       <c r="N53" s="17" t="n">
-        <v>808.7423817918761</v>
+        <v>788.8809125695841</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>1482.694366618436</v>
+        <v>1446.281673044238</v>
       </c>
     </row>
     <row r="54">
@@ -9996,7 +10049,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>0</v>
@@ -10030,7 +10083,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>0</v>
@@ -10064,7 +10117,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>0</v>
@@ -10091,7 +10144,7 @@
         </is>
       </c>
       <c r="L56" s="16" t="n">
-        <v>87.04720147609115</v>
+        <v>83.80894370742</v>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
@@ -10099,10 +10152,10 @@
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>307.7419391756284</v>
+        <v>300.1842703974726</v>
       </c>
       <c r="O56" s="17" t="n">
-        <v>564.1935551553188</v>
+        <v>550.3378290620321</v>
       </c>
     </row>
     <row r="57"/>
@@ -10138,17 +10191,17 @@
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>Rules-Based AI Selection</t>
+          <t>Framework AI Selection</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>mcclenahan</t>
+          <t>bondy</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>Reported count triangle — expect the shortest tail of all measures, materially shorter than incurred loss and paid loss. The cutoff is set at 71 months (interval 71-83) with is_monotone_from_here=True, cv_at_starting_age=0.0012 (essentially zero), slope_sign_changes=0, and n_factors_in_fit=5. This is an exceptional quality starting point: monotone declining LDFs, near-zero variance across accident years, and no structural breaks whatsoever. min_selected_ldf=0.9963, max_selected_ldf=1.027, avg_selected_ldf=1.002 at the cutoff confirm the last selected factors are extremely small and volatile around 1.000. The triangle shows complete practical development by age 71 months: from interval 35-47 onward all selected LDFs are 1.000, and the selected LDFs from 71-83 through 131-143 are all 1.000. Gap Rule: All methods have gap_flag=False. No methods are disqualified by the Gap Rule. Fit quality: The exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) all achieve R²=1.000 and LOO std dev=0.000 — a perfect fit, which is expected when fitting a series of factors that are essentially all 1.000. The tail from all exponential methods is 1.000 (to machine precision). Bondy variants also produce tail=1.000 since the last factor is 1.000. Skurnick produces a tail of 2.928 with R²=0.070 — far below the 0.75 reject threshold — and is rejected. Method preference: Per the framework's preference hierarchy, mcclenahan is the preferred method for count triangles (Reported Count and Closed Count), providing a synthetic incremental approach appropriate for the discrete nature of claim count development. All valid methods converge to tail=1.000 for this triangle, making the method choice consistent regardless of selection. The mcclenahan method is selected following the framework hierarchy for count triangles. Anchor Rule: Materiality anchor fully applies — pct_of_cdf is essentially zero (materiality_ok=True for exponential forms; the reported count triangle is fully developed at cutoff). Sensitivity: +/-10% sensitivity deltas are approximately $809 and -$988 respectively — negligible at this scale, confirming the tail is completely immaterial. The selection of tail=1.000 is empirically supported, theoretically expected for reported counts at 71 months of development, and consistent across all valid methods. Prior selection: No prior selections available for comparison. Environmental considerations: No ULAE, excess layer, or construction defect considerations apply to reported count triangles. This measure is selected independently from paid and incurred loss measures. Conclusion: mcclenahan is selected as the preferred method for count triangles per the framework hierarchy; the selection yields tail=1.000, consistent with all other valid methods and confirmed by the triangle's complete development pattern.</t>
+          <t>Bondy selected, tail factor = 1.0000. Triangle type: Reported Count — expected to carry the shortest tail of all measures, materially shorter than Incurred and Paid Loss; strongly confirmed here, as reported counts flatten to exactly 1.0000 by 47-59 months and stay flat through the remainder of the triangle. Cutoff is 83 months (comfortably beyond the 48-month Reported Count minimum). Diagnostics at the starting age are the cleanest of any measure in this analysis: is_monotone_from_here=True, slope_sign_changes=0, cv_at_starting_age=0.0 — a perfectly flat, structurally unambiguous pattern indicating claims are fully reported by this age. All three non-fitted heuristics (bondy, modified_bondy_double_dev, modified_bondy_square_ratio) agree exactly at tail=1.0 since the last selected LDF is 1.0000, so the selection is not sensitive to which simple method is applied. The exponential forms (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) produced tail factors effectively at unity as well, with a borderline R²=0.843 (in the ambiguous 0.75-0.85 band, not a clean accept), but were rejected under the hard Gap Rule: gap_to_last_observed=0.0589, well above the 0.005 threshold — an unnecessary and disconnected fit for what is already a fully flat, degenerate pattern. Skurnick was clearly rejected: R²=0.070 (essentially no explanatory power), tail=2.628 and pct_of_cdf=83.8% — a nonsensical extrapolation for a count triangle with no remaining development. McClenahan, the framework's typically preferred form for count triangles, was not offered as a scenario for this measure (likely because the fully flat empirical pattern requires no synthetic incremental fitting); Bondy reaches the same null-tail conclusion directly and transparently from the data. Anchor Rule satisfied decisively via materiality (tail is at unity, 0% effective addition to CDF) and is directly supported by the closure/reporting pattern — reported claim counts stop developing entirely at this maturity. No reserve sensitivity attaches to this tail choice.</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr"/>
@@ -10166,7 +10219,7 @@
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>bondy is selected for reported count. The reported count triangle is essentially complete by 35 months: all selected LDFs from 35 months onward are 1.000, with only trivial movement at 23-35 (1.002) and the first interval (1.090 reflecting initial lag in claim registration). Beyond 71 months — the cutoff — there is no detectable development across any accident year. All exponential decay methods converge to a tail factor of effectively 1.000 (R²=1.0, LOO std dev=0.0 with zero residuals), confirming the parametric fit is uninformative — the data is flat by construction. Bondy likewise produces 1.000 with a tight LOO range (0.9998–1.002) and no slope sign changes. Any of the non-Skurnick methods would yield the same result, but Bondy is selected as the most transparent and convention-appropriate choice for a count triangle with demonstrated closure: it imposes minimal structure, requires no parametric assumptions, and will continue to produce 1.000 reliably as the triangle matures. The Skurnick method (tail = 2.628, R² = 0.070) is clearly spurious — its inverse power form is not appropriate for a count measure that is already fully developed — and is excluded. The implied tail of 1.000 correctly reflects that reported counts in this book close out within 3 years of accident year inception with no meaningful IBNR count tail.</t>
+          <t>Bondy tail curve (tail factor = 1.000) selected. Reported claim counts are fully developed well before the 83-month cutoff: every selected LDF from 47-59 months onward is exactly 1.0000, CV and slope are zero across virtually all late intervals, and the empirical age-to-age factors show only trivial, non-systematic noise (e.g., a single 0.9883 blip at 2015/107-119) with no genuine residual reporting pattern. Bondy captures this directly -- is_monotone_from_here=True, cv_at_starting_age=0.0, zero slope sign changes -- producing a clean flat unity tail with no distortion. The exponential decay variants (exp_dev_quick, exp_dev_quick_exact_last, exp_dev_product) mathematically converge to the same ~1.0 result and are technically acceptable (materiality_ok=True, tiny gap), but add unnecessary curve-fitting complexity to a pattern that is already flat by inspection, and their R^2 of 0.84 reflects fitting near-zero residual noise rather than genuine curvature. Skurnick is clearly unsuitable here: R^2=0.07 and a spurious 2.63 tail factor driven by fitting sparse early noise, with materiality_ok=False confirming it should be rejected. For a count triangle that closes out reporting this early, the simplest, most transparent choice -- a flat Bondy tail at unity -- is the most defensible and consistent with claims administration reality (no new claims reported beyond ~7 years of maturity).</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr"/>
